--- a/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="180">
   <si>
     <t>name</t>
   </si>
@@ -615,9 +616,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，$pull指定的字段名和字段值存在</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$pull更新数据，$pull指定的字段名和字段值存在
 2、检查更新结果</t>
   </si>
@@ -659,11 +657,6 @@
 2、检查更新结果</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pull更新符更新数据，对应的字段名不存在，如：
-{$pullt:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]}}，其中&lt;字段名1&gt;不存在
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，覆盖$pull字段值无效取值</t>
   </si>
   <si>
@@ -693,17 +686,294 @@
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，$pull取值为空</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pull更新符更新数据，数据为空，如：
-{$pull:{a:}}    或    {$pull:}
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL中已存在数据，指定$addtose更新符更新数据，对应的字段名不存在，如：
 {$addtose:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]}}，其中&lt;字段名1&gt;不存在
 2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，字段名存在值也存在，则清除指定对象的指定值
+2、db.cs.cl.find查看字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，字段名存在值不存在，则跳过不做任何操作，其他指定字段更新成功
+2、db.cs.cl.find查看字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，字段名不存在则添加字段名和值，则跳过不做任何操作，其他指定字段更新成功
+2、db.cs.cl.find查看字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，指定对象的指定值被清除
+2、db.cs.cl.find查看字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新失败，提示数值超出边界
+2、db.cs.cl.find查看指定更新的字段未被更新</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$addtose指定的字段名非数组对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$addtose更新符更新数据，$addtose指定的字段名非数组对象，如：
+{$addtose:{a:1}}，其中a为string类型的普通记录
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$pull指定的字段名和字段值存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$pop指定的字段名非数组对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$pop更新符更新数据，$pop指定的字段名非数组对象，如：
+{$pop:{a:}}，其中a为string类型的普通记录
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$pull取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$pull指定的字段名非数组对象</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$pull更新符更新数据，$pull指定的字段名非数组对象，如：
+{$pull:{a:1}}，其中a为string类型的普通记录
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，指定$push_all更新数据，$push_all指定的字段名和字段值存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$push_all指定的字段名存在但字段值不存在</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，指定$push_all更新数据，$push_all指定的字段名存在但字段值不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$push_all指定的字段名不存在</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，指定$push_all更新数据，$push_all指定的字段名不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，覆盖$push_all字段值有效取值</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，覆盖$push_all更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
+int：-2147483648、2147483647
+long：-9223372036854775808、9223372036854775807
+float：1.7E-308、1.7E+308
+string:16M
+oid：24位字节
+bool：true、false
+date:1902-01-18、2038-01-18
+timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
+binary(Base64)：
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，覆盖$push_all字段值无效取值</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，覆盖$push_all更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
+int：-2147483649、2147483648
+long：-9223372036854775809、9223372036854775808
+float：1.6E-308、1.8E+308
+string:16.5M
+oid：23、25位字节
+bool：test
+date:1902-01-17、2038-01-19
+timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$push_all指定的字段跟原字段数据类型不一致</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$push_all更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$push_all取值为空</t>
+  </si>
+  <si>
+    <t>update，$push_all指定的字段名非数组对象</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$push_all更新符更新数据，$push_all指定的字段名非数组对象，如：
+{$push_all:{a:1}}，其中a为string类型的普通记录
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$push_all指定的字段名和字段值存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新符：$push_all，向指定数组对象推入每一个指定值。操作对象必须为数组类型的字段。
+如果记录中不存在指定的字段名，插入字段名和数值；如果记录中存在指定的字段名和数值，指定的数值也会插入。
+语法：{$push_all:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$push_all更新符更新数据，数据为空，如：
+{$push_all:{&lt;字段名1&gt;:[,,]  或  {$push_all:{"":[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$pull更新符更新数据，数据为空，如：
+{$push:{&lt;字段名1&gt;:}}  或  {$push:{"":""}}
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$push指定的字段名和字段值存在</t>
+  </si>
+  <si>
+    <t>更新符：$push，清除指定数组对象的指定值。操作对象必须为数组类型的字段。
+如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的值不存在数组对象中，也不做任何操作。
+语法：{$push:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，指定$push更新数据，$push指定的字段名和字段值存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$push指定的字段名存在但字段值不存在</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，指定$push更新数据，$push指定的字段名存在但字段值不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$push指定的字段名不存在</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，指定$push更新数据，$push指定的字段名不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，覆盖$push字段值有效取值</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，覆盖$push更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
+int：-2147483648、2147483647
+long：-9223372036854775808、9223372036854775807
+float：1.7E-308、1.7E+308
+string:16M
+oid：24位字节
+bool：true、false
+date:1902-01-18、2038-01-18
+timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
+binary(Base64)：
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，覆盖$push字段值无效取值</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，覆盖$push更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
+int：-2147483649、2147483648
+long：-9223372036854775809、9223372036854775808
+float：1.6E-308、1.8E+308
+string:16.5M
+oid：23、25位字节
+bool：test
+date:1902-01-17、2038-01-19
+timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$push指定的字段跟原字段数据类型不一致</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$push更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$push取值为空</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$push更新符更新数据，数据为空，如：
+{$push:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$push指定的字段名非数组对象</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$push更新符更新数据，$push指定的字段名非数组对象，如：
+{$push:{a:1}}，其中a为string类型的普通记录
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>更新符：$push，将给定数值插入到目标数组中，操作对象必须为数组类型的字段。如果记录中不存在指定的字段名，插入字段名和数值；如果记录中存在指定的字段名和数值，指定的数值也会插入。
+语法：{$push:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，存在指定的字段名和数值，指定的数值也会插入
+2、db.cs.cl.find查看字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，字段名存在值不存在，则插入指定的值
+2、db.cs.cl.find查看字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，字段名存在值不存在，则插入字段名和数值
+2、db.cs.cl.find查看字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，指定的字段名和值被插入成功
+2、db.cs.cl.find查看字段更新正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -715,6 +985,26 @@
   <si>
     <t>1、更新成功，字段名存在值也存在，则跳过不添加，其他指定字段更新成功
 2、db.cs.cl.find查看字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，字段名存在值不存在，则只添加值，其他指定字段更新成功
+2、db.cs.cl.find查看字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，db.cs.cl.find查看指定更新的字段已更新
+2、指定更新的字段名对应的字段值已增加指定的值，数据更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，不存在的字段名系统自动补充该字段名和指定的值
+2、db.cs.cl.find查看指定更新的字段已更新，不存在的字段名新增，字段值为指定添加的值，更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新失败，提示参数错误，提示信息合理准确
+2、db.cs.cl.find查看指定更新的字段未被更新</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -874,8 +1164,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I66" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I66"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I80" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I80"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1194,7 +1484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I70"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
@@ -1713,7 +2003,7 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>36</v>
@@ -1774,12 +2064,9 @@
       </c>
       <c r="I29" s="4"/>
     </row>
-    <row r="30" spans="1:9" ht="162">
+    <row r="30" spans="1:9" ht="67.5">
       <c r="A30" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>92</v>
+        <v>126</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>26</v>
@@ -1788,16 +2075,19 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="2" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="I30" s="4"/>
     </row>
-    <row r="31" spans="1:9" ht="108">
+    <row r="31" spans="1:9" ht="162">
       <c r="A31" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>92</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>26</v>
@@ -1806,16 +2096,16 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="I31" s="4"/>
     </row>
     <row r="32" spans="1:9" ht="108">
       <c r="A32" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>26</v>
@@ -1824,34 +2114,34 @@
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>100</v>
       </c>
       <c r="I32" s="4"/>
     </row>
-    <row r="33" spans="1:9" ht="67.5">
+    <row r="33" spans="1:9" ht="108">
       <c r="A33" s="2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="2" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>38</v>
+        <v>100</v>
       </c>
       <c r="I33" s="4"/>
     </row>
     <row r="34" spans="1:9" ht="67.5">
       <c r="A34" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>104</v>
@@ -1860,37 +2150,34 @@
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>38</v>
       </c>
       <c r="I34" s="4"/>
     </row>
-    <row r="35" spans="1:9" ht="121.5">
+    <row r="35" spans="1:9" ht="67.5">
       <c r="A35" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>26</v>
+        <v>104</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="2" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>126</v>
+        <v>38</v>
       </c>
       <c r="I35" s="4"/>
     </row>
-    <row r="36" spans="1:9" ht="54">
+    <row r="36" spans="1:9" ht="67.5">
       <c r="A36" s="2" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>26</v>
@@ -1899,16 +2186,19 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="2" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="I36" s="4"/>
     </row>
-    <row r="37" spans="1:9" ht="54">
+    <row r="37" spans="1:9" ht="121.5">
       <c r="A37" s="2" t="s">
-        <v>113</v>
+        <v>128</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>174</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>26</v>
@@ -1917,16 +2207,16 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="2" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="I37" s="4"/>
     </row>
-    <row r="38" spans="1:9" ht="168" customHeight="1">
+    <row r="38" spans="1:9" ht="67.5">
       <c r="A38" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>26</v>
@@ -1935,16 +2225,16 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>35</v>
+        <v>176</v>
       </c>
       <c r="I38" s="4"/>
     </row>
-    <row r="39" spans="1:9" ht="81">
+    <row r="39" spans="1:9" ht="67.5">
       <c r="A39" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>26</v>
@@ -1953,16 +2243,16 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="I39" s="4"/>
     </row>
     <row r="40" spans="1:9" ht="168" customHeight="1">
       <c r="A40" s="2" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>26</v>
@@ -1971,16 +2261,16 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="I40" s="4"/>
     </row>
-    <row r="41" spans="1:9" ht="67.5">
+    <row r="41" spans="1:9" ht="168" customHeight="1">
       <c r="A41" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>26</v>
@@ -1989,16 +2279,16 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>38</v>
+        <v>178</v>
       </c>
       <c r="I41" s="4"/>
     </row>
     <row r="42" spans="1:9" ht="67.5">
       <c r="A42" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>26</v>
@@ -2007,79 +2297,145 @@
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="I42" s="4"/>
     </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="2"/>
+    <row r="43" spans="1:9" ht="67.5">
+      <c r="A43" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
-      <c r="G43" s="2"/>
-      <c r="H43" s="2"/>
+      <c r="G43" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="I43" s="4"/>
     </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="2"/>
+    <row r="44" spans="1:9" ht="67.5">
+      <c r="A44" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
+      <c r="G44" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="I44" s="4"/>
     </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="2"/>
+    <row r="45" spans="1:9" ht="148.5">
+      <c r="A45" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
+      <c r="G45" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>175</v>
+      </c>
       <c r="I45" s="4"/>
     </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="2"/>
+    <row r="46" spans="1:9" ht="67.5">
+      <c r="A46" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
+      <c r="G46" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>176</v>
+      </c>
       <c r="I46" s="4"/>
     </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="2"/>
+    <row r="47" spans="1:9" ht="67.5">
+      <c r="A47" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
-      <c r="G47" s="2"/>
-      <c r="H47" s="2"/>
+      <c r="G47" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>87</v>
+      </c>
       <c r="I47" s="4"/>
     </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="2"/>
+    <row r="48" spans="1:9" ht="168" customHeight="1">
+      <c r="A48" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
-      <c r="G48" s="2"/>
-      <c r="H48" s="2"/>
+      <c r="G48" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="I48" s="4"/>
     </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="2"/>
+    <row r="49" spans="1:9" ht="168" customHeight="1">
+      <c r="A49" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
-      <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
+      <c r="G49" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>178</v>
+      </c>
       <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" ht="67.5">
       <c r="A50" s="2" t="s">
-        <v>33</v>
+        <v>143</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>26</v>
@@ -2087,13 +2443,17 @@
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
-      <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
+      <c r="G50" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" ht="67.5">
       <c r="A51" s="2" t="s">
-        <v>32</v>
+        <v>145</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>26</v>
@@ -2102,95 +2462,180 @@
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H51" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="I51" s="4"/>
     </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="2"/>
+    <row r="52" spans="1:9" ht="81">
+      <c r="A52" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
-      <c r="G52" s="2"/>
-      <c r="H52" s="2"/>
+      <c r="G52" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>179</v>
+      </c>
       <c r="I52" s="4"/>
     </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="2"/>
+    <row r="53" spans="1:9" ht="108">
+      <c r="A53" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
-      <c r="G53" s="2"/>
-      <c r="H53" s="2"/>
+      <c r="G53" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>170</v>
+      </c>
       <c r="I53" s="4"/>
     </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="2"/>
+    <row r="54" spans="1:9" ht="67.5">
+      <c r="A54" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
-      <c r="G54" s="2"/>
-      <c r="H54" s="2"/>
+      <c r="G54" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>171</v>
+      </c>
       <c r="I54" s="4"/>
     </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="2"/>
+    <row r="55" spans="1:9" ht="67.5">
+      <c r="A55" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
-      <c r="G55" s="2"/>
-      <c r="H55" s="2"/>
+      <c r="G55" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>172</v>
+      </c>
       <c r="I55" s="4"/>
     </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="2"/>
+    <row r="56" spans="1:9" ht="168" customHeight="1">
+      <c r="A56" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
-      <c r="G56" s="2"/>
-      <c r="H56" s="2"/>
+      <c r="G56" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="I56" s="4"/>
     </row>
-    <row r="57" spans="1:9">
-      <c r="A57" s="2"/>
+    <row r="57" spans="1:9" ht="168" customHeight="1">
+      <c r="A57" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
-      <c r="G57" s="2"/>
-      <c r="H57" s="2"/>
+      <c r="G57" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="I57" s="4"/>
     </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="2"/>
+    <row r="58" spans="1:9" ht="67.5">
+      <c r="A58" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
+      <c r="G58" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="I58" s="4"/>
     </row>
-    <row r="59" spans="1:9">
-      <c r="A59" s="2"/>
+    <row r="59" spans="1:9" ht="67.5">
+      <c r="A59" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
+      <c r="G59" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="I59" s="4"/>
     </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="2"/>
+    <row r="60" spans="1:9" ht="67.5">
+      <c r="A60" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
-      <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
+      <c r="G60" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="I60" s="4"/>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" s="2"/>
-      <c r="B61" s="6"/>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
@@ -2201,45 +2646,184 @@
     <row r="62" spans="1:9">
       <c r="A62" s="2"/>
       <c r="D62" s="4"/>
+      <c r="E62" s="4"/>
+      <c r="F62" s="4"/>
       <c r="G62" s="2"/>
       <c r="H62" s="2"/>
+      <c r="I62" s="4"/>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" s="2"/>
       <c r="D63" s="4"/>
+      <c r="E63" s="4"/>
+      <c r="F63" s="4"/>
       <c r="G63" s="2"/>
       <c r="H63" s="2"/>
-    </row>
-    <row r="64" spans="1:9">
-      <c r="A64" s="2"/>
-      <c r="B64" s="6"/>
+      <c r="I63" s="4"/>
+    </row>
+    <row r="64" spans="1:9" ht="67.5">
+      <c r="A64" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D64" s="4"/>
+      <c r="E64" s="4"/>
+      <c r="F64" s="4"/>
       <c r="G64" s="2"/>
       <c r="H64" s="2"/>
-    </row>
-    <row r="65" spans="1:8">
-      <c r="A65" s="2"/>
+      <c r="I64" s="4"/>
+    </row>
+    <row r="65" spans="1:9" ht="67.5">
+      <c r="A65" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D65" s="4"/>
-      <c r="G65" s="2"/>
+      <c r="E65" s="4"/>
+      <c r="F65" s="4"/>
+      <c r="G65" s="2" t="s">
+        <v>81</v>
+      </c>
       <c r="H65" s="2"/>
-    </row>
-    <row r="66" spans="1:8">
+      <c r="I65" s="4"/>
+    </row>
+    <row r="66" spans="1:9">
       <c r="A66" s="2"/>
       <c r="D66" s="4"/>
+      <c r="E66" s="4"/>
+      <c r="F66" s="4"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
-    </row>
-    <row r="67" spans="1:8">
+      <c r="I66" s="4"/>
+    </row>
+    <row r="67" spans="1:9">
       <c r="A67" s="2"/>
-    </row>
-    <row r="68" spans="1:8">
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="4"/>
+    </row>
+    <row r="68" spans="1:9">
       <c r="A68" s="2"/>
-    </row>
-    <row r="69" spans="1:8">
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2"/>
+      <c r="I68" s="4"/>
+    </row>
+    <row r="69" spans="1:9">
       <c r="A69" s="2"/>
-    </row>
-    <row r="70" spans="1:8">
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2"/>
+      <c r="I69" s="4"/>
+    </row>
+    <row r="70" spans="1:9">
       <c r="A70" s="2"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="2"/>
+      <c r="H70" s="2"/>
+      <c r="I70" s="4"/>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" s="2"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="2"/>
+      <c r="H71" s="2"/>
+      <c r="I71" s="4"/>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" s="2"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="2"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="4"/>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" s="2"/>
+      <c r="D73" s="4"/>
+      <c r="E73" s="4"/>
+      <c r="F73" s="4"/>
+      <c r="G73" s="2"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="4"/>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" s="2"/>
+      <c r="D74" s="4"/>
+      <c r="E74" s="4"/>
+      <c r="F74" s="4"/>
+      <c r="G74" s="2"/>
+      <c r="H74" s="2"/>
+      <c r="I74" s="4"/>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" s="2"/>
+      <c r="B75" s="6"/>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="4"/>
+      <c r="G75" s="2"/>
+      <c r="H75" s="2"/>
+      <c r="I75" s="4"/>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" s="2"/>
+      <c r="D76" s="4"/>
+      <c r="G76" s="2"/>
+      <c r="H76" s="2"/>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" s="2"/>
+      <c r="D77" s="4"/>
+      <c r="G77" s="2"/>
+      <c r="H77" s="2"/>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" s="2"/>
+      <c r="B78" s="6"/>
+      <c r="D78" s="4"/>
+      <c r="G78" s="2"/>
+      <c r="H78" s="2"/>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" s="2"/>
+      <c r="D79" s="4"/>
+      <c r="G79" s="2"/>
+      <c r="H79" s="2"/>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" s="2"/>
+      <c r="D80" s="4"/>
+      <c r="G80" s="2"/>
+      <c r="H80" s="2"/>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="2"/>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="2"/>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="2"/>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2249,4 +2833,173 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
+  <cols>
+    <col min="1" max="3" width="30.5" customWidth="1"/>
+    <col min="7" max="8" width="37.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="121.5">
+      <c r="A1" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I1" s="4"/>
+    </row>
+    <row r="2" spans="1:9" s="1" customFormat="1" ht="54">
+      <c r="A2" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="54">
+      <c r="A3" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="4"/>
+      <c r="E3" s="4"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I3" s="4"/>
+    </row>
+    <row r="4" spans="1:9" s="1" customFormat="1" ht="168" customHeight="1">
+      <c r="A4" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="168" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="67.5">
+      <c r="A6" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:9" s="1" customFormat="1" ht="67.5">
+      <c r="A7" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7" s="4"/>
+    </row>
+    <row r="8" spans="1:9" s="1" customFormat="1" ht="81">
+      <c r="A8" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="4"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="218">
   <si>
     <t>name</t>
   </si>
@@ -692,26 +692,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、更新成功，字段名存在值也存在，则清除指定对象的指定值
-2、db.cs.cl.find查看字段更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、更新成功，字段名存在值不存在，则跳过不做任何操作，其他指定字段更新成功
-2、db.cs.cl.find查看字段更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、更新成功，字段名不存在则添加字段名和值，则跳过不做任何操作，其他指定字段更新成功
-2、db.cs.cl.find查看字段更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、更新成功，指定对象的指定值被清除
-2、db.cs.cl.find查看字段更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新失败，提示数值超出边界
 2、db.cs.cl.find查看指定更新的字段未被更新</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -836,22 +816,6 @@
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，$push_all指定的字段名和字段值存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新符：$push_all，向指定数组对象推入每一个指定值。操作对象必须为数组类型的字段。
-如果记录中不存在指定的字段名，插入字段名和数值；如果记录中存在指定的字段名和数值，指定的数值也会插入。
-语法：{$push_all:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$push_all更新符更新数据，数据为空，如：
-{$push_all:{&lt;字段名1&gt;:[,,]  或  {$push_all:{"":[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL中已存在数据，指定$pull更新符更新数据，数据为空，如：
 {$push:{&lt;字段名1&gt;:}}  或  {$push:{"":""}}
 2、检查更新结果</t>
@@ -859,11 +823,6 @@
   </si>
   <si>
     <t>update，$push指定的字段名和字段值存在</t>
-  </si>
-  <si>
-    <t>更新符：$push，清除指定数组对象的指定值。操作对象必须为数组类型的字段。
-如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的值不存在数组对象中，也不做任何操作。
-语法：{$push:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
   </si>
   <si>
     <t>1、进入sdb，update更新CL指定数据，指定$push更新数据，$push指定的字段名和字段值存在
@@ -1007,12 +966,290 @@
 2、db.cs.cl.find查看指定更新的字段未被更新</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>update，$push_all指定的字段名和字段值存在</t>
+  </si>
+  <si>
+    <t>update，$pull_all指定的字段名和字段值存在</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，指定$pull_all更新数据，$pull_all指定的字段名和字段值存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$pull_all指定的字段名存在但字段值不存在</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，指定$pull_all更新数据，$pull_all指定的字段名存在但字段值不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$pull_all指定的字段名不存在</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，指定$pull_all更新数据，$pull_all指定的字段名不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，覆盖$pull_all字段值有效取值</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，覆盖$pull_all更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
+int：-2147483648、2147483647
+long：-9223372036854775808、9223372036854775807
+float：1.7E-308、1.7E+308
+string:16M
+oid：24位字节
+bool：true、false
+date:1902-01-18、2038-01-18
+timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
+binary(Base64)：
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，覆盖$pull_all字段值无效取值</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，覆盖$pull_all更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
+int：-2147483649、2147483648
+long：-9223372036854775809、9223372036854775808
+float：1.6E-308、1.8E+308
+string:16.5M
+oid：23、25位字节
+bool：test
+date:1902-01-17、2038-01-19
+timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$pull_all指定的字段跟原字段数据类型不一致</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$pull_all更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$pull_all取值为空</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$pull_all更新符更新数据，数据为空，如：
+{$pull_all:{&lt;字段名1&gt;:[,,]  或  {$pull_all:{"":[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$pull_all指定的字段名非数组对象</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$pull_all更新符更新数据，$pull_all指定的字段名非数组对象，如：
+{$pull_all:{a:1}}，其中a为string类型的普通记录
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>更新符：$pull_all，清除指定数组对象的指定值。操作对象必须为数组类型的字段。
+如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的值不存在数组对象中，也不做任何操作。
+语法：{$pull_all:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新符：$push_all，向指定数组对象推入每一个指定值。操作对象必须为数组类型的字段。
+如果记录中不存在指定的字段名，插入字段名和数值；如果记录中存在指定的字段名和数值，指定的数值也会插入。
+语法：{$push_all:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$push_all更新符更新数据，数据为空，如：
+{$push_all:{&lt;字段名1&gt;:[,,]  或  {$push_all:{"":[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，指定$replace更新数据，$replace指定的字段名和字段值存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$replace指定的字段名不存在</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，指定$replace更新数据，$replace指定的字段名不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，覆盖$replace字段值有效取值</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，覆盖$replace更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
+int：-2147483648、2147483647
+long：-9223372036854775808、9223372036854775807
+float：1.7E-308、1.7E+308
+string:16M
+oid：24位字节
+bool：true、false
+date:1902-01-18、2038-01-18
+timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
+binary(Base64)：
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，覆盖$replace字段值无效取值</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，覆盖$replace更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
+int：-2147483649、2147483648
+long：-9223372036854775809、9223372036854775808
+float：1.6E-308、1.8E+308
+string:16.5M
+oid：23、25位字节
+bool：test
+date:1902-01-17、2038-01-19
+timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$replace指定的字段跟原字段数据类型不一致</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$replace更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>update，$replace取值为空</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$replace更新符更新数据，数据为空，如：
+{$replace:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>更新符：$replace， 操作是将文档全部替换成"{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}"。除了保留原始的 _id 之外，原始文档的内容会全部清空，并替换成"{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}"。
+语法：{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
+语法：{$replace:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$replace指定的字段名存在</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，指定的字段名存在则直接替换为指定的值
+2、db.cs.cl.find查看字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1、更新成功，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>字段名不存在则跳过不做替换</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+2、db.cs.cl.find查看字段更新正确</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，字段名不存在，则插入字段名和数值
+2、db.cs.cl.find查看字段更新正确</t>
+  </si>
+  <si>
+    <t>1、更新成功，指定的值被替换成功
+2、db.cs.cl.find查看字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中已存在数据，指定$replace更新符更新数据，数据为空，如：
+{$replace:{&lt;字段名1&gt;:}}  或  {$replace:{"":&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、为空时，更新所有记录，不为空时，更新符合条件的记录。
+2、格式：[{"字段名1":{"匹配符1":"值1"},"字段名2":{"匹配符2":"值2"},...}]  
+匹配符：$gt、$gte、$lt、$lte……</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、字段名存在，为空
+2、按匹配符匹配记录更新</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、字段名为空串
+2、格式错误</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、字段名为空串
+2、格式错误</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、字段值为null，如：{"":null}
+2、字段值不为空，如：{"":"&lt; indexname &gt;"}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>格式错误</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，cond</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，hint</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1034,6 +1271,21 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1043,7 +1295,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1051,11 +1303,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1074,6 +1341,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1164,8 +1437,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I80" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I80"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I96" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I96"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1484,7 +1757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
@@ -2066,7 +2339,7 @@
     </row>
     <row r="30" spans="1:9" ht="67.5">
       <c r="A30" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>26</v>
@@ -2075,7 +2348,7 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="2" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>38</v>
@@ -2177,7 +2450,7 @@
     </row>
     <row r="36" spans="1:9" ht="67.5">
       <c r="A36" s="2" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>26</v>
@@ -2186,7 +2459,7 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>38</v>
@@ -2195,10 +2468,10 @@
     </row>
     <row r="37" spans="1:9" ht="121.5">
       <c r="A37" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>26</v>
@@ -2210,7 +2483,7 @@
         <v>109</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I37" s="4"/>
     </row>
@@ -2228,7 +2501,7 @@
         <v>111</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I38" s="4"/>
     </row>
@@ -2264,7 +2537,7 @@
         <v>115</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I40" s="4"/>
     </row>
@@ -2282,7 +2555,7 @@
         <v>117</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I41" s="4"/>
     </row>
@@ -2300,13 +2573,13 @@
         <v>119</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I42" s="4"/>
     </row>
     <row r="43" spans="1:9" ht="67.5">
       <c r="A43" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>26</v>
@@ -2315,16 +2588,16 @@
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="2" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I43" s="4"/>
     </row>
     <row r="44" spans="1:9" ht="67.5">
       <c r="A44" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>26</v>
@@ -2333,19 +2606,19 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" ht="148.5">
       <c r="A45" s="2" t="s">
-        <v>148</v>
+        <v>173</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>26</v>
@@ -2354,16 +2627,16 @@
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="2" t="s">
-        <v>134</v>
+        <v>174</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" ht="67.5">
       <c r="A46" s="2" t="s">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>26</v>
@@ -2372,16 +2645,16 @@
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="2" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" ht="67.5">
       <c r="A47" s="2" t="s">
-        <v>137</v>
+        <v>177</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>26</v>
@@ -2390,7 +2663,7 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="2" t="s">
-        <v>138</v>
+        <v>178</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>87</v>
@@ -2399,7 +2672,7 @@
     </row>
     <row r="48" spans="1:9" ht="168" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>139</v>
+        <v>179</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>26</v>
@@ -2408,16 +2681,16 @@
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="2" t="s">
-        <v>140</v>
+        <v>180</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" ht="168" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>141</v>
+        <v>181</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>26</v>
@@ -2426,16 +2699,16 @@
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="2" t="s">
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" ht="67.5">
       <c r="A50" s="2" t="s">
-        <v>143</v>
+        <v>183</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>26</v>
@@ -2444,16 +2717,16 @@
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="2" t="s">
-        <v>144</v>
+        <v>184</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I50" s="4"/>
     </row>
     <row r="51" spans="1:9" ht="67.5">
       <c r="A51" s="2" t="s">
-        <v>145</v>
+        <v>185</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>26</v>
@@ -2462,16 +2735,16 @@
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="2" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I51" s="4"/>
     </row>
     <row r="52" spans="1:9" ht="81">
       <c r="A52" s="2" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>26</v>
@@ -2480,19 +2753,19 @@
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="2" t="s">
-        <v>147</v>
+        <v>188</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="I52" s="4"/>
     </row>
     <row r="53" spans="1:9" ht="108">
       <c r="A53" s="2" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>26</v>
@@ -2501,16 +2774,16 @@
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="2" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="I53" s="4"/>
     </row>
     <row r="54" spans="1:9" ht="67.5">
       <c r="A54" s="2" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>26</v>
@@ -2519,16 +2792,16 @@
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="2" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="I54" s="4"/>
     </row>
     <row r="55" spans="1:9" ht="67.5">
       <c r="A55" s="2" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>26</v>
@@ -2537,16 +2810,16 @@
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="2" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>172</v>
+        <v>207</v>
       </c>
       <c r="I55" s="4"/>
     </row>
     <row r="56" spans="1:9" ht="168" customHeight="1">
       <c r="A56" s="2" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>26</v>
@@ -2555,16 +2828,16 @@
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="2" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="I56" s="4"/>
     </row>
     <row r="57" spans="1:9" ht="168" customHeight="1">
       <c r="A57" s="2" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>26</v>
@@ -2573,16 +2846,16 @@
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="2" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="I57" s="4"/>
     </row>
     <row r="58" spans="1:9" ht="67.5">
       <c r="A58" s="2" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>26</v>
@@ -2591,7 +2864,7 @@
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
       <c r="G58" s="2" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>38</v>
@@ -2600,7 +2873,7 @@
     </row>
     <row r="59" spans="1:9" ht="67.5">
       <c r="A59" s="2" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>26</v>
@@ -2609,7 +2882,7 @@
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
       <c r="G59" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>38</v>
@@ -2618,7 +2891,7 @@
     </row>
     <row r="60" spans="1:9" ht="67.5">
       <c r="A60" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>26</v>
@@ -2627,43 +2900,73 @@
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
       <c r="G60" s="2" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>38</v>
       </c>
       <c r="I60" s="4"/>
     </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="2"/>
+    <row r="61" spans="1:9" ht="148.5">
+      <c r="A61" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
+      <c r="G61" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="I61" s="4"/>
     </row>
-    <row r="62" spans="1:9">
-      <c r="A62" s="2"/>
+    <row r="62" spans="1:9" ht="54">
+      <c r="A62" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
-      <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
+      <c r="G62" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>163</v>
+      </c>
       <c r="I62" s="4"/>
     </row>
-    <row r="63" spans="1:9">
-      <c r="A63" s="2"/>
+    <row r="63" spans="1:9" ht="67.5">
+      <c r="A63" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
-      <c r="G63" s="2"/>
-      <c r="H63" s="2"/>
+      <c r="G63" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="H63" s="2" t="s">
+        <v>207</v>
+      </c>
       <c r="I63" s="4"/>
     </row>
-    <row r="64" spans="1:9" ht="67.5">
+    <row r="64" spans="1:9" ht="168" customHeight="1">
       <c r="A64" s="2" t="s">
-        <v>33</v>
+        <v>135</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>26</v>
@@ -2671,13 +2974,17 @@
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
-      <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
+      <c r="G64" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="I64" s="4"/>
     </row>
-    <row r="65" spans="1:9" ht="67.5">
+    <row r="65" spans="1:9" ht="168" customHeight="1">
       <c r="A65" s="2" t="s">
-        <v>32</v>
+        <v>137</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>26</v>
@@ -2686,95 +2993,188 @@
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H65" s="2"/>
+        <v>138</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="I65" s="4"/>
     </row>
-    <row r="66" spans="1:9">
-      <c r="A66" s="2"/>
+    <row r="66" spans="1:9" ht="67.5">
+      <c r="A66" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
-      <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
+      <c r="G66" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="I66" s="4"/>
     </row>
-    <row r="67" spans="1:9">
-      <c r="A67" s="2"/>
+    <row r="67" spans="1:9" ht="67.5">
+      <c r="A67" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
-      <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
+      <c r="G67" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H67" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="I67" s="4"/>
     </row>
-    <row r="68" spans="1:9">
-      <c r="A68" s="2"/>
+    <row r="68" spans="1:9" ht="81">
+      <c r="A68" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
-      <c r="G68" s="2"/>
-      <c r="H68" s="2"/>
+      <c r="G68" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="I68" s="4"/>
     </row>
-    <row r="69" spans="1:9">
-      <c r="A69" s="2"/>
+    <row r="69" spans="1:9" ht="148.5">
+      <c r="A69" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
-      <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
+      <c r="G69" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>205</v>
+      </c>
       <c r="I69" s="4"/>
     </row>
-    <row r="70" spans="1:9">
-      <c r="A70" s="2"/>
+    <row r="70" spans="1:9" ht="67.5">
+      <c r="A70" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
-      <c r="G70" s="2"/>
-      <c r="H70" s="2"/>
+      <c r="G70" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="I70" s="4"/>
     </row>
-    <row r="71" spans="1:9">
-      <c r="A71" s="2"/>
+    <row r="71" spans="1:9" ht="168" customHeight="1">
+      <c r="A71" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
-      <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
+      <c r="G71" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H71" s="2" t="s">
+        <v>208</v>
+      </c>
       <c r="I71" s="4"/>
     </row>
-    <row r="72" spans="1:9">
-      <c r="A72" s="2"/>
+    <row r="72" spans="1:9" ht="168" customHeight="1">
+      <c r="A72" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
-      <c r="G72" s="2"/>
-      <c r="H72" s="2"/>
+      <c r="G72" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>121</v>
+      </c>
       <c r="I72" s="4"/>
     </row>
-    <row r="73" spans="1:9">
-      <c r="A73" s="2"/>
+    <row r="73" spans="1:9" ht="67.5">
+      <c r="A73" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
-      <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
+      <c r="G73" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="I73" s="4"/>
     </row>
-    <row r="74" spans="1:9">
-      <c r="A74" s="2"/>
+    <row r="74" spans="1:9" ht="67.5">
+      <c r="A74" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
-      <c r="G74" s="2"/>
-      <c r="H74" s="2"/>
+      <c r="G74" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>38</v>
+      </c>
       <c r="I74" s="4"/>
     </row>
-    <row r="75" spans="1:9">
-      <c r="A75" s="2"/>
-      <c r="B75" s="6"/>
+    <row r="75" spans="1:9" ht="94.5">
+      <c r="A75" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
@@ -2782,48 +3182,222 @@
       <c r="H75" s="2"/>
       <c r="I75" s="4"/>
     </row>
-    <row r="76" spans="1:9">
+    <row r="76" spans="1:9" ht="25.5">
       <c r="A76" s="2"/>
+      <c r="B76" s="7" t="s">
+        <v>211</v>
+      </c>
       <c r="D76" s="4"/>
+      <c r="E76" s="4"/>
+      <c r="F76" s="4"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
-    </row>
-    <row r="77" spans="1:9">
+      <c r="I76" s="4"/>
+    </row>
+    <row r="77" spans="1:9" ht="25.5">
       <c r="A77" s="2"/>
+      <c r="B77" s="7" t="s">
+        <v>213</v>
+      </c>
       <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
       <c r="G77" s="2"/>
       <c r="H77" s="2"/>
-    </row>
-    <row r="78" spans="1:9">
-      <c r="A78" s="2"/>
-      <c r="B78" s="6"/>
+      <c r="I77" s="4"/>
+    </row>
+    <row r="78" spans="1:9" ht="38.25">
+      <c r="A78" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="B78" s="7" t="s">
+        <v>214</v>
+      </c>
       <c r="D78" s="4"/>
+      <c r="E78" s="4"/>
+      <c r="F78" s="4"/>
       <c r="G78" s="2"/>
       <c r="H78" s="2"/>
+      <c r="I78" s="4"/>
     </row>
     <row r="79" spans="1:9">
-      <c r="A79" s="2"/>
+      <c r="A79" s="5"/>
+      <c r="B79" s="7" t="s">
+        <v>215</v>
+      </c>
       <c r="D79" s="4"/>
+      <c r="E79" s="4"/>
+      <c r="F79" s="4"/>
       <c r="G79" s="2"/>
       <c r="H79" s="2"/>
-    </row>
-    <row r="80" spans="1:9">
-      <c r="A80" s="2"/>
+      <c r="I79" s="4"/>
+    </row>
+    <row r="80" spans="1:9" ht="67.5">
+      <c r="A80" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>26</v>
+      </c>
       <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
       <c r="G80" s="2"/>
       <c r="H80" s="2"/>
-    </row>
-    <row r="81" spans="1:1">
-      <c r="A81" s="2"/>
-    </row>
-    <row r="82" spans="1:1">
+      <c r="I80" s="4"/>
+    </row>
+    <row r="81" spans="1:9" ht="67.5">
+      <c r="A81" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D81" s="4"/>
+      <c r="E81" s="4"/>
+      <c r="F81" s="4"/>
+      <c r="G81" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H81" s="2"/>
+      <c r="I81" s="4"/>
+    </row>
+    <row r="82" spans="1:9" ht="25.5">
       <c r="A82" s="2"/>
-    </row>
-    <row r="83" spans="1:1">
+      <c r="C82" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="4"/>
+      <c r="G82" s="2"/>
+      <c r="H82" s="2"/>
+      <c r="I82" s="4"/>
+    </row>
+    <row r="83" spans="1:9">
       <c r="A83" s="2"/>
-    </row>
-    <row r="84" spans="1:1">
+      <c r="D83" s="4"/>
+      <c r="E83" s="4"/>
+      <c r="F83" s="4"/>
+      <c r="G83" s="2"/>
+      <c r="H83" s="2"/>
+      <c r="I83" s="4"/>
+    </row>
+    <row r="84" spans="1:9">
       <c r="A84" s="2"/>
+      <c r="D84" s="4"/>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="2"/>
+      <c r="H84" s="2"/>
+      <c r="I84" s="4"/>
+    </row>
+    <row r="85" spans="1:9">
+      <c r="A85" s="2"/>
+      <c r="D85" s="4"/>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="2"/>
+      <c r="H85" s="2"/>
+      <c r="I85" s="4"/>
+    </row>
+    <row r="86" spans="1:9">
+      <c r="A86" s="2"/>
+      <c r="D86" s="4"/>
+      <c r="E86" s="4"/>
+      <c r="F86" s="4"/>
+      <c r="G86" s="2"/>
+      <c r="H86" s="2"/>
+      <c r="I86" s="4"/>
+    </row>
+    <row r="87" spans="1:9">
+      <c r="A87" s="2"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="2"/>
+      <c r="H87" s="2"/>
+      <c r="I87" s="4"/>
+    </row>
+    <row r="88" spans="1:9">
+      <c r="A88" s="2"/>
+      <c r="D88" s="4"/>
+      <c r="E88" s="4"/>
+      <c r="F88" s="4"/>
+      <c r="G88" s="2"/>
+      <c r="H88" s="2"/>
+      <c r="I88" s="4"/>
+    </row>
+    <row r="89" spans="1:9">
+      <c r="A89" s="2"/>
+      <c r="D89" s="4"/>
+      <c r="E89" s="4"/>
+      <c r="F89" s="4"/>
+      <c r="G89" s="2"/>
+      <c r="H89" s="2"/>
+      <c r="I89" s="4"/>
+    </row>
+    <row r="90" spans="1:9">
+      <c r="A90" s="2"/>
+      <c r="D90" s="4"/>
+      <c r="E90" s="4"/>
+      <c r="F90" s="4"/>
+      <c r="G90" s="2"/>
+      <c r="H90" s="2"/>
+      <c r="I90" s="4"/>
+    </row>
+    <row r="91" spans="1:9">
+      <c r="A91" s="2"/>
+      <c r="B91" s="6"/>
+      <c r="D91" s="4"/>
+      <c r="E91" s="4"/>
+      <c r="F91" s="4"/>
+      <c r="G91" s="2"/>
+      <c r="H91" s="2"/>
+      <c r="I91" s="4"/>
+    </row>
+    <row r="92" spans="1:9">
+      <c r="A92" s="2"/>
+      <c r="D92" s="4"/>
+      <c r="G92" s="2"/>
+      <c r="H92" s="2"/>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" s="2"/>
+      <c r="D93" s="4"/>
+      <c r="G93" s="2"/>
+      <c r="H93" s="2"/>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" s="2"/>
+      <c r="B94" s="6"/>
+      <c r="D94" s="4"/>
+      <c r="G94" s="2"/>
+      <c r="H94" s="2"/>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" s="2"/>
+      <c r="D95" s="4"/>
+      <c r="G95" s="2"/>
+      <c r="H95" s="2"/>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" s="2"/>
+      <c r="D96" s="4"/>
+      <c r="G96" s="2"/>
+      <c r="H96" s="2"/>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="2"/>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="2"/>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="2"/>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -2837,19 +3411,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="3" width="30.5" customWidth="1"/>
     <col min="7" max="8" width="37.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="121.5">
+    <row r="1" spans="1:9" s="1" customFormat="1" ht="135">
       <c r="A1" s="2" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>153</v>
+        <v>203</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>26</v>
@@ -2858,16 +3432,16 @@
       <c r="E1" s="4"/>
       <c r="F1" s="4"/>
       <c r="G1" s="2" t="s">
-        <v>154</v>
+        <v>192</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>121</v>
+        <v>162</v>
       </c>
       <c r="I1" s="4"/>
     </row>
     <row r="2" spans="1:9" s="1" customFormat="1" ht="54">
       <c r="A2" s="2" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" s="1" t="s">
@@ -2877,16 +3451,16 @@
       <c r="E2" s="4"/>
       <c r="F2" s="4"/>
       <c r="G2" s="2" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>122</v>
+        <v>164</v>
       </c>
       <c r="I2" s="4"/>
     </row>
-    <row r="3" spans="1:9" s="1" customFormat="1" ht="54">
+    <row r="3" spans="1:9" s="1" customFormat="1" ht="168" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" s="1" t="s">
@@ -2896,16 +3470,16 @@
       <c r="E3" s="4"/>
       <c r="F3" s="4"/>
       <c r="G3" s="2" t="s">
-        <v>158</v>
+        <v>196</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>123</v>
+        <v>165</v>
       </c>
       <c r="I3" s="4"/>
     </row>
     <row r="4" spans="1:9" s="1" customFormat="1" ht="168" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>159</v>
+        <v>197</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="1" t="s">
@@ -2915,16 +3489,16 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="2" t="s">
-        <v>160</v>
+        <v>198</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" s="1" customFormat="1" ht="168" customHeight="1">
+    <row r="5" spans="1:9" s="1" customFormat="1" ht="67.5">
       <c r="A5" s="2" t="s">
-        <v>161</v>
+        <v>199</v>
       </c>
       <c r="B5" s="5"/>
       <c r="C5" s="1" t="s">
@@ -2934,16 +3508,16 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>162</v>
+        <v>200</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>125</v>
+        <v>38</v>
       </c>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:9" s="1" customFormat="1" ht="67.5">
+    <row r="6" spans="1:9" s="1" customFormat="1" ht="81">
       <c r="A6" s="2" t="s">
-        <v>163</v>
+        <v>201</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="1" t="s">
@@ -2953,50 +3527,12 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
-        <v>164</v>
+        <v>202</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>38</v>
       </c>
       <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" s="1" customFormat="1" ht="67.5">
-      <c r="A7" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="5"/>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" s="1" customFormat="1" ht="81">
-      <c r="A8" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="B8" s="5"/>
-      <c r="C8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="216">
   <si>
     <t>name</t>
   </si>
@@ -926,11 +925,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、更新成功，字段名存在值不存在，则插入字段名和数值
-2、db.cs.cl.find查看字段更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新成功，指定的字段名和值被插入成功
 2、db.cs.cl.find查看字段更新正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1141,11 +1135,6 @@
   </si>
   <si>
     <t>update，$replace取值为空</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$replace更新符更新数据，数据为空，如：
-{$replace:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
-2、检查更新结果</t>
   </si>
   <si>
     <t>更新符：$replace， 操作是将文档全部替换成"{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}"。除了保留原始的 _id 之外，原始文档的内容会全部清空，并替换成"{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}"。
@@ -2471,7 +2460,7 @@
         <v>124</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>26</v>
@@ -2483,7 +2472,7 @@
         <v>109</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I37" s="4"/>
     </row>
@@ -2501,7 +2490,7 @@
         <v>111</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I38" s="4"/>
     </row>
@@ -2537,7 +2526,7 @@
         <v>115</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I40" s="4"/>
     </row>
@@ -2555,7 +2544,7 @@
         <v>117</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I41" s="4"/>
     </row>
@@ -2591,7 +2580,7 @@
         <v>144</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I43" s="4"/>
     </row>
@@ -2609,16 +2598,16 @@
         <v>129</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I44" s="4"/>
     </row>
     <row r="45" spans="1:9" ht="148.5">
       <c r="A45" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>26</v>
@@ -2627,16 +2616,16 @@
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I45" s="4"/>
     </row>
     <row r="46" spans="1:9" ht="67.5">
       <c r="A46" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>26</v>
@@ -2645,16 +2634,16 @@
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I46" s="4"/>
     </row>
     <row r="47" spans="1:9" ht="67.5">
       <c r="A47" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>26</v>
@@ -2663,7 +2652,7 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>87</v>
@@ -2672,7 +2661,7 @@
     </row>
     <row r="48" spans="1:9" ht="168" customHeight="1">
       <c r="A48" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>26</v>
@@ -2681,16 +2670,16 @@
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I48" s="4"/>
     </row>
     <row r="49" spans="1:9" ht="168" customHeight="1">
       <c r="A49" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>26</v>
@@ -2699,16 +2688,16 @@
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I49" s="4"/>
     </row>
     <row r="50" spans="1:9" ht="67.5">
       <c r="A50" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>26</v>
@@ -2717,7 +2706,7 @@
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>121</v>
@@ -2726,7 +2715,7 @@
     </row>
     <row r="51" spans="1:9" ht="67.5">
       <c r="A51" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>26</v>
@@ -2735,16 +2724,16 @@
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I51" s="4"/>
     </row>
     <row r="52" spans="1:9" ht="81">
       <c r="A52" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>26</v>
@@ -2753,10 +2742,10 @@
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="I52" s="4"/>
     </row>
@@ -2813,7 +2802,7 @@
         <v>150</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I55" s="4"/>
     </row>
@@ -2831,7 +2820,7 @@
         <v>152</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I56" s="4"/>
     </row>
@@ -2909,10 +2898,10 @@
     </row>
     <row r="61" spans="1:9" ht="148.5">
       <c r="A61" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>26</v>
@@ -2928,7 +2917,7 @@
       </c>
       <c r="I61" s="4"/>
     </row>
-    <row r="62" spans="1:9" ht="54">
+    <row r="62" spans="1:9" ht="67.5">
       <c r="A62" s="2" t="s">
         <v>131</v>
       </c>
@@ -2960,7 +2949,7 @@
         <v>134</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="I63" s="4"/>
     </row>
@@ -2978,7 +2967,7 @@
         <v>136</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I64" s="4"/>
     </row>
@@ -3029,7 +3018,7 @@
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>38</v>
@@ -3056,10 +3045,10 @@
     </row>
     <row r="69" spans="1:9" ht="148.5">
       <c r="A69" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>26</v>
@@ -3068,16 +3057,16 @@
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="2" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="67.5">
       <c r="A70" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>26</v>
@@ -3086,16 +3075,16 @@
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="I70" s="4"/>
     </row>
     <row r="71" spans="1:9" ht="168" customHeight="1">
       <c r="A71" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>26</v>
@@ -3104,16 +3093,16 @@
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I71" s="4"/>
     </row>
     <row r="72" spans="1:9" ht="168" customHeight="1">
       <c r="A72" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>26</v>
@@ -3122,7 +3111,7 @@
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="G72" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>121</v>
@@ -3131,7 +3120,7 @@
     </row>
     <row r="73" spans="1:9" ht="67.5">
       <c r="A73" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>26</v>
@@ -3140,7 +3129,7 @@
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
       <c r="G73" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>38</v>
@@ -3149,7 +3138,7 @@
     </row>
     <row r="74" spans="1:9" ht="67.5">
       <c r="A74" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>26</v>
@@ -3158,7 +3147,7 @@
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>38</v>
@@ -3167,10 +3156,10 @@
     </row>
     <row r="75" spans="1:9" ht="94.5">
       <c r="A75" s="8" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>26</v>
@@ -3185,7 +3174,7 @@
     <row r="76" spans="1:9" ht="25.5">
       <c r="A76" s="2"/>
       <c r="B76" s="7" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -3197,7 +3186,7 @@
     <row r="77" spans="1:9" ht="25.5">
       <c r="A77" s="2"/>
       <c r="B77" s="7" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -3208,10 +3197,10 @@
     </row>
     <row r="78" spans="1:9" ht="38.25">
       <c r="A78" s="8" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B78" s="7" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
@@ -3223,7 +3212,7 @@
     <row r="79" spans="1:9">
       <c r="A79" s="5"/>
       <c r="B79" s="7" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -3265,7 +3254,7 @@
     <row r="82" spans="1:9" ht="25.5">
       <c r="A82" s="2"/>
       <c r="C82" s="7" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -3407,135 +3396,4 @@
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="3" width="30.5" customWidth="1"/>
-    <col min="7" max="8" width="37.75" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" s="1" customFormat="1" ht="135">
-      <c r="A1" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="I1" s="4"/>
-    </row>
-    <row r="2" spans="1:9" s="1" customFormat="1" ht="54">
-      <c r="A2" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I2" s="4"/>
-    </row>
-    <row r="3" spans="1:9" s="1" customFormat="1" ht="168" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="I3" s="4"/>
-    </row>
-    <row r="4" spans="1:9" s="1" customFormat="1" ht="168" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I4" s="4"/>
-    </row>
-    <row r="5" spans="1:9" s="1" customFormat="1" ht="67.5">
-      <c r="A5" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" s="1" customFormat="1" ht="81">
-      <c r="A6" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="4"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="236">
   <si>
     <t>name</t>
   </si>
@@ -120,13 +120,6 @@
     <t>1、sdb运行正常
 2、sdb已存在domian、CS、CL
 3、sdb已插入待更新的数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>db.cs.cl.find查看不存在的字段更新失败，不存在字段之前的字段更新成功，之后的字段更新失败，如：
-"字段名1"更新成功；
-"字段名2"更新失败；
-"字段名3"更新失败；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -157,12 +150,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>更新符：$inc，给指定“&lt;字段名&gt;”增加指定的“&lt;值&gt;”
-如果字段名不存在则补充，如果存在则更新。
-语法：{$inc:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新成功，db.cs.cl.find查看指定更新的字段已更新
 2、指定更新的字段名对应的字段值已增加指定的值，数据更新正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -183,23 +170,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>更新符：$set，将指定的“&lt;字段名&gt;”更新为指定的“&lt;值&gt;”
-如果字段名不存在则补充，如果存在则更新。
-语法：{$set:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新成功，db.cs.cl.find查看指定更新的字段已更新
 2、指定更新的字段名对应的字段值已更新为指定的值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>更新符：$unset，删除集合中指定的字段名。
-如果记录中没有指定的字段名，跳过。
-语法：{$unset:{&lt;字段名1&gt;:"",&lt;字段名2&gt;:"",...}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update，覆盖$inc字段值有效取值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -236,10 +211,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，$set取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update，$unset指定的字段名存在</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -257,20 +228,6 @@
   </si>
   <si>
     <t>update，$unset取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$addtose取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新符：$addtose，向数组对象中添加元素和值，操作对象必须为数组类型的字段；
-如字段名存在值也存在，则跳过不添加；如果字段名存在值不存在，则只添加值；如果字段名不存在则添加字段名和值。
-语法：{$addtoset:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]，&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$addtose指定的字段名和字段值存在</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -418,11 +375,6 @@
 2、检查更新结果</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL指定数据，指定$set更新符更新数据，数据为空，如：
-{$set:{a:}}    或    {$set:}
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$unset更新符更新数据，对应的字段名存在，如：
 {$unset:{&lt;字段名1&gt;:"",&lt;字段名2&gt;:"",...}}
 2、检查更新结果</t>
@@ -444,11 +396,6 @@
 2、检查更新结果</t>
   </si>
   <si>
-    <t>1、更新成功，字段名存在值也存在，则跳过不添加，其他指定字段更新成功
-2、db.cs.cl.find查看字段更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新成功，字段名存在值不存在，则只添加值，其他指定字段更新成功
 2、db.cs.cl.find查看字段更新正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -474,60 +421,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，覆盖$addtose更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
-int：-2147483648、2147483647
-long：-9223372036854775808、9223372036854775807
-float：1.7E-308、1.7E+308
-string:16M
-oid：24位字节
-bool：true、false
-date:1902-01-18、2038-01-18
-timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
-binary(Base64)：
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，覆盖$addtose更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
-int：-2147483649、2147483648
-long：-9223372036854775809、9223372036854775808
-float：1.6E-308、1.8E+308
-string:16.5M
-oid：23、25位字节
-bool：test
-date:1902-01-17、2038-01-19
-timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$addtose更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$addtose更新符更新数据，数据为空，如：
-{$addtose:{a:}}    或    {$addtose:}
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>更新符：$pop，删除指定数组对象最后 N 个元素，操作对象必须为数组类型的字段。
-如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的 N 值大于数组对象的长度，数组对象的长度更新为0，即它的元素全部被删除；如果指定的 N 值 &lt; 0，即从数组起始删除第 -N 个元素。
-语法：{$pop:{&lt;字段名1&gt;:,&lt;字段名2&gt;:,...}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update，覆盖$addtose字段值有效取值</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -541,13 +434,6 @@
   </si>
   <si>
     <t>update，覆盖$pop字段值有效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pop更新符更新数据，字段值覆盖如下取值：
-   -1、0、1
-如：{$pop:{a:-1,b:0,c:-1}}
-2、检查更新结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -559,15 +445,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pop更新符更新数据，字段值覆盖如下取值：
-  取值等于数组字段值个数，如a:[1,1,1,1]，指定pop字段值为4|-4
-如：
-{$pop:{a:4}}
-{$pop:{a:-4}}
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新成功，数组对象中的所有值被全部删除，数组为空
 2、db.cs.cl.find查看指定字段数据已被更新，删除的数据正确；</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -581,40 +458,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pop更新符更新数据，字段值覆盖如下取值：
-  取值大于数组字段值个数，如a:[1,1,1,1]，指定pop字段值为5|-5
-如：
-{$pop:{a:5}}
-{$pop:{a:-5}}
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、空串，如：{$pop:{&lt;字段名1&gt;:}}   或  {$pop:{"":}}
 2、取值非整数，如{$pop:{age:test}}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，$pop取值为空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pop更新符更新数据，$pop取值为空串，如：
-  {$pop:{&lt;字段名1&gt;:}}   或  {$pop:{"":}}
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update，$pop取值非法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pop更新符更新数据，$pop取值非法，如：
-  {$pop:{age:test}}
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$pull更新数据，$pull指定的字段名和字段值存在
 2、检查更新结果</t>
   </si>
@@ -636,59 +488,10 @@
     <t>update，覆盖$pull字段值有效取值</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，覆盖$pull更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
-int：-2147483648、2147483647
-long：-9223372036854775808、9223372036854775807
-float：1.7E-308、1.7E+308
-string:16M
-oid：24位字节
-bool：true、false
-date:1902-01-18、2038-01-18
-timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
-binary(Base64)：
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，覆盖$pull字段值无效取值</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，覆盖$pull更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
-int：-2147483649、2147483648
-long：-9223372036854775809、9223372036854775808
-float：1.6E-308、1.8E+308
-string:16.5M
-oid：23、25位字节
-bool：test
-date:1902-01-17、2038-01-19
-timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，$pull指定的字段跟原字段数据类型不一致</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pull更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$addtose更新符更新数据，对应的字段名不存在，如：
-{$addtose:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]}}，其中&lt;字段名1&gt;不存在
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、更新失败，提示数值超出边界
@@ -700,12 +503,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$addtose更新符更新数据，$addtose指定的字段名非数组对象，如：
-{$addtose:{a:1}}，其中a为string类型的普通记录
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update，$pull指定的字段名和字段值存在</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -714,12 +511,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pop更新符更新数据，$pop指定的字段名非数组对象，如：
-{$pop:{a:}}，其中a为string类型的普通记录
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update，$pull取值为空</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -728,12 +519,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pull更新符更新数据，$pull指定的字段名非数组对象，如：
-{$pull:{a:1}}，其中a为string类型的普通记录
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$push_all更新数据，$push_all指定的字段名和字段值存在
 2、检查更新结果</t>
   </si>
@@ -755,72 +540,15 @@
     <t>update，覆盖$push_all字段值有效取值</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，覆盖$push_all更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
-int：-2147483648、2147483647
-long：-9223372036854775808、9223372036854775807
-float：1.7E-308、1.7E+308
-string:16M
-oid：24位字节
-bool：true、false
-date:1902-01-18、2038-01-18
-timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
-binary(Base64)：
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，覆盖$push_all字段值无效取值</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，覆盖$push_all更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
-int：-2147483649、2147483648
-long：-9223372036854775809、9223372036854775808
-float：1.6E-308、1.8E+308
-string:16.5M
-oid：23、25位字节
-bool：test
-date:1902-01-17、2038-01-19
-timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，$push_all指定的字段跟原字段数据类型不一致</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$push_all更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>update，$push_all取值为空</t>
-  </si>
-  <si>
     <t>update，$push_all指定的字段名非数组对象</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$push_all更新符更新数据，$push_all指定的字段名非数组对象，如：
-{$push_all:{a:1}}，其中a为string类型的普通记录
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pull更新符更新数据，数据为空，如：
-{$push:{&lt;字段名1&gt;:}}  或  {$push:{"":""}}
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update，$push指定的字段名和字段值存在</t>
   </si>
   <si>
@@ -845,74 +573,13 @@
     <t>update，覆盖$push字段值有效取值</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，覆盖$push更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
-int：-2147483648、2147483647
-long：-9223372036854775808、9223372036854775807
-float：1.7E-308、1.7E+308
-string:16M
-oid：24位字节
-bool：true、false
-date:1902-01-18、2038-01-18
-timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
-binary(Base64)：
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，覆盖$push字段值无效取值</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，覆盖$push更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
-int：-2147483649、2147483648
-long：-9223372036854775809、9223372036854775808
-float：1.6E-308、1.8E+308
-string:16.5M
-oid：23、25位字节
-bool：test
-date:1902-01-17、2038-01-19
-timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，$push指定的字段跟原字段数据类型不一致</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$push更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>update，$push取值为空</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$push更新符更新数据，数据为空，如：
-{$push:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，$push指定的字段名非数组对象</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$push更新符更新数据，$push指定的字段名非数组对象，如：
-{$push:{a:1}}，其中a为string类型的普通记录
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>更新符：$push，将给定数值插入到目标数组中，操作对象必须为数组类型的字段。如果记录中不存在指定的字段名，插入字段名和数值；如果记录中存在指定的字段名和数值，指定的数值也会插入。
-语法：{$push:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、更新成功，存在指定的字段名和数值，指定的数值也会插入
@@ -930,12 +597,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>更新符：$pull，清除指定数组对象的指定值。操作对象必须为数组类型的字段。
-如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的值不存在数组对象中，也不做任何操作。
-语法：{$pull:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新成功，字段名存在值也存在，则跳过不添加，其他指定字段更新成功
 2、db.cs.cl.find查看字段更新正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -988,89 +649,15 @@
     <t>update，覆盖$pull_all字段值有效取值</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，覆盖$pull_all更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
-int：-2147483648、2147483647
-long：-9223372036854775808、9223372036854775807
-float：1.7E-308、1.7E+308
-string:16M
-oid：24位字节
-bool：true、false
-date:1902-01-18、2038-01-18
-timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
-binary(Base64)：
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，覆盖$pull_all字段值无效取值</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，覆盖$pull_all更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
-int：-2147483649、2147483648
-long：-9223372036854775809、9223372036854775808
-float：1.6E-308、1.8E+308
-string:16.5M
-oid：23、25位字节
-bool：test
-date:1902-01-17、2038-01-19
-timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，$pull_all指定的字段跟原字段数据类型不一致</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pull_all更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>update，$pull_all取值为空</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pull_all更新符更新数据，数据为空，如：
-{$pull_all:{&lt;字段名1&gt;:[,,]  或  {$pull_all:{"":[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，$pull_all指定的字段名非数组对象</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$pull_all更新符更新数据，$pull_all指定的字段名非数组对象，如：
-{$pull_all:{a:1}}，其中a为string类型的普通记录
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>更新符：$pull_all，清除指定数组对象的指定值。操作对象必须为数组类型的字段。
-如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的值不存在数组对象中，也不做任何操作。
-语法：{$pull_all:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新符：$push_all，向指定数组对象推入每一个指定值。操作对象必须为数组类型的字段。
-如果记录中不存在指定的字段名，插入字段名和数值；如果记录中存在指定的字段名和数值，指定的数值也会插入。
-语法：{$push_all:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$push_all更新符更新数据，数据为空，如：
-{$push_all:{&lt;字段名1&gt;:[,,]  或  {$push_all:{"":[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$replace更新数据，$replace指定的字段名和字段值存在
 2、检查更新结果</t>
   </si>
@@ -1085,62 +672,10 @@
     <t>update，覆盖$replace字段值有效取值</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，覆盖$replace更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
-int：-2147483648、2147483647
-long：-9223372036854775808、9223372036854775807
-float：1.7E-308、1.7E+308
-string:16M
-oid：24位字节
-bool：true、false
-date:1902-01-18、2038-01-18
-timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
-binary(Base64)：
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，覆盖$replace字段值无效取值</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，覆盖$replace更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
-int：-2147483649、2147483648
-long：-9223372036854775809、9223372036854775808
-float：1.6E-308、1.8E+308
-string:16.5M
-oid：23、25位字节
-bool：test
-date:1902-01-17、2038-01-19
-timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>update，$replace指定的字段跟原字段数据类型不一致</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$replace更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>update，$replace取值为空</t>
-  </si>
-  <si>
-    <t>更新符：$replace， 操作是将文档全部替换成"{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}"。除了保留原始的 _id 之外，原始文档的内容会全部清空，并替换成"{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}"。
-语法：{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
-语法：{$replace:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>update，$replace指定的字段名存在</t>
@@ -1190,47 +725,613 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中已存在数据，指定$replace更新符更新数据，数据为空，如：
-{$replace:{&lt;字段名1&gt;:}}  或  {$replace:{"":&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、为空时，更新所有记录，不为空时，更新符合条件的记录。
-2、格式：[{"字段名1":{"匹配符1":"值1"},"字段名2":{"匹配符2":"值2"},...}]  
-匹配符：$gt、$gte、$lt、$lte……</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、字段名存在，为空
-2、按匹配符匹配记录更新</t>
+    <t>update，$pop取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
+语法：{$replace:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
+更新符：$replace， 操作是将文档全部替换成"{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}"。除了保留原始的 _id 之外，原始文档的内容会全部清空，并替换成"{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}"</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、字段名为空串
-2、格式错误</t>
+    <t>语法：
+{$push_all:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}
+更新符：$push_all，向指定数组对象推入每一个指定值。操作对象必须为数组类型的字段。
+如果记录中不存在指定的字段名，插入字段名和数值；如果记录中存在指定的字段名和数值，指定的数值也会插入。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+{$push:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
+更新符：$push，将给定数值插入到目标数组中，操作对象必须为数组类型的字段。如果记录中不存在指定的字段名，插入字段名和数值；如果记录中存在指定的字段名和数值，指定的数值也会插入。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+{$pull_all:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}
+更新符：$pull_all，清除指定数组对象的指定值。操作对象必须为数组类型的字段。
+如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的值不存在数组对象中，也不做任何操作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+{$pull:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
+更新符：$pull，清除指定数组对象的指定值。操作对象必须为数组类型的字段。
+如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的值不存在数组对象中，也不做任何操作。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>1、字段名为空串
-2、格式错误</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、字段值为null，如：{"":null}
-2、字段值不为空，如：{"":"&lt; indexname &gt;"}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>格式错误</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，cond</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，hint</t>
+    <t>update，$addtose指定的字段名和字段值存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+3、sdb已插入待更新的数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新成功，字段名存在值也存在，则跳过不添加，其他指定字段更新成功
+2、db.cs.cl.find查看字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+{$set:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
+更新符：$set，将指定的“&lt;字段名&gt;”更新为指定的“&lt;值&gt;”
+如果字段名不存在则补充，如果存在则更新。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+{$unset:{&lt;字段名1&gt;:"",&lt;字段名2&gt;:"",...}}
+更新符：$unset，删除集合中指定的字段名。
+如果记录中没有指定的字段名，跳过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+{$addtoset:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]，&lt;字段名2&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;],...}}
+更新符：$addtose，向数组对象中添加元素和值，操作对象必须为数组类型的字段；
+如字段名存在值也存在，则跳过不添加；如果字段名存在值不存在，则只添加值；如果字段名不存在则添加字段名和值。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+{$pop:{&lt;字段名1&gt;:,&lt;字段名2&gt;:,...}}
+更新符：$pop，删除指定数组对象最后 N 个元素，操作对象必须为数组类型的字段。
+如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的 N 值大于数组对象的长度，数组对象的长度更新为0，即它的元素全部被删除；如果指定的 N 值 &lt; 0，即从数组起始删除第 -N 个元素。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+{$inc:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
+更新符：$inc，给指定“&lt;字段名&gt;”增加指定的“&lt;值&gt;”
+如果字段名不存在则补充，如果存在则更新。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格式：
+[{"字段名1":{"匹配符1":"值1"},"字段名2":{"匹配符2":"值2"},...}]  
+匹配符：$gt、$gte、$lt、$lte……
+非必填，为空时，更新所有记录，不为空时，更新符合条件的记录。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，覆盖$addtose更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
+int：-2147483648、2147483647
+long：-9223372036854775808、9223372036854775807
+float：1.7E-308、1.7E+308
+string:16M
+oid：24位字节
+bool：true、false
+date:1902-01-18、2038-01-18
+timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
+binary(Base64)：
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$addtose更新符更新数据，对应的字段名不存在，如：
+{$addtose:{&lt;字段名1&gt;:[&lt;值1&gt;,&lt;值2&gt;,...,&lt;值N&gt;]}}，其中&lt;字段名1&gt;不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，覆盖$addtose更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
+int：-2147483649、2147483648
+long：-9223372036854775809、9223372036854775808
+float：1.6E-308、1.8E+308
+string:16.5M
+oid：23、25位字节
+bool：test
+date:1902-01-17、2038-01-19
+timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$addtose更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$addtose更新符更新数据，$addtose指定的字段名非数组对象，如：
+{$addtose:{a:1}}，其中a为string类型的普通记录
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$pop更新符更新数据，字段值覆盖如下取值：
+   -1、0、1
+如：{$pop:{a:-1,b:0,c:-1}}
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$pop更新符更新数据，字段值覆盖如下取值：
+  取值等于数组字段值个数，如a:[1,1,1,1]，指定pop字段值为4|-4
+如：
+{$pop:{a:4}}
+{$pop:{a:-4}}
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$pop更新符更新数据，字段值覆盖如下取值：
+  取值大于数组字段值个数，如a:[1,1,1,1]，指定pop字段值为5|-5
+如：
+{$pop:{a:5}}
+{$pop:{a:-5}}
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$pop更新符更新数据，$pop取值为空串，如：
+  {$pop:{&lt;字段名1&gt;:}}   或  {$pop:{"":}}
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$pop更新符更新数据，$pop取值非法，如：
+  {$pop:{age:test}}
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$pop更新符更新数据，$pop指定的字段名非数组对象，如：
+{$pop:{a:}}，其中a为string类型的普通记录
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，覆盖$pull更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
+int：-2147483648、2147483647
+long：-9223372036854775808、9223372036854775807
+float：1.7E-308、1.7E+308
+string:16M
+oid：24位字节
+bool：true、false
+date:1902-01-18、2038-01-18
+timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
+binary(Base64)：
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，覆盖$pull更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
+int：-2147483649、2147483648
+long：-9223372036854775809、9223372036854775808
+float：1.6E-308、1.8E+308
+string:16.5M
+oid：23、25位字节
+bool：test
+date:1902-01-17、2038-01-19
+timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$pull更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$pull更新符更新数据，数据为空，如：
+{$push:{&lt;字段名1&gt;:}}  或  {$push:{"":""}}
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$pull更新符更新数据，$pull指定的字段名非数组对象，如：
+{$pull:{a:1}}，其中a为string类型的普通记录
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，覆盖$pull_all更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
+int：-2147483648、2147483647
+long：-9223372036854775808、9223372036854775807
+float：1.7E-308、1.7E+308
+string:16M
+oid：24位字节
+bool：true、false
+date:1902-01-18、2038-01-18
+timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
+binary(Base64)：
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，覆盖$pull_all更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
+int：-2147483649、2147483648
+long：-9223372036854775809、9223372036854775808
+float：1.6E-308、1.8E+308
+string:16.5M
+oid：23、25位字节
+bool：test
+date:1902-01-17、2038-01-19
+timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$pull_all更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$pull_all更新符更新数据，$pull_all指定的字段名非数组对象，如：
+{$pull_all:{a:1}}，其中a为string类型的普通记录
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，覆盖$push更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
+int：-2147483648、2147483647
+long：-9223372036854775808、9223372036854775807
+float：1.7E-308、1.7E+308
+string:16M
+oid：24位字节
+bool：true、false
+date:1902-01-18、2038-01-18
+timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
+binary(Base64)：
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，覆盖$push更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
+int：-2147483649、2147483648
+long：-9223372036854775809、9223372036854775808
+float：1.6E-308、1.8E+308
+string:16.5M
+oid：23、25位字节
+bool：test
+date:1902-01-17、2038-01-19
+timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$push更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$push更新符更新数据，$push指定的字段名非数组对象，如：
+{$push:{a:1}}，其中a为string类型的普通记录
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，覆盖$push_all更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
+int：-2147483648、2147483647
+long：-9223372036854775808、9223372036854775807
+float：1.7E-308、1.7E+308
+string:16M
+oid：24位字节
+bool：true、false
+date:1902-01-18、2038-01-18
+timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
+binary(Base64)：
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，覆盖$push_all更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
+int：-2147483649、2147483648
+long：-9223372036854775809、9223372036854775808
+float：1.6E-308、1.8E+308
+string:16.5M
+oid：23、25位字节
+bool：test
+date:1902-01-17、2038-01-19
+timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$push_all更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$push_all更新符更新数据，$push_all指定的字段名非数组对象，如：
+{$push_all:{a:1}}，其中a为string类型的普通记录
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，覆盖$replace更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
+int：-2147483648、2147483647
+long：-9223372036854775808、9223372036854775807
+float：1.7E-308、1.7E+308
+string:16M
+oid：24位字节
+bool：true、false
+date:1902-01-18、2038-01-18
+timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
+binary(Base64)：
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，覆盖$replace更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
+int：-2147483649、2147483648
+long：-9223372036854775809、9223372036854775808
+float：1.6E-308、1.8E+308
+string:16.5M
+oid：23、25位字节
+bool：test
+date:1902-01-17、2038-01-19
+timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$replace更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，cond指定的字段名存在且值为空，如：
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>db.cs.cl.find查看不存在的字段更新失败，不存在字段之前的字段更新成功，之后的字段更新失败，如：
+"字段名1"更新成功；
+"字段名2"更新失败；
+"字段名3"更新失败；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，cond指定匹配符更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，cond指定的字段名不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新失败，提示字段不存在，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格式：
+[{"":"索引名"|null}]
+hint 参数是一个包含一个单一字段的 Json 对象，字段名会被忽略，而其字段值则指定为需要访问索引的名称，当字段值为 null 时，则遍历集合中所有的记录，它的格式为{"":null}或者{"":"&lt; indexname &gt;"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，hint指定的字段值为null</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，hint指定的字段值为需要访问索引的名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新成功，遍历所有的记录更新，记录更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新失败，提示索引字段值不能重复，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新成功，字段名不存在upsert直接做插入操作，更新成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同update，upsert更新调用的是update的接口，跟update交叉测试即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upsert，指定无效的字段名和字段值更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upsert，指定有效的字段名和字段值更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update，returnNew指定为true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.collectionspace.collection.upsert(&lt;rule&gt;,[cond],[hint],[setOnInsert])
+upsert
+当使用cond参数在集合中匹配不到记录时，update 不做任何操作，而 upsert 方法会做一次插入操作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upsert，cond指定的字段名不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格式：query.update(&lt;update&gt;,[returnNew])
+update：Json对象，更新规则。记录按update的内容更新。必填
+returnNew： bool，是否返回更新后的记录。非必填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，cond指定的字段名不存在，如：
+db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":"testIndex"})，其中age字段不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，hint指定的字段值为需要访问索引的名称，如：
+db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":"testIndex"})，其中"testIndex"为需要访问索引的名称
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>更新成功，使用索引名为 testIndex 的索引访问集合中匹配条件的记录，记录更新正确，如：
+db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":"testIndex"})&gt;
+此操作使用索引名为 testIndex 的索引访问集合 bar 中 age 字段值大于20的记录，将这些记录的 age 字段名加1。</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，hint指定的字段值为null，如：
+db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":""})
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建索引testIndex，update更新CL中数据，指定的字段为所有字段，指定的值为索引字段的值，且修改索引字段值重复，如：testCL表中存在记录{age:1,age:2}
+创建索引：db.CS.CL.createIndex("ageIndex",{age:1},true)
+update更新age的值为1
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，upsert更新CL指定数据，cond指定的字段名不存在，如：
+db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":"testIndex"})，其中age字段不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update更新CL指定数据，returnNew指定为true，其他参数正确，如：
+db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:true)
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新成功，结果返回修改后的所有记录值，返回的记录跟实际更新的记录数以及内容一致，修改正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update，指定有效的字段名和字段值更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update，指定无效的字段名和字段值更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同update，跟update交叉测试即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update，returnNew指定为false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update更新CL指定数据，returnNew指定为false，其他参数正确，如：
+db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:false)
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update，returnNew取值非法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update更新CL指定数据，returnNew取值非法，如：
+db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:test)
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update，returnNew取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update更新CL指定数据，returnNew取值为空，如：
+db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:)
+db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},)
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新失败，结果不打印修改后的所有记录值
+2、db.cs.cl.find查看指定更新的字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新失败，提示参数错误，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+3、sdb已插入待更新的数据</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1238,7 +1339,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1268,13 +1369,6 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1284,7 +1378,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -1292,26 +1386,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1328,14 +1407,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1426,8 +1502,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I96" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I96"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I83" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I83"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1746,12 +1822,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30" style="5" customWidth="1"/>
-    <col min="3" max="3" width="22.25" style="1" customWidth="1"/>
+    <col min="1" max="1" width="33.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.875" style="5" customWidth="1"/>
+    <col min="3" max="3" width="25.75" style="1" customWidth="1"/>
     <col min="4" max="6" width="5" style="1" customWidth="1"/>
     <col min="7" max="7" width="44.375" style="1" customWidth="1"/>
     <col min="8" max="8" width="34" style="1" customWidth="1"/>
@@ -1822,7 +1898,7 @@
         <v>19</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
@@ -1837,7 +1913,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>20</v>
@@ -1857,7 +1933,7 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>23</v>
@@ -1875,7 +1951,7 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>24</v>
@@ -1893,16 +1969,16 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>27</v>
+        <v>198</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="67.5">
       <c r="A7" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>26</v>
@@ -1911,16 +1987,16 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I7" s="4"/>
     </row>
     <row r="8" spans="1:9" ht="67.5">
       <c r="A8" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>26</v>
@@ -1929,19 +2005,19 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="2" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="I8" s="4"/>
     </row>
     <row r="9" spans="1:9" ht="168" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>34</v>
+        <v>164</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>26</v>
@@ -1950,16 +2026,16 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="67.5">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>26</v>
@@ -1968,16 +2044,16 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="168" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>26</v>
@@ -1986,16 +2062,16 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I11" s="4"/>
     </row>
     <row r="12" spans="1:9" ht="67.5">
       <c r="A12" s="2" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>26</v>
@@ -2004,16 +2080,16 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" ht="67.5">
       <c r="A13" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>26</v>
@@ -2022,19 +2098,19 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I13" s="4"/>
     </row>
     <row r="14" spans="1:9" ht="168" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>39</v>
+        <v>160</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>26</v>
@@ -2042,17 +2118,17 @@
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
-      <c r="G14" s="2" t="s">
-        <v>73</v>
+      <c r="G14" s="7" t="s">
+        <v>65</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="67.5">
       <c r="A15" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>26</v>
@@ -2061,16 +2137,16 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="168" customHeight="1">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>26</v>
@@ -2079,16 +2155,16 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="67.5">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>26</v>
@@ -2097,16 +2173,19 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="67.5">
+    <row r="18" spans="1:9" ht="94.5">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>26</v>
@@ -2115,19 +2194,16 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="81">
+    <row r="19" spans="1:9" ht="67.5">
       <c r="A19" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>26</v>
@@ -2136,16 +2212,16 @@
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="67.5">
       <c r="A20" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>26</v>
@@ -2154,37 +2230,37 @@
       <c r="E20" s="4"/>
       <c r="F20" s="4"/>
       <c r="G20" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="67.5">
+    <row r="21" spans="1:9" ht="162">
       <c r="A21" s="2" t="s">
-        <v>56</v>
+        <v>157</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>26</v>
+        <v>158</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="4"/>
       <c r="G21" s="2" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>38</v>
+        <v>159</v>
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="86.25" customHeight="1">
+    <row r="22" spans="1:9" ht="67.5">
       <c r="A22" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>26</v>
@@ -2193,16 +2269,16 @@
       <c r="E22" s="4"/>
       <c r="F22" s="4"/>
       <c r="G22" s="2" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="I22" s="4"/>
     </row>
     <row r="23" spans="1:9" ht="67.5">
       <c r="A23" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>26</v>
@@ -2211,16 +2287,16 @@
       <c r="E23" s="4"/>
       <c r="F23" s="4"/>
       <c r="G23" s="2" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="67.5">
+    <row r="24" spans="1:9" ht="168" customHeight="1">
       <c r="A24" s="2" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>26</v>
@@ -2229,16 +2305,16 @@
       <c r="E24" s="4"/>
       <c r="F24" s="4"/>
       <c r="G24" s="2" t="s">
-        <v>86</v>
+        <v>166</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="168" customHeight="1">
+    <row r="25" spans="1:9" ht="67.5">
       <c r="A25" s="2" t="s">
-        <v>93</v>
+        <v>53</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>26</v>
@@ -2247,16 +2323,16 @@
       <c r="E25" s="4"/>
       <c r="F25" s="4"/>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>167</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="81">
+    <row r="26" spans="1:9" ht="168" customHeight="1">
       <c r="A26" s="2" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>26</v>
@@ -2265,16 +2341,16 @@
       <c r="E26" s="4"/>
       <c r="F26" s="4"/>
       <c r="G26" s="2" t="s">
-        <v>120</v>
+        <v>168</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="I26" s="4"/>
     </row>
-    <row r="27" spans="1:9" ht="168" customHeight="1">
+    <row r="27" spans="1:9" ht="67.5">
       <c r="A27" s="2" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>26</v>
@@ -2283,16 +2359,16 @@
       <c r="E27" s="4"/>
       <c r="F27" s="4"/>
       <c r="G27" s="2" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I27" s="4"/>
     </row>
     <row r="28" spans="1:9" ht="67.5">
       <c r="A28" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>26</v>
@@ -2301,16 +2377,19 @@
       <c r="E28" s="4"/>
       <c r="F28" s="4"/>
       <c r="G28" s="2" t="s">
-        <v>90</v>
+        <v>170</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I28" s="4"/>
     </row>
-    <row r="29" spans="1:9" ht="67.5">
+    <row r="29" spans="1:9" ht="175.5">
       <c r="A29" s="2" t="s">
-        <v>57</v>
+        <v>81</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>163</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>26</v>
@@ -2319,16 +2398,16 @@
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>171</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>38</v>
+        <v>82</v>
       </c>
       <c r="I29" s="4"/>
     </row>
-    <row r="30" spans="1:9" ht="67.5">
+    <row r="30" spans="1:9" ht="108">
       <c r="A30" s="2" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>26</v>
@@ -2337,19 +2416,16 @@
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
       <c r="G30" s="2" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>38</v>
+        <v>83</v>
       </c>
       <c r="I30" s="4"/>
     </row>
-    <row r="31" spans="1:9" ht="162">
+    <row r="31" spans="1:9" ht="108">
       <c r="A31" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>26</v>
@@ -2358,88 +2434,91 @@
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
       <c r="G31" s="2" t="s">
-        <v>97</v>
+        <v>173</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="I31" s="4"/>
     </row>
-    <row r="32" spans="1:9" ht="108">
+    <row r="32" spans="1:9" ht="67.5">
       <c r="A32" s="2" t="s">
-        <v>101</v>
+        <v>151</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
       <c r="G32" s="2" t="s">
-        <v>99</v>
+        <v>174</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="I32" s="4"/>
     </row>
-    <row r="33" spans="1:9" ht="108">
+    <row r="33" spans="1:9" ht="67.5">
       <c r="A33" s="2" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>26</v>
+        <v>86</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
       <c r="G33" s="2" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>100</v>
+        <v>36</v>
       </c>
       <c r="I33" s="4"/>
     </row>
-    <row r="34" spans="1:9" ht="67.5">
+    <row r="34" spans="1:9" ht="54">
       <c r="A34" s="2" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
       <c r="G34" s="2" t="s">
-        <v>106</v>
+        <v>176</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I34" s="4"/>
     </row>
-    <row r="35" spans="1:9" ht="67.5">
+    <row r="35" spans="1:9" ht="148.5">
       <c r="A35" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>156</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
       <c r="G35" s="2" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>38</v>
+        <v>124</v>
       </c>
       <c r="I35" s="4"/>
     </row>
     <row r="36" spans="1:9" ht="67.5">
       <c r="A36" s="2" t="s">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>26</v>
@@ -2448,19 +2527,16 @@
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
       <c r="G36" s="2" t="s">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>38</v>
+        <v>125</v>
       </c>
       <c r="I36" s="4"/>
     </row>
-    <row r="37" spans="1:9" ht="121.5">
+    <row r="37" spans="1:9" ht="67.5">
       <c r="A37" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>165</v>
+        <v>91</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>26</v>
@@ -2469,16 +2545,16 @@
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
       <c r="G37" s="2" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="I37" s="4"/>
     </row>
-    <row r="38" spans="1:9" ht="67.5">
+    <row r="38" spans="1:9" ht="168" customHeight="1">
       <c r="A38" s="2" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>26</v>
@@ -2487,16 +2563,16 @@
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
       <c r="G38" s="2" t="s">
-        <v>111</v>
+        <v>177</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="I38" s="4"/>
     </row>
-    <row r="39" spans="1:9" ht="67.5">
+    <row r="39" spans="1:9" ht="168" customHeight="1">
       <c r="A39" s="2" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>26</v>
@@ -2505,16 +2581,16 @@
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
       <c r="G39" s="2" t="s">
-        <v>113</v>
+        <v>178</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="I39" s="4"/>
     </row>
-    <row r="40" spans="1:9" ht="168" customHeight="1">
+    <row r="40" spans="1:9" ht="54">
       <c r="A40" s="2" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>26</v>
@@ -2523,16 +2599,16 @@
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
       <c r="G40" s="2" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="I40" s="4"/>
     </row>
-    <row r="41" spans="1:9" ht="168" customHeight="1">
+    <row r="41" spans="1:9" ht="54">
       <c r="A41" s="2" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>26</v>
@@ -2541,16 +2617,16 @@
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
       <c r="G41" s="2" t="s">
-        <v>117</v>
+        <v>180</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="I41" s="4"/>
     </row>
-    <row r="42" spans="1:9" ht="67.5">
+    <row r="42" spans="1:9" ht="54">
       <c r="A42" s="2" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>26</v>
@@ -2559,16 +2635,19 @@
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
       <c r="G42" s="2" t="s">
-        <v>119</v>
+        <v>181</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="I42" s="4"/>
     </row>
-    <row r="43" spans="1:9" ht="67.5">
+    <row r="43" spans="1:9" ht="175.5">
       <c r="A43" s="2" t="s">
-        <v>127</v>
+        <v>130</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>26</v>
@@ -2577,16 +2656,16 @@
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
       <c r="G43" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>170</v>
+        <v>124</v>
       </c>
       <c r="I43" s="4"/>
     </row>
     <row r="44" spans="1:9" ht="67.5">
       <c r="A44" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>26</v>
@@ -2595,19 +2674,16 @@
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
       <c r="G44" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>170</v>
+        <v>125</v>
       </c>
       <c r="I44" s="4"/>
     </row>
-    <row r="45" spans="1:9" ht="148.5">
+    <row r="45" spans="1:9" ht="67.5">
       <c r="A45" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>188</v>
+        <v>134</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>26</v>
@@ -2616,16 +2692,16 @@
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
       <c r="G45" s="2" t="s">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="I45" s="4"/>
     </row>
-    <row r="46" spans="1:9" ht="67.5">
+    <row r="46" spans="1:9" ht="168" customHeight="1">
       <c r="A46" s="2" t="s">
-        <v>174</v>
+        <v>136</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>26</v>
@@ -2634,16 +2710,16 @@
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
       <c r="G46" s="2" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>167</v>
+        <v>126</v>
       </c>
       <c r="I46" s="4"/>
     </row>
-    <row r="47" spans="1:9" ht="67.5">
+    <row r="47" spans="1:9" ht="168" customHeight="1">
       <c r="A47" s="2" t="s">
-        <v>176</v>
+        <v>137</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>26</v>
@@ -2652,16 +2728,16 @@
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="I47" s="4"/>
     </row>
-    <row r="48" spans="1:9" ht="168" customHeight="1">
+    <row r="48" spans="1:9" ht="67.5">
       <c r="A48" s="2" t="s">
-        <v>178</v>
+        <v>138</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>26</v>
@@ -2670,16 +2746,16 @@
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>168</v>
+        <v>96</v>
       </c>
       <c r="I48" s="4"/>
     </row>
-    <row r="49" spans="1:9" ht="168" customHeight="1">
+    <row r="49" spans="1:9" ht="81">
       <c r="A49" s="2" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>26</v>
@@ -2688,16 +2764,19 @@
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="2" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="I49" s="4"/>
     </row>
-    <row r="50" spans="1:9" ht="67.5">
+    <row r="50" spans="1:9" ht="135">
       <c r="A50" s="2" t="s">
-        <v>182</v>
+        <v>111</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>154</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>26</v>
@@ -2706,7 +2785,7 @@
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="2" t="s">
-        <v>183</v>
+        <v>112</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>121</v>
@@ -2715,7 +2794,7 @@
     </row>
     <row r="51" spans="1:9" ht="67.5">
       <c r="A51" s="2" t="s">
-        <v>184</v>
+        <v>113</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>26</v>
@@ -2724,16 +2803,16 @@
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="2" t="s">
-        <v>185</v>
+        <v>114</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>170</v>
+        <v>122</v>
       </c>
       <c r="I51" s="4"/>
     </row>
-    <row r="52" spans="1:9" ht="81">
+    <row r="52" spans="1:9" ht="67.5">
       <c r="A52" s="2" t="s">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>26</v>
@@ -2742,19 +2821,16 @@
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="2" t="s">
-        <v>187</v>
+        <v>116</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>170</v>
+        <v>149</v>
       </c>
       <c r="I52" s="4"/>
     </row>
-    <row r="53" spans="1:9" ht="108">
+    <row r="53" spans="1:9" ht="168" customHeight="1">
       <c r="A53" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>26</v>
@@ -2763,16 +2839,16 @@
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="2" t="s">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>162</v>
+        <v>123</v>
       </c>
       <c r="I53" s="4"/>
     </row>
-    <row r="54" spans="1:9" ht="67.5">
+    <row r="54" spans="1:9" ht="168" customHeight="1">
       <c r="A54" s="2" t="s">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>26</v>
@@ -2781,16 +2857,16 @@
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="2" t="s">
-        <v>148</v>
+        <v>187</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>163</v>
+        <v>96</v>
       </c>
       <c r="I54" s="4"/>
     </row>
-    <row r="55" spans="1:9" ht="67.5">
+    <row r="55" spans="1:9" ht="54">
       <c r="A55" s="2" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>26</v>
@@ -2799,16 +2875,16 @@
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="2" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>205</v>
+        <v>36</v>
       </c>
       <c r="I55" s="4"/>
     </row>
-    <row r="56" spans="1:9" ht="168" customHeight="1">
+    <row r="56" spans="1:9" ht="54">
       <c r="A56" s="2" t="s">
-        <v>151</v>
+        <v>120</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>26</v>
@@ -2817,15 +2893,18 @@
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="2" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>164</v>
+        <v>36</v>
       </c>
       <c r="I56" s="4"/>
     </row>
-    <row r="57" spans="1:9" ht="168" customHeight="1">
+    <row r="57" spans="1:9" ht="175.5">
       <c r="A57" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B57" s="5" t="s">
         <v>153</v>
       </c>
       <c r="C57" s="1" t="s">
@@ -2835,7 +2914,7 @@
       <c r="E57" s="4"/>
       <c r="F57" s="4"/>
       <c r="G57" s="2" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>121</v>
@@ -2844,7 +2923,7 @@
     </row>
     <row r="58" spans="1:9" ht="67.5">
       <c r="A58" s="2" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>26</v>
@@ -2853,16 +2932,16 @@
       <c r="E58" s="4"/>
       <c r="F58" s="4"/>
       <c r="G58" s="2" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>38</v>
+        <v>122</v>
       </c>
       <c r="I58" s="4"/>
     </row>
     <row r="59" spans="1:9" ht="67.5">
       <c r="A59" s="2" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>26</v>
@@ -2871,16 +2950,16 @@
       <c r="E59" s="4"/>
       <c r="F59" s="4"/>
       <c r="G59" s="2" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="I59" s="4"/>
     </row>
-    <row r="60" spans="1:9" ht="67.5">
+    <row r="60" spans="1:9" ht="168" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>26</v>
@@ -2889,19 +2968,16 @@
       <c r="E60" s="4"/>
       <c r="F60" s="4"/>
       <c r="G60" s="2" t="s">
-        <v>160</v>
+        <v>190</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="I60" s="4"/>
     </row>
-    <row r="61" spans="1:9" ht="148.5">
+    <row r="61" spans="1:9" ht="168" customHeight="1">
       <c r="A61" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B61" s="5" t="s">
-        <v>189</v>
+        <v>108</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>26</v>
@@ -2910,16 +2986,16 @@
       <c r="E61" s="4"/>
       <c r="F61" s="4"/>
       <c r="G61" s="2" t="s">
-        <v>130</v>
+        <v>191</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="I61" s="4"/>
     </row>
     <row r="62" spans="1:9" ht="67.5">
       <c r="A62" s="2" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>26</v>
@@ -2928,16 +3004,16 @@
       <c r="E62" s="4"/>
       <c r="F62" s="4"/>
       <c r="G62" s="2" t="s">
-        <v>132</v>
+        <v>192</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>163</v>
+        <v>36</v>
       </c>
       <c r="I62" s="4"/>
     </row>
-    <row r="63" spans="1:9" ht="67.5">
+    <row r="63" spans="1:9" ht="81">
       <c r="A63" s="2" t="s">
-        <v>133</v>
+        <v>110</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>26</v>
@@ -2946,16 +3022,19 @@
       <c r="E63" s="4"/>
       <c r="F63" s="4"/>
       <c r="G63" s="2" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>205</v>
+        <v>36</v>
       </c>
       <c r="I63" s="4"/>
     </row>
-    <row r="64" spans="1:9" ht="168" customHeight="1">
+    <row r="64" spans="1:9" ht="175.5">
       <c r="A64" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>26</v>
@@ -2964,16 +3043,16 @@
       <c r="E64" s="4"/>
       <c r="F64" s="4"/>
       <c r="G64" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="I64" s="4"/>
     </row>
-    <row r="65" spans="1:9" ht="168" customHeight="1">
+    <row r="65" spans="1:9" ht="67.5">
       <c r="A65" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>26</v>
@@ -2982,16 +3061,16 @@
       <c r="E65" s="4"/>
       <c r="F65" s="4"/>
       <c r="G65" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="I65" s="4"/>
     </row>
-    <row r="66" spans="1:9" ht="67.5">
+    <row r="66" spans="1:9" ht="168" customHeight="1">
       <c r="A66" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>26</v>
@@ -3000,16 +3079,16 @@
       <c r="E66" s="4"/>
       <c r="F66" s="4"/>
       <c r="G66" s="2" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>38</v>
+        <v>150</v>
       </c>
       <c r="I66" s="4"/>
     </row>
-    <row r="67" spans="1:9" ht="67.5">
+    <row r="67" spans="1:9" ht="168" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>26</v>
@@ -3018,16 +3097,16 @@
       <c r="E67" s="4"/>
       <c r="F67" s="4"/>
       <c r="G67" s="2" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="I67" s="4"/>
     </row>
-    <row r="68" spans="1:9" ht="81">
+    <row r="68" spans="1:9" ht="67.5">
       <c r="A68" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>26</v>
@@ -3036,19 +3115,19 @@
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="2" t="s">
-        <v>143</v>
+        <v>196</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="I68" s="4"/>
     </row>
-    <row r="69" spans="1:9" ht="148.5">
-      <c r="A69" s="2" t="s">
-        <v>202</v>
+    <row r="69" spans="1:9" ht="121.5">
+      <c r="A69" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>26</v>
@@ -3057,17 +3136,16 @@
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H69" s="2" t="s">
-        <v>203</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="H69" s="2"/>
       <c r="I69" s="4"/>
     </row>
     <row r="70" spans="1:9" ht="67.5">
       <c r="A70" s="2" t="s">
-        <v>192</v>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="B70" s="2"/>
       <c r="C70" s="1" t="s">
         <v>26</v>
       </c>
@@ -3075,16 +3153,19 @@
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="2" t="s">
-        <v>193</v>
+        <v>216</v>
       </c>
       <c r="H70" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="I70" s="4"/>
+    </row>
+    <row r="71" spans="1:9" ht="135">
+      <c r="A71" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="I70" s="4"/>
-    </row>
-    <row r="71" spans="1:9" ht="168" customHeight="1">
-      <c r="A71" s="2" t="s">
-        <v>194</v>
+      <c r="B71" s="5" t="s">
+        <v>202</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>26</v>
@@ -3093,16 +3174,16 @@
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="2" t="s">
-        <v>195</v>
+        <v>217</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="I71" s="4"/>
     </row>
-    <row r="72" spans="1:9" ht="168" customHeight="1">
+    <row r="72" spans="1:9" ht="67.5">
       <c r="A72" s="2" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>26</v>
@@ -3111,16 +3192,16 @@
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="G72" s="2" t="s">
-        <v>197</v>
+        <v>219</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>121</v>
+        <v>205</v>
       </c>
       <c r="I72" s="4"/>
     </row>
-    <row r="73" spans="1:9" ht="67.5">
+    <row r="73" spans="1:9" ht="121.5">
       <c r="A73" s="2" t="s">
-        <v>198</v>
+        <v>32</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>26</v>
@@ -3129,37 +3210,37 @@
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
       <c r="G73" s="2" t="s">
-        <v>199</v>
+        <v>220</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>38</v>
+        <v>206</v>
       </c>
       <c r="I73" s="4"/>
     </row>
     <row r="74" spans="1:9" ht="67.5">
       <c r="A74" s="2" t="s">
-        <v>200</v>
+        <v>31</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D74" s="4"/>
+      <c r="D74" s="4">
+        <v>1</v>
+      </c>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="H74" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="H74" s="2"/>
       <c r="I74" s="4"/>
     </row>
-    <row r="75" spans="1:9" ht="94.5">
-      <c r="A75" s="8" t="s">
-        <v>214</v>
+    <row r="75" spans="1:9" ht="121.5">
+      <c r="A75" s="2" t="s">
+        <v>211</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>26</v>
@@ -3167,226 +3248,167 @@
       <c r="D75" s="4"/>
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
-      <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
+      <c r="G75" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="I75" s="4"/>
     </row>
-    <row r="76" spans="1:9" ht="25.5">
-      <c r="A76" s="2"/>
-      <c r="B76" s="7" t="s">
-        <v>209</v>
+    <row r="76" spans="1:9" ht="54">
+      <c r="A76" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
+      <c r="G76" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="I76" s="4"/>
     </row>
-    <row r="77" spans="1:9" ht="25.5">
-      <c r="A77" s="2"/>
-      <c r="B77" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="4"/>
-    </row>
-    <row r="78" spans="1:9" ht="38.25">
-      <c r="A78" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="B78" s="7" t="s">
-        <v>212</v>
+    <row r="77" spans="1:9" ht="67.5">
+      <c r="A77" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D77" s="4">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="121.5">
+      <c r="A78" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
-      <c r="G78" s="2"/>
-      <c r="H78" s="2"/>
+      <c r="G78" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="I78" s="4"/>
     </row>
-    <row r="79" spans="1:9">
-      <c r="A79" s="5"/>
-      <c r="B79" s="7" t="s">
-        <v>213</v>
+    <row r="79" spans="1:9" ht="54">
+      <c r="A79" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
       <c r="F79" s="4"/>
-      <c r="G79" s="2"/>
-      <c r="H79" s="2"/>
+      <c r="G79" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="H79" s="2" t="s">
+        <v>209</v>
+      </c>
       <c r="I79" s="4"/>
     </row>
-    <row r="80" spans="1:9" ht="67.5">
+    <row r="80" spans="1:9" ht="121.5">
       <c r="A80" s="2" t="s">
-        <v>33</v>
+        <v>212</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="2"/>
-      <c r="H80" s="2"/>
-      <c r="I80" s="4"/>
+      <c r="D80" s="4">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>223</v>
+      </c>
     </row>
     <row r="81" spans="1:9" ht="67.5">
       <c r="A81" s="2" t="s">
-        <v>32</v>
+        <v>227</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D81" s="4"/>
+        <v>235</v>
+      </c>
+      <c r="D81" s="4">
+        <v>1</v>
+      </c>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="G81" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H81" s="2"/>
+        <v>228</v>
+      </c>
+      <c r="H81" s="2" t="s">
+        <v>233</v>
+      </c>
       <c r="I81" s="4"/>
     </row>
-    <row r="82" spans="1:9" ht="25.5">
-      <c r="A82" s="2"/>
-      <c r="C82" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D82" s="4"/>
+    <row r="82" spans="1:9" ht="67.5">
+      <c r="A82" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D82" s="4">
+        <v>1</v>
+      </c>
       <c r="E82" s="4"/>
       <c r="F82" s="4"/>
-      <c r="G82" s="2"/>
-      <c r="H82" s="2"/>
+      <c r="G82" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="I82" s="4"/>
     </row>
-    <row r="83" spans="1:9">
-      <c r="A83" s="2"/>
-      <c r="D83" s="4"/>
+    <row r="83" spans="1:9" ht="94.5">
+      <c r="A83" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D83" s="4">
+        <v>1</v>
+      </c>
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
-      <c r="G83" s="2"/>
-      <c r="H83" s="2"/>
+      <c r="G83" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="I83" s="4"/>
-    </row>
-    <row r="84" spans="1:9">
-      <c r="A84" s="2"/>
-      <c r="D84" s="4"/>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
-      <c r="G84" s="2"/>
-      <c r="H84" s="2"/>
-      <c r="I84" s="4"/>
-    </row>
-    <row r="85" spans="1:9">
-      <c r="A85" s="2"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="2"/>
-      <c r="H85" s="2"/>
-      <c r="I85" s="4"/>
-    </row>
-    <row r="86" spans="1:9">
-      <c r="A86" s="2"/>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="4"/>
-      <c r="G86" s="2"/>
-      <c r="H86" s="2"/>
-      <c r="I86" s="4"/>
-    </row>
-    <row r="87" spans="1:9">
-      <c r="A87" s="2"/>
-      <c r="D87" s="4"/>
-      <c r="E87" s="4"/>
-      <c r="F87" s="4"/>
-      <c r="G87" s="2"/>
-      <c r="H87" s="2"/>
-      <c r="I87" s="4"/>
-    </row>
-    <row r="88" spans="1:9">
-      <c r="A88" s="2"/>
-      <c r="D88" s="4"/>
-      <c r="E88" s="4"/>
-      <c r="F88" s="4"/>
-      <c r="G88" s="2"/>
-      <c r="H88" s="2"/>
-      <c r="I88" s="4"/>
-    </row>
-    <row r="89" spans="1:9">
-      <c r="A89" s="2"/>
-      <c r="D89" s="4"/>
-      <c r="E89" s="4"/>
-      <c r="F89" s="4"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="4"/>
-    </row>
-    <row r="90" spans="1:9">
-      <c r="A90" s="2"/>
-      <c r="D90" s="4"/>
-      <c r="E90" s="4"/>
-      <c r="F90" s="4"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="4"/>
-    </row>
-    <row r="91" spans="1:9">
-      <c r="A91" s="2"/>
-      <c r="B91" s="6"/>
-      <c r="D91" s="4"/>
-      <c r="E91" s="4"/>
-      <c r="F91" s="4"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="4"/>
-    </row>
-    <row r="92" spans="1:9">
-      <c r="A92" s="2"/>
-      <c r="D92" s="4"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-    </row>
-    <row r="93" spans="1:9">
-      <c r="A93" s="2"/>
-      <c r="D93" s="4"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-    </row>
-    <row r="94" spans="1:9">
-      <c r="A94" s="2"/>
-      <c r="B94" s="6"/>
-      <c r="D94" s="4"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-    </row>
-    <row r="95" spans="1:9">
-      <c r="A95" s="2"/>
-      <c r="D95" s="4"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-    </row>
-    <row r="96" spans="1:9">
-      <c r="A96" s="2"/>
-      <c r="D96" s="4"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-    </row>
-    <row r="97" spans="1:1">
-      <c r="A97" s="2"/>
-    </row>
-    <row r="98" spans="1:1">
-      <c r="A98" s="2"/>
-    </row>
-    <row r="99" spans="1:1">
-      <c r="A99" s="2"/>
-    </row>
-    <row r="100" spans="1:1">
-      <c r="A100" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="246">
   <si>
     <t>name</t>
   </si>
@@ -1146,15 +1146,6 @@
 2、检查更新结果</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中数据，指定$replace更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中数据，cond指定的字段名存在且值为空，如：
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>db.cs.cl.find查看不存在的字段更新失败，不存在字段之前的字段更新成功，之后的字段更新失败，如：
 "字段名1"更新成功；
 "字段名2"更新失败；
@@ -1162,10 +1153,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，cond指定匹配符更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update，cond指定的字段名不存在</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1332,6 +1319,69 @@
     <t>1、sdb运行正常
 2、sdb已存在domian、CS、CL
 3、sdb已插入待更新的数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参考查询的cond --跟余婷的find交叉测试即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新成功，使用匹配符匹配数据正确，数据更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，cond指定匹配符更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，cond指定正确的"$+标识符"匹配数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，cond指定错误的"$+标识符"匹配数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误的书写格式：$5.4，$a2，$3c，$MA。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法
+{"字段名.$+标识符":value}
+$+标识符是一种特殊的命令符，这种命令符只作用于数组对象，标识符是一个整数，如 $1，$3，标识符相当于一个临时的存储，会把匹配成功的数组元素的索引存储起来。
+这种命令符只作用于数组，用来代替数组的索引 Key，并且可以把匹配到的第一个索引值传递到方法 update 的 rule 参数中。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、sdb运行正常
+2、sdb已存在domian、CS、CL
+3、sdb已插入待更新的数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$replace更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update，cond指定正确的"$+标识符"匹配数据，如：
+db.foo.bar.find({"a.$1":5},{a:1})
+无边界，取较大值测试
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新成功，记录按指定的匹配规格匹配数据，数据更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update，cond指定错误的"$+标识符"匹配数据，覆盖如下取值：
+错误的书写格式：$5.4，$a2，$3c，$MA。
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新失败，提示参数错误，提示信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1502,8 +1552,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I83" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I83"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I85" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I85"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1822,7 +1872,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="33.375" style="1" customWidth="1"/>
@@ -1972,11 +2022,11 @@
         <v>57</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:9" ht="67.5">
+    <row r="7" spans="1:9" ht="54">
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
@@ -2087,7 +2137,7 @@
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:9" ht="67.5">
+    <row r="13" spans="1:9" ht="54">
       <c r="A13" s="2" t="s">
         <v>42</v>
       </c>
@@ -2219,7 +2269,7 @@
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="67.5">
+    <row r="20" spans="1:9" ht="54">
       <c r="A20" s="2" t="s">
         <v>51</v>
       </c>
@@ -2258,7 +2308,7 @@
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="67.5">
+    <row r="22" spans="1:9" ht="54">
       <c r="A22" s="2" t="s">
         <v>52</v>
       </c>
@@ -2276,7 +2326,7 @@
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="67.5">
+    <row r="23" spans="1:9" ht="54">
       <c r="A23" s="2" t="s">
         <v>53</v>
       </c>
@@ -2495,7 +2545,7 @@
       </c>
       <c r="I34" s="4"/>
     </row>
-    <row r="35" spans="1:9" ht="148.5">
+    <row r="35" spans="1:9" ht="135">
       <c r="A35" s="2" t="s">
         <v>98</v>
       </c>
@@ -2516,7 +2566,7 @@
       </c>
       <c r="I35" s="4"/>
     </row>
-    <row r="36" spans="1:9" ht="67.5">
+    <row r="36" spans="1:9" ht="54">
       <c r="A36" s="2" t="s">
         <v>89</v>
       </c>
@@ -2534,7 +2584,7 @@
       </c>
       <c r="I36" s="4"/>
     </row>
-    <row r="37" spans="1:9" ht="67.5">
+    <row r="37" spans="1:9" ht="54">
       <c r="A37" s="2" t="s">
         <v>91</v>
       </c>
@@ -2642,7 +2692,7 @@
       </c>
       <c r="I42" s="4"/>
     </row>
-    <row r="43" spans="1:9" ht="175.5">
+    <row r="43" spans="1:9" ht="148.5">
       <c r="A43" s="2" t="s">
         <v>130</v>
       </c>
@@ -2663,7 +2713,7 @@
       </c>
       <c r="I43" s="4"/>
     </row>
-    <row r="44" spans="1:9" ht="67.5">
+    <row r="44" spans="1:9" ht="54">
       <c r="A44" s="2" t="s">
         <v>132</v>
       </c>
@@ -2681,7 +2731,7 @@
       </c>
       <c r="I44" s="4"/>
     </row>
-    <row r="45" spans="1:9" ht="67.5">
+    <row r="45" spans="1:9" ht="54">
       <c r="A45" s="2" t="s">
         <v>134</v>
       </c>
@@ -2792,7 +2842,7 @@
       </c>
       <c r="I50" s="4"/>
     </row>
-    <row r="51" spans="1:9" ht="67.5">
+    <row r="51" spans="1:9" ht="54">
       <c r="A51" s="2" t="s">
         <v>113</v>
       </c>
@@ -2810,7 +2860,7 @@
       </c>
       <c r="I51" s="4"/>
     </row>
-    <row r="52" spans="1:9" ht="67.5">
+    <row r="52" spans="1:9" ht="54">
       <c r="A52" s="2" t="s">
         <v>115</v>
       </c>
@@ -2900,7 +2950,7 @@
       </c>
       <c r="I56" s="4"/>
     </row>
-    <row r="57" spans="1:9" ht="175.5">
+    <row r="57" spans="1:9" ht="162">
       <c r="A57" s="2" t="s">
         <v>129</v>
       </c>
@@ -2921,7 +2971,7 @@
       </c>
       <c r="I57" s="4"/>
     </row>
-    <row r="58" spans="1:9" ht="67.5">
+    <row r="58" spans="1:9" ht="54">
       <c r="A58" s="2" t="s">
         <v>103</v>
       </c>
@@ -2939,7 +2989,7 @@
       </c>
       <c r="I58" s="4"/>
     </row>
-    <row r="59" spans="1:9" ht="67.5">
+    <row r="59" spans="1:9" ht="54">
       <c r="A59" s="2" t="s">
         <v>105</v>
       </c>
@@ -3029,7 +3079,7 @@
       </c>
       <c r="I63" s="4"/>
     </row>
-    <row r="64" spans="1:9" ht="175.5">
+    <row r="64" spans="1:9" ht="162">
       <c r="A64" s="2" t="s">
         <v>146</v>
       </c>
@@ -3050,7 +3100,7 @@
       </c>
       <c r="I64" s="4"/>
     </row>
-    <row r="65" spans="1:9" ht="67.5">
+    <row r="65" spans="1:9" ht="54">
       <c r="A65" s="2" t="s">
         <v>141</v>
       </c>
@@ -3115,7 +3165,7 @@
       <c r="E68" s="4"/>
       <c r="F68" s="4"/>
       <c r="G68" s="2" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>36</v>
@@ -3124,7 +3174,7 @@
     </row>
     <row r="69" spans="1:9" ht="121.5">
       <c r="A69" s="6" t="s">
-        <v>199</v>
+        <v>235</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>165</v>
@@ -3136,55 +3186,57 @@
       <c r="E69" s="4"/>
       <c r="F69" s="4"/>
       <c r="G69" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="H69" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="H69" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="I69" s="4"/>
     </row>
-    <row r="70" spans="1:9" ht="67.5">
+    <row r="70" spans="1:9" ht="162">
       <c r="A70" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="B70" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>239</v>
+      </c>
       <c r="C70" s="1" t="s">
-        <v>26</v>
+        <v>240</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
       <c r="F70" s="4"/>
       <c r="G70" s="2" t="s">
-        <v>216</v>
+        <v>242</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>201</v>
+        <v>243</v>
       </c>
       <c r="I70" s="4"/>
     </row>
-    <row r="71" spans="1:9" ht="135">
-      <c r="A71" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C71" s="1" t="s">
-        <v>26</v>
+    <row r="71" spans="1:9" ht="54">
+      <c r="A71" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>238</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
       <c r="F71" s="4"/>
       <c r="G71" s="2" t="s">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="I71" s="4"/>
     </row>
     <row r="72" spans="1:9" ht="67.5">
       <c r="A72" s="2" t="s">
-        <v>203</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="B72" s="2"/>
       <c r="C72" s="1" t="s">
         <v>26</v>
       </c>
@@ -3192,16 +3244,19 @@
       <c r="E72" s="4"/>
       <c r="F72" s="4"/>
       <c r="G72" s="2" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="I72" s="4"/>
     </row>
-    <row r="73" spans="1:9" ht="121.5">
+    <row r="73" spans="1:9" ht="135">
       <c r="A73" s="2" t="s">
-        <v>32</v>
+        <v>201</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>199</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>26</v>
@@ -3210,37 +3265,34 @@
       <c r="E73" s="4"/>
       <c r="F73" s="4"/>
       <c r="G73" s="2" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="I73" s="4"/>
     </row>
     <row r="74" spans="1:9" ht="67.5">
       <c r="A74" s="2" t="s">
-        <v>31</v>
+        <v>200</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D74" s="4">
-        <v>1</v>
-      </c>
+      <c r="D74" s="4"/>
       <c r="E74" s="4"/>
       <c r="F74" s="4"/>
       <c r="G74" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H74" s="2"/>
+        <v>216</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>202</v>
+      </c>
       <c r="I74" s="4"/>
     </row>
     <row r="75" spans="1:9" ht="121.5">
       <c r="A75" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>213</v>
+        <v>32</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>26</v>
@@ -3249,54 +3301,55 @@
       <c r="E75" s="4"/>
       <c r="F75" s="4"/>
       <c r="G75" s="2" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="I75" s="4"/>
     </row>
-    <row r="76" spans="1:9" ht="54">
+    <row r="76" spans="1:9" ht="67.5">
       <c r="A76" s="2" t="s">
-        <v>210</v>
+        <v>31</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D76" s="4"/>
+      <c r="D76" s="4">
+        <v>1</v>
+      </c>
       <c r="E76" s="4"/>
       <c r="F76" s="4"/>
       <c r="G76" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H76" s="2"/>
+      <c r="I76" s="4"/>
+    </row>
+    <row r="77" spans="1:9" ht="121.5">
+      <c r="A77" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="H76" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I76" s="4"/>
-    </row>
-    <row r="77" spans="1:9" ht="67.5">
-      <c r="A77" s="2" t="s">
-        <v>214</v>
+      <c r="B77" s="5" t="s">
+        <v>210</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D77" s="4">
-        <v>1</v>
-      </c>
+      <c r="D77" s="4"/>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
       <c r="G77" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="H77" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I77" s="4"/>
+    </row>
+    <row r="78" spans="1:9" ht="54">
+      <c r="A78" s="2" t="s">
         <v>207</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="121.5">
-      <c r="A78" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>213</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>26</v>
@@ -3305,97 +3358,95 @@
       <c r="E78" s="4"/>
       <c r="F78" s="4"/>
       <c r="G78" s="2" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="I78" s="4"/>
     </row>
-    <row r="79" spans="1:9" ht="54">
+    <row r="79" spans="1:9" ht="67.5">
       <c r="A79" s="2" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D79" s="4"/>
-      <c r="E79" s="4"/>
-      <c r="F79" s="4"/>
+      <c r="D79" s="4">
+        <v>1</v>
+      </c>
       <c r="G79" s="2" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="I79" s="4"/>
+        <v>204</v>
+      </c>
     </row>
     <row r="80" spans="1:9" ht="121.5">
       <c r="A80" s="2" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D80" s="4">
-        <v>1</v>
-      </c>
+      <c r="D80" s="4"/>
+      <c r="E80" s="4"/>
+      <c r="F80" s="4"/>
       <c r="G80" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="I80" s="4"/>
+    </row>
+    <row r="81" spans="1:9" ht="54">
+      <c r="A81" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" ht="67.5">
-      <c r="A81" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="C81" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="D81" s="4">
-        <v>1</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="D81" s="4"/>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
       <c r="G81" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>233</v>
+        <v>206</v>
       </c>
       <c r="I81" s="4"/>
     </row>
-    <row r="82" spans="1:9" ht="67.5">
+    <row r="82" spans="1:9" ht="121.5">
       <c r="A82" s="2" t="s">
-        <v>229</v>
+        <v>209</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>212</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>235</v>
+        <v>26</v>
       </c>
       <c r="D82" s="4">
         <v>1</v>
       </c>
-      <c r="E82" s="4"/>
-      <c r="F82" s="4"/>
       <c r="G82" s="2" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I82" s="4"/>
-    </row>
-    <row r="83" spans="1:9" ht="94.5">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" ht="67.5">
       <c r="A83" s="2" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D83" s="4">
         <v>1</v>
@@ -3403,12 +3454,52 @@
       <c r="E83" s="4"/>
       <c r="F83" s="4"/>
       <c r="G83" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="H83" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I83" s="4"/>
+    </row>
+    <row r="84" spans="1:9" ht="67.5">
+      <c r="A84" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C84" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="H83" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I83" s="4"/>
+      <c r="D84" s="4">
+        <v>1</v>
+      </c>
+      <c r="E84" s="4"/>
+      <c r="F84" s="4"/>
+      <c r="G84" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I84" s="4"/>
+    </row>
+    <row r="85" spans="1:9" ht="94.5">
+      <c r="A85" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="D85" s="4">
+        <v>1</v>
+      </c>
+      <c r="E85" s="4"/>
+      <c r="F85" s="4"/>
+      <c r="G85" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="H85" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I85" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
@@ -10,7 +10,79 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+每个更新符都需要覆盖，分区表</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>sharding key</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A86" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+覆盖分区表和普通表</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22,7 +94,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="260">
   <si>
     <t>name</t>
   </si>
@@ -88,19 +160,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，rule配置正确更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>更新成功，db.cs.cl.find查看指定更新的字段已更新，且数据更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，rule指定更新的部分字段为分区键字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，rule指定更新的字段均为分区键字段</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -109,24 +169,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>更新失败，提示分区键字段不能更新，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update，rule指定的字段名不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-3、sdb已插入待更新的数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：db.collectionspace.collection.update(&lt; rule &gt;,[ cond ],[ hint ])
-参数规格：
-Json 对象，格式：{"更新符1":{字段名1:"值"},"更新符2":{"字段名2":"值2"},...}
-update暂不支持对表分区键（ShardingKey）字段更新，如果包含对分区键的更新操作，跳过不更新。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -175,18 +218,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，覆盖$inc字段值有效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$inc指定更新的字段名不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，覆盖$inc字段值无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update，$inc指定的字段跟原字段数据类型不一致</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -195,10 +226,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，覆盖$set字段值有效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update，$set指定的字段名不存在</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -211,18 +238,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，$unset指定的字段名存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新成功，指定的字段名和字段值在集合中被删除</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，$unset指定的部分字段名不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新成功，指定的字段名在记录中不存在则跳过不更新，跳过后往下继续更新</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -237,31 +256,6 @@
   <si>
     <t>update，$addtose指定的字段名不存在</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL指定数据，覆盖如下场景：
-  a.更新1个字段的值,如：{"更新符1":{字段名1:"值"}}
-  b.更新多个字段的值，如：{"更新符1":{"字段名1":"值1"，"字段名2":"值2"，"字段名3":"值3"}}
-输入的更新符、字段名、值正确
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL指定数据，rule指定更新的部分字段为分区键字段，如：
-更新多个字段的值，如：{"更新符1":{"字段名1":"值1"，"字段名2":"值2"，"字段名3":"值3"}}
----其中"字段名2"为分区键字段
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL指定数据，rule指定更新的部分字段为分区键字段，如：
-更新多个字段的值，如：{"更新符1":{"字段名1":"值1"，"字段名2":"值2"，"字段名3":"值3"}}
----其中指定更新的所有字段均为分区键字段
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL指定数据，rule指定更新的部分字段为分区键字段，如：
-更新多个字段的值，如：{"更新符1":{"字段名1":"值1"，"字段名2":"值2"，"字段名3":"值3"}}
----其中"字段名2"在sdb不存在
-2、检查更新结果</t>
   </si>
   <si>
     <t>1、进入sdb，update更新CL指定数据，rule指定的更新符错误，如：{"test1":{"字段名1":"值1"}}
@@ -271,50 +265,6 @@
     <t>1、进入sdb，update更新CL指定数据，rule指定的更新符错误，如：
 {"":{字段名1:"值"}}    或  
 {"字段名1":{字段名1:""}}
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL指定数据，覆盖$inc更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
-int：-2147483648、2147483647
-long：-9223372036854775808、9223372036854775807
-float：1.7E-308、1.7E+308
-string:16M
-oid：24位字节
-bool：true、false
-date:1902-01-18、2038-01-18
-timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
-binary(Base64)：
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL指定数据，指定$inc更新符更新数据，对应的字段名不存在，如：
-{$inc:{&lt;字段名1&gt;:&lt;值1&gt;}，其中&lt;字段名1&gt;不存在
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL指定数据，覆盖$inc更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
-int：-2147483649、2147483648
-long：-9223372036854775809、9223372036854775808
-float：1.6E-308、1.8E+308
-string:16.5M
-oid：23、25位字节
-bool：test
-date:1902-01-17、2038-01-19
-timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
-regex：
-subobj：
-array(数组)：
-null：
-minkey：
-maxkey：
-说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
 2、检查更新结果</t>
   </si>
   <si>
@@ -458,11 +408,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、空串，如：{$pop:{&lt;字段名1&gt;:}}   或  {$pop:{"":}}
-2、取值非整数，如{$pop:{age:test}}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>update，$pop取值非法</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -486,9 +431,6 @@
   </si>
   <si>
     <t>update，覆盖$pull字段值有效取值</t>
-  </si>
-  <si>
-    <t>update，覆盖$pull字段值无效取值</t>
   </si>
   <si>
     <t>update，$pull指定的字段跟原字段数据类型不一致</t>
@@ -540,12 +482,6 @@
     <t>update，覆盖$push_all字段值有效取值</t>
   </si>
   <si>
-    <t>update，覆盖$push_all字段值无效取值</t>
-  </si>
-  <si>
-    <t>update，$push_all指定的字段跟原字段数据类型不一致</t>
-  </si>
-  <si>
     <t>update，$push_all指定的字段名非数组对象</t>
   </si>
   <si>
@@ -571,9 +507,6 @@
   </si>
   <si>
     <t>update，覆盖$push字段值有效取值</t>
-  </si>
-  <si>
-    <t>update，覆盖$push字段值无效取值</t>
   </si>
   <si>
     <t>update，$push指定的字段跟原字段数据类型不一致</t>
@@ -612,11 +545,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、更新成功，不存在的字段名系统自动补充该字段名和指定的值
-2、db.cs.cl.find查看指定更新的字段已更新，不存在的字段名新增，字段值为指定添加的值，更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新失败，提示参数错误，提示信息合理准确
 2、db.cs.cl.find查看指定更新的字段未被更新</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -649,9 +577,6 @@
     <t>update，覆盖$pull_all字段值有效取值</t>
   </si>
   <si>
-    <t>update，覆盖$pull_all字段值无效取值</t>
-  </si>
-  <si>
     <t>update，$pull_all指定的字段跟原字段数据类型不一致</t>
   </si>
   <si>
@@ -670,9 +595,6 @@
   </si>
   <si>
     <t>update，覆盖$replace字段值有效取值</t>
-  </si>
-  <si>
-    <t>update，覆盖$replace字段值无效取值</t>
   </si>
   <si>
     <t>update，$replace指定的字段跟原字段数据类型不一致</t>
@@ -767,12 +689,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-3、sdb已插入待更新的数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新成功，字段名存在值也存在，则跳过不添加，其他指定字段更新成功
 2、db.cs.cl.find查看字段更新正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -782,13 +698,6 @@
 {$set:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
 更新符：$set，将指定的“&lt;字段名&gt;”更新为指定的“&lt;值&gt;”
 如果字段名不存在则补充，如果存在则更新。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：
-{$unset:{&lt;字段名1&gt;:"",&lt;字段名2&gt;:"",...}}
-更新符：$unset，删除集合中指定的字段名。
-如果记录中没有指定的字段名，跳过</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -953,11 +862,6 @@
 2、检查更新结果</t>
   </si>
   <si>
-    <t>1、进入sdb，update更新CL中数据，指定$pull更新符更新数据，数据为空，如：
-{$push:{&lt;字段名1&gt;:}}  或  {$push:{"":""}}
-2、检查更新结果</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL中数据，指定$pull更新符更新数据，$pull指定的字段名非数组对象，如：
 {$pull:{a:1}}，其中a为string类型的普通记录
 2、检查更新结果</t>
@@ -1127,6 +1031,293 @@
 2、检查更新结果</t>
   </si>
   <si>
+    <t>db.cs.cl.find查看不存在的字段更新失败，不存在字段之前的字段更新成功，之后的字段更新失败，如：
+"字段名1"更新成功；
+"字段名2"更新失败；
+"字段名3"更新失败；</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，cond指定的字段名不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新失败，提示字段不存在，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格式：
+[{"":"索引名"|null}]
+hint 参数是一个包含一个单一字段的 Json 对象，字段名会被忽略，而其字段值则指定为需要访问索引的名称，当字段值为 null 时，则遍历集合中所有的记录，它的格式为{"":null}或者{"":"&lt; indexname &gt;"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，hint指定的字段值为null</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，hint指定的字段值为需要访问索引的名称</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新成功，遍历所有的记录更新，记录更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新失败，提示索引字段值不能重复，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新成功，字段名不存在upsert直接做插入操作，更新成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同update，upsert更新调用的是update的接口，跟update交叉测试即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同update</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upsert，指定无效的字段名和字段值更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upsert，指定有效的字段名和字段值更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update，returnNew指定为true</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.collectionspace.collection.upsert(&lt;rule&gt;,[cond],[hint],[setOnInsert])
+upsert
+当使用cond参数在集合中匹配不到记录时，update 不做任何操作，而 upsert 方法会做一次插入操作。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>upsert，cond指定的字段名不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格式：query.update(&lt;update&gt;,[returnNew])
+update：Json对象，更新规则。记录按update的内容更新。必填
+returnNew： bool，是否返回更新后的记录。非必填</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，cond指定的字段名不存在，如：
+db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":"testIndex"})，其中age字段不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，hint指定的字段值为需要访问索引的名称，如：
+db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":"testIndex"})，其中"testIndex"为需要访问索引的名称
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>更新成功，使用索引名为 testIndex 的索引访问集合中匹配条件的记录，记录更新正确，如：
+db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":"testIndex"})&gt;
+此操作使用索引名为 testIndex 的索引访问集合 bar 中 age 字段值大于20的记录，将这些记录的 age 字段名加1。</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，hint指定的字段值为null，如：
+db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":""})
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建索引testIndex，update更新CL中数据，指定的字段为所有字段，指定的值为索引字段的值，且修改索引字段值重复，如：testCL表中存在记录{age:1,age:2}
+创建索引：db.CS.CL.createIndex("ageIndex",{age:1},true)
+update更新age的值为1
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，upsert更新CL指定数据，cond指定的字段名不存在，如：
+db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":"testIndex"})，其中age字段不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update更新CL指定数据，returnNew指定为true，其他参数正确，如：
+db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:true)
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新成功，结果返回修改后的所有记录值，返回的记录跟实际更新的记录数以及内容一致，修改正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update，指定有效的字段名和字段值更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update，指定无效的字段名和字段值更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>同update，跟update交叉测试即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update，returnNew指定为false</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update更新CL指定数据，returnNew指定为false，其他参数正确，如：
+db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:false)
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update，returnNew取值非法</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update更新CL指定数据，returnNew取值非法，如：
+db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:test)
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update，returnNew取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update更新CL指定数据，returnNew取值为空，如：
+db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:)
+db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},)
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新失败，结果不打印修改后的所有记录值
+2、db.cs.cl.find查看指定更新的字段更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、更新失败，提示参数错误，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>参考查询的cond --跟余婷的find交叉测试即可</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新成功，使用匹配符匹配数据正确，数据更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，cond指定匹配符更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，cond指定正确的"$+标识符"匹配数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，cond指定错误的"$+标识符"匹配数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>错误的书写格式：$5.4，$a2，$3c，$MA。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法
+{"字段名.$+标识符":value}
+$+标识符是一种特殊的命令符，这种命令符只作用于数组对象，标识符是一个整数，如 $1，$3，标识符相当于一个临时的存储，会把匹配成功的数组元素的索引存储起来。
+这种命令符只作用于数组，用来代替数组的索引 Key，并且可以把匹配到的第一个索引值传递到方法 update 的 rule 参数中。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$replace更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update，cond指定正确的"$+标识符"匹配数据，如：
+db.foo.bar.find({"a.$1":5},{a:1})
+无边界，取较大值测试
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新成功，记录按指定的匹配规格匹配数据，数据更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update，cond指定错误的"$+标识符"匹配数据，覆盖如下取值：
+错误的书写格式：$5.4，$a2，$3c，$MA。
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新失败，提示参数错误，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，rule配置正确更新数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，覆盖如下场景：
+  a.更新1个字段的值,如：{"更新符1":{字段名1:"值"}}
+  b.更新多个字段的值，如：{"更新符1":{"字段名1":"值1"，"字段名2":"值2"，"字段名3":"值3"}}
+输入的更新符、字段名、值正确
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，覆盖$inc更新符中字段值有效取值，对应的字段名存在，覆盖所有数据类型边界：
+int：-2147483648、2147483647
+long：-9223372036854775808、9223372036854775807
+float：1.7E-308、1.7E+308
+string:16M
+oid：24位字节
+bool：true、false
+date:1902-01-18、2038-01-18
+timestamp：1902-01-18-00.00.00.000000、2038-01-18-00.00.00.000000
+binary(Base64)：
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，覆盖$inc更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
+int：-2147483649、2147483648
+long：-9223372036854775809、9223372036854775808
+float：1.6E-308、1.8E+308
+string:16.5M
+oid：23、25位字节
+bool：test
+date:1902-01-17、2038-01-19
+timestamp：1902-01-17-00.00.00.000000、2038-01-19-00.00.00.000000
+regex：
+subobj：
+array(数组)：
+null：
+minkey：
+maxkey：
+说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+{$unset:{&lt;字段名1&gt;:"",&lt;字段名2&gt;:"",...}}
+更新符：$unset，删除集合中指定的字段名。
+如果记录中没有指定的字段名，跳过</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>1、进入sdb，update更新CL中数据，覆盖$replace更新符中字段值无效取值，对应的字段名存在，覆盖所有数据类型超出边界的值：
 int：-2147483649、2147483648
 long：-9223372036854775809、9223372036854775808
@@ -1144,241 +1335,202 @@
 maxkey：
 说明：原始数据可以取值为0测试增加该数据类型最大边界值，查看数据是否更新成功
 2、检查更新结果</t>
-  </si>
-  <si>
-    <t>db.cs.cl.find查看不存在的字段更新失败，不存在字段之前的字段更新成功，之后的字段更新失败，如：
-"字段名1"更新成功；
-"字段名2"更新失败；
-"字段名3"更新失败；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，cond指定的字段名不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新失败，提示字段不存在，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>格式：
-[{"":"索引名"|null}]
-hint 参数是一个包含一个单一字段的 Json 对象，字段名会被忽略，而其字段值则指定为需要访问索引的名称，当字段值为 null 时，则遍历集合中所有的记录，它的格式为{"":null}或者{"":"&lt; indexname &gt;"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，hint指定的字段值为null</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，hint指定的字段值为需要访问索引的名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新成功，遍历所有的记录更新，记录更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新失败，提示索引字段值不能重复，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新成功，字段名不存在upsert直接做插入操作，更新成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同update，upsert更新调用的是update的接口，跟update交叉测试即可</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同update</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upsert，指定无效的字段名和字段值更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upsert，指定有效的字段名和字段值更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query.update，returnNew指定为true</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：db.collectionspace.collection.upsert(&lt;rule&gt;,[cond],[hint],[setOnInsert])
-upsert
-当使用cond参数在集合中匹配不到记录时，update 不做任何操作，而 upsert 方法会做一次插入操作。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upsert，cond指定的字段名不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>格式：query.update(&lt;update&gt;,[returnNew])
-update：Json对象，更新规则。记录按update的内容更新。必填
-returnNew： bool，是否返回更新后的记录。非必填</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中数据，cond指定的字段名不存在，如：
-db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":"testIndex"})，其中age字段不存在
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中数据，hint指定的字段值为需要访问索引的名称，如：
-db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":"testIndex"})，其中"testIndex"为需要访问索引的名称
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>更新成功，使用索引名为 testIndex 的索引访问集合中匹配条件的记录，记录更新正确，如：
-db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":"testIndex"})&gt;
-此操作使用索引名为 testIndex 的索引访问集合 bar 中 age 字段值大于20的记录，将这些记录的 age 字段名加1。</t>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中数据，hint指定的字段值为null，如：
-db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":""})
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建索引testIndex，update更新CL中数据，指定的字段为所有字段，指定的值为索引字段的值，且修改索引字段值重复，如：testCL表中存在记录{age:1,age:2}
-创建索引：db.CS.CL.createIndex("ageIndex",{age:1},true)
-update更新age的值为1
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，upsert更新CL指定数据，cond指定的字段名不存在，如：
-db.CS.CL.update({$inc:{age:1}},{age:{$gt:20}},{"":"testIndex"})，其中age字段不存在
-2、检查更新结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，query.update更新CL指定数据，returnNew指定为true，其他参数正确，如：
-db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:true)
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新成功，结果返回修改后的所有记录值，返回的记录跟实际更新的记录数以及内容一致，修改正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query.update，指定有效的字段名和字段值更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query.update，指定无效的字段名和字段值更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>同update，跟update交叉测试即可</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query.update，returnNew指定为false</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，query.update更新CL指定数据，returnNew指定为false，其他参数正确，如：
-db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:false)
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query.update，returnNew取值非法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，query.update更新CL指定数据，returnNew取值非法，如：
-db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:test)
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query.update，returnNew取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，query.update更新CL指定数据，returnNew取值为空，如：
-db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:)
-db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},)
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、更新失败，结果不打印修改后的所有记录值
-2、db.cs.cl.find查看指定更新的字段更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、更新失败，提示参数错误，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-3、sdb已插入待更新的数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>参考查询的cond --跟余婷的find交叉测试即可</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新成功，使用匹配符匹配数据正确，数据更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，cond指定匹配符更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，cond指定正确的"$+标识符"匹配数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，cond指定错误的"$+标识符"匹配数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>错误的书写格式：$5.4，$a2，$3c，$MA。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法
-{"字段名.$+标识符":value}
-$+标识符是一种特殊的命令符，这种命令符只作用于数组对象，标识符是一个整数，如 $1，$3，标识符相当于一个临时的存储，会把匹配成功的数组元素的索引存储起来。
-这种命令符只作用于数组，用来代替数组的索引 Key，并且可以把匹配到的第一个索引值传递到方法 update 的 rule 参数中。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdb运行正常
-2、sdb已存在domian、CS、CL
-3、sdb已插入待更新的数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，update更新CL中数据，指定$replace更新符更新数据，更新的字段值跟原字段值数据类型不一致，如：插入的是int数组，更新的字段值为字符串
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，update，cond指定正确的"$+标识符"匹配数据，如：
-db.foo.bar.find({"a.$1":5},{a:1})
-无边界，取较大值测试
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>更新成功，记录按指定的匹配规格匹配数据，数据更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，update，cond指定错误的"$+标识符"匹配数据，覆盖如下取值：
-错误的书写格式：$5.4，$a2，$3c，$MA。
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.collectionspace.collection.update(&lt; rule &gt;,[ cond ],[ hint ])
+参数规格：
+Json 对象，格式：{"更新符1":{字段名1:"值"},"更新符2":{"字段名2":"值2"},...}
+update暂不支持对表分区键（ShardingKey）字段更新，如果包含对分区键的更新操作，跳过不更新。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，覆盖$inc字段值有效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$inc指定更新的字段名不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，指定$inc更新符更新数据，对应的字段名不存在，如：
+{$inc:{&lt;字段名1&gt;:&lt;值1&gt;}，其中&lt;字段名1&gt;不存在
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新失败，提示分区键字段不能更新，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，覆盖$set字段值有效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$unset指定的部分字段名不存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$inc指定更新的字段为分区键字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$set指定更新的字段为分区键字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$unset指定的字段名存在</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$unset指定更新的字段为分区键字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$addtose指定更新的字段为分区键字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$pop指定更新的字段为分区键字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，rule指定更新的字段为分区键字段</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，rule指定更新的字段为分区键字段，如：
+更新多个字段的值，如：{"更新符1":{"字段名1":"值1"，"字段名2":"值2"，"字段名3":"值3"}}
+---其中"字段名2"为分区键字段
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，rule指定更新的字段为分区键字段，如：
+更新多个字段的值，如：{"更新符1":{"字段名1":"值1"，"字段名2":"值2"，"字段名3":"值3"}}
+---其中"字段名2"在sdb不存在
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，$inc指定更新的字段为分区键字段，如：
+{$inc:{&lt;字段名1&gt;:&lt;值1&gt;}}
+---其中"字段名1"为分区键字段
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，$set指定更新的字段为分区键字段，如：
+{$set:{&lt;字段名1&gt;:&lt;值1&gt;}}
+---其中"字段名1"为分区键字段
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，$unset指定更新的字段为分区键字段，如：
+{$unset:{&lt;字段名1&gt;:&lt;值1&gt;}}
+---其中"字段名1"为分区键字段
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，$addtose指定更新的字段为分区键字段，如：
+{$addtose:{&lt;字段名1&gt;:&lt;值1&gt;}}
+---其中"字段名1"为分区键字段
+2、检查更新结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，$pop指定更新的字段为分区键字段，如：
+{$pop:{&lt;字段名1&gt;:}}
+---其中"字段名1"为分区键字段
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，覆盖$pull字段值无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$pull指定更新的字段为分区键字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL中数据，指定$pull更新符更新数据，数据为空，如：
+{$pull:{&lt;字段名1&gt;:}}  或  {$pull:{"":""}}
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，覆盖$pull_all字段值无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$pull_all字指定更新的字段为分区键字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，$pull_all字指定更新的字段为分区键字段，如：
+{$pull_all:&lt;字段名1&gt;:[&lt;值1&gt;}}
+---其中"字段名1"为分区键字段
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，$pull指定更新的字段为分区键字段，如：
+{$pull:&lt;字段名1&gt;:[&lt;值1&gt;}}
+---其中"字段名1"为分区键字段
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，覆盖$push字段值无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$push字指定更新的字段为分区键字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，$push字指定更新的字段为分区键字段，如：
+{$push:&lt;字段名1&gt;:[&lt;值1&gt;}}
+---其中"字段名1"为分区键字段
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$push_all指定的字段跟原字段数据类型不一致</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，覆盖$push_all字段值无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$push_all字指定更新的字段为分区键字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，$push_all字指定更新的字段为分区键字段，如：
+{$push_all:&lt;字段名1&gt;:[&lt;值1&gt;}}
+---其中"字段名1"为分区键字段
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，覆盖$replace字段值无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$replace字指定更新的字段为分区键字段</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，update更新CL指定数据，$replace字指定更新的字段为分区键字段，如：
+{$replace:&lt;字段名1&gt;:[&lt;值1&gt;}}
+---其中"字段名1"为分区键字段
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，$inc字段值类型超出边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新失败，提示参数错误，提示信息合理准确</t>
   </si>
   <si>
     <t>更新失败，提示参数错误，提示信息合理准确</t>
@@ -1389,7 +1541,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1418,6 +1570,27 @@
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1552,8 +1725,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I85" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I85"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I94" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I94"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1872,7 +2045,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="33.375" style="1" customWidth="1"/>
@@ -1945,28 +2118,28 @@
     </row>
     <row r="3" spans="1:9" ht="175.5">
       <c r="A3" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4">
+        <v>1</v>
+      </c>
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+      <c r="F3" s="4">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>19</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="4">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -1974,1539 +2147,2426 @@
     </row>
     <row r="4" spans="1:9" ht="81">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>232</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
       <c r="G4" s="2" t="s">
-        <v>55</v>
+        <v>233</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="4"/>
+        <v>20</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="81">
       <c r="A5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="54">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="4"/>
-    </row>
-    <row r="6" spans="1:9" ht="81">
-      <c r="A6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="I6" s="4"/>
-    </row>
-    <row r="7" spans="1:9" ht="54">
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="67.5">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
       <c r="G7" s="2" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I7" s="4"/>
-    </row>
-    <row r="8" spans="1:9" ht="67.5">
+        <v>22</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="168" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>29</v>
+        <v>220</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D8" s="4">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
       <c r="G8" s="2" t="s">
-        <v>59</v>
+        <v>215</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="I8" s="4"/>
-    </row>
-    <row r="9" spans="1:9" ht="168" customHeight="1">
+        <v>27</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="67.5">
       <c r="A9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D9" s="4">
+        <v>1</v>
+      </c>
+      <c r="E9" s="4">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
       <c r="G9" s="2" t="s">
-        <v>60</v>
+        <v>235</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I9" s="4"/>
+        <v>223</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="67.5">
       <c r="A10" s="2" t="s">
-        <v>39</v>
+        <v>221</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D10" s="4">
+        <v>1</v>
+      </c>
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
       <c r="G10" s="2" t="s">
-        <v>61</v>
+        <v>222</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="168" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>257</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D11" s="4">
+        <v>1</v>
+      </c>
+      <c r="E11" s="4">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>62</v>
+        <v>216</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I11" s="4"/>
+        <v>29</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="67.5">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
       <c r="G12" s="2" t="s">
-        <v>63</v>
+        <v>44</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I12" s="4"/>
+        <v>259</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="54">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
       <c r="G13" s="2" t="s">
-        <v>64</v>
+        <v>45</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="168" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>224</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>160</v>
+        <v>132</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
       <c r="G14" s="7" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I14" s="4"/>
+        <v>31</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="67.5">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>227</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D15" s="4">
+        <v>1</v>
+      </c>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
       <c r="G15" s="2" t="s">
-        <v>66</v>
+        <v>236</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="67.5">
+      <c r="A16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" ht="168" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="C16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
       <c r="G16" s="2" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="168" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:9" ht="67.5">
-      <c r="A17" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="C17" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
       <c r="G17" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="67.5">
+      <c r="A18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I17" s="4"/>
-    </row>
-    <row r="18" spans="1:9" ht="94.5">
-      <c r="A18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>161</v>
-      </c>
       <c r="C18" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
       <c r="G18" s="2" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="1:9" ht="67.5">
+        <v>258</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="94.5">
       <c r="A19" s="2" t="s">
-        <v>49</v>
+        <v>228</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>217</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1</v>
+      </c>
       <c r="G19" s="2" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="I19" s="4"/>
-    </row>
-    <row r="20" spans="1:9" ht="54">
+        <v>37</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="67.5">
       <c r="A20" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="E20" s="4">
+        <v>2</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="67.5">
+      <c r="A21" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="E21" s="4">
+        <v>1</v>
+      </c>
+      <c r="F21" s="4">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="1:9" ht="162">
-      <c r="A21" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="I21" s="4"/>
+        <v>38</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:9" ht="54">
       <c r="A22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="2" t="s">
-        <v>75</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I22" s="4"/>
-    </row>
-    <row r="23" spans="1:9" ht="54">
+        <v>30</v>
+      </c>
+      <c r="I22" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="162">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>130</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1</v>
+      </c>
       <c r="G23" s="2" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I23" s="4"/>
-    </row>
-    <row r="24" spans="1:9" ht="168" customHeight="1">
+        <v>131</v>
+      </c>
+      <c r="I23" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="54">
       <c r="A24" s="2" t="s">
-        <v>78</v>
+        <v>40</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
       <c r="G24" s="2" t="s">
-        <v>166</v>
+        <v>56</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I24" s="4"/>
-    </row>
-    <row r="25" spans="1:9" ht="67.5">
+        <v>54</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" ht="54">
       <c r="A25" s="2" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4">
+        <v>1</v>
+      </c>
       <c r="G25" s="2" t="s">
-        <v>167</v>
+        <v>57</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="4"/>
-    </row>
-    <row r="26" spans="1:9" ht="168" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>79</v>
+        <v>58</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="67.5">
+      <c r="A26" s="6" t="s">
+        <v>230</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="E26" s="4">
+        <v>2</v>
+      </c>
+      <c r="F26" s="4">
+        <v>1</v>
+      </c>
       <c r="G26" s="2" t="s">
-        <v>168</v>
+        <v>238</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I26" s="4"/>
-    </row>
-    <row r="27" spans="1:9" ht="67.5">
+        <v>223</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="168" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4">
+        <v>1</v>
+      </c>
       <c r="G27" s="2" t="s">
-        <v>169</v>
+        <v>137</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I27" s="4"/>
+        <v>27</v>
+      </c>
+      <c r="I27" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:9" ht="67.5">
       <c r="A28" s="2" t="s">
-        <v>97</v>
+        <v>41</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4">
+        <v>1</v>
+      </c>
       <c r="G28" s="2" t="s">
-        <v>170</v>
+        <v>138</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I28" s="4"/>
-    </row>
-    <row r="29" spans="1:9" ht="175.5">
+        <v>28</v>
+      </c>
+      <c r="I28" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="168" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>163</v>
+        <v>60</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4">
+        <v>2</v>
+      </c>
+      <c r="F29" s="4">
+        <v>1</v>
+      </c>
       <c r="G29" s="2" t="s">
-        <v>171</v>
+        <v>139</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="I29" s="4"/>
-    </row>
-    <row r="30" spans="1:9" ht="108">
+        <v>29</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="67.5">
       <c r="A30" s="2" t="s">
-        <v>84</v>
+        <v>61</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4">
+        <v>2</v>
+      </c>
+      <c r="F30" s="4">
+        <v>1</v>
+      </c>
       <c r="G30" s="2" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I30" s="4"/>
-    </row>
-    <row r="31" spans="1:9" ht="108">
+        <v>258</v>
+      </c>
+      <c r="I30" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" ht="67.5">
       <c r="A31" s="2" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4">
+        <v>2</v>
+      </c>
+      <c r="F31" s="4">
+        <v>1</v>
+      </c>
       <c r="G31" s="2" t="s">
-        <v>173</v>
+        <v>141</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I31" s="4"/>
-    </row>
-    <row r="32" spans="1:9" ht="67.5">
+        <v>30</v>
+      </c>
+      <c r="I31" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="175.5">
       <c r="A32" s="2" t="s">
-        <v>151</v>
+        <v>62</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>134</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D32" s="4">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4">
+        <v>1</v>
+      </c>
+      <c r="F32" s="4">
+        <v>1</v>
+      </c>
       <c r="G32" s="2" t="s">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I32" s="4"/>
-    </row>
-    <row r="33" spans="1:9" ht="67.5">
+        <v>63</v>
+      </c>
+      <c r="I32" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="108">
       <c r="A33" s="2" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4">
+        <v>1</v>
+      </c>
+      <c r="F33" s="4">
+        <v>1</v>
+      </c>
       <c r="G33" s="2" t="s">
-        <v>175</v>
+        <v>143</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I33" s="4"/>
-    </row>
-    <row r="34" spans="1:9" ht="54">
+        <v>64</v>
+      </c>
+      <c r="I33" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="108">
       <c r="A34" s="2" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4">
+        <v>1</v>
+      </c>
+      <c r="F34" s="4">
+        <v>1</v>
+      </c>
       <c r="G34" s="2" t="s">
-        <v>176</v>
+        <v>144</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I34" s="4"/>
-    </row>
-    <row r="35" spans="1:9" ht="135">
-      <c r="A35" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>156</v>
+        <v>64</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="67.5">
+      <c r="A35" s="6" t="s">
+        <v>231</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1</v>
+      </c>
+      <c r="E35" s="4">
+        <v>2</v>
+      </c>
+      <c r="F35" s="4">
+        <v>1</v>
+      </c>
       <c r="G35" s="2" t="s">
-        <v>88</v>
+        <v>239</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I35" s="4"/>
+        <v>223</v>
+      </c>
+      <c r="I35" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="36" spans="1:9" ht="54">
       <c r="A36" s="2" t="s">
-        <v>89</v>
+        <v>124</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4">
+        <v>2</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1</v>
+      </c>
       <c r="G36" s="2" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I36" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="I36" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="37" spans="1:9" ht="54">
       <c r="A37" s="2" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1</v>
+      </c>
       <c r="G37" s="2" t="s">
-        <v>92</v>
+        <v>146</v>
       </c>
       <c r="H37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="54">
+      <c r="A38" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1</v>
+      </c>
+      <c r="E38" s="4">
+        <v>2</v>
+      </c>
+      <c r="F38" s="4">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="135">
+      <c r="A39" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="I37" s="4"/>
-    </row>
-    <row r="38" spans="1:9" ht="168" customHeight="1">
-      <c r="A38" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I38" s="4"/>
-    </row>
-    <row r="39" spans="1:9" ht="168" customHeight="1">
-      <c r="A39" s="2" t="s">
-        <v>94</v>
+      <c r="B39" s="5" t="s">
+        <v>129</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D39" s="4">
+        <v>1</v>
+      </c>
+      <c r="E39" s="4">
+        <v>1</v>
+      </c>
+      <c r="F39" s="4">
+        <v>1</v>
+      </c>
       <c r="G39" s="2" t="s">
-        <v>178</v>
+        <v>68</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="I39" s="4"/>
+        <v>100</v>
+      </c>
+      <c r="I39" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="40" spans="1:9" ht="54">
       <c r="A40" s="2" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
       <c r="G40" s="2" t="s">
-        <v>179</v>
+        <v>70</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I40" s="4"/>
+        <v>101</v>
+      </c>
+      <c r="I40" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="1:9" ht="54">
       <c r="A41" s="2" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D41" s="4"/>
-      <c r="E41" s="4"/>
-      <c r="F41" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1</v>
+      </c>
+      <c r="E41" s="4">
+        <v>1</v>
+      </c>
+      <c r="F41" s="4">
+        <v>1</v>
+      </c>
       <c r="G41" s="2" t="s">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I41" s="4"/>
-    </row>
-    <row r="42" spans="1:9" ht="54">
+        <v>58</v>
+      </c>
+      <c r="I41" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="168" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D42" s="4"/>
-      <c r="E42" s="4"/>
-      <c r="F42" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" s="4">
+        <v>1</v>
+      </c>
       <c r="G42" s="2" t="s">
-        <v>181</v>
+        <v>148</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I42" s="4"/>
-    </row>
-    <row r="43" spans="1:9" ht="148.5">
+        <v>102</v>
+      </c>
+      <c r="I42" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="168" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>155</v>
+        <v>240</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D43" s="4">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4">
+        <v>2</v>
+      </c>
+      <c r="F43" s="4">
+        <v>1</v>
+      </c>
       <c r="G43" s="2" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I43" s="4"/>
-    </row>
-    <row r="44" spans="1:9" ht="54">
-      <c r="A44" s="2" t="s">
-        <v>132</v>
+        <v>75</v>
+      </c>
+      <c r="I43" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="67.5">
+      <c r="A44" s="6" t="s">
+        <v>241</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D44" s="4">
+        <v>1</v>
+      </c>
+      <c r="E44" s="4">
+        <v>2</v>
+      </c>
+      <c r="F44" s="4">
+        <v>1</v>
+      </c>
       <c r="G44" s="2" t="s">
-        <v>133</v>
+        <v>246</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I44" s="4"/>
+        <v>223</v>
+      </c>
+      <c r="I44" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="45" spans="1:9" ht="54">
       <c r="A45" s="2" t="s">
-        <v>134</v>
+        <v>74</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1</v>
+      </c>
+      <c r="E45" s="4">
+        <v>2</v>
+      </c>
+      <c r="F45" s="4">
+        <v>1</v>
+      </c>
       <c r="G45" s="2" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I45" s="4"/>
-    </row>
-    <row r="46" spans="1:9" ht="168" customHeight="1">
+        <v>212</v>
+      </c>
+      <c r="I45" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="54">
       <c r="A46" s="2" t="s">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D46" s="4">
+        <v>1</v>
+      </c>
+      <c r="E46" s="4">
+        <v>2</v>
+      </c>
+      <c r="F46" s="4">
+        <v>1</v>
+      </c>
       <c r="G46" s="2" t="s">
-        <v>182</v>
+        <v>242</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I46" s="4"/>
-    </row>
-    <row r="47" spans="1:9" ht="168" customHeight="1">
+        <v>103</v>
+      </c>
+      <c r="I46" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="54">
       <c r="A47" s="2" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D47" s="4"/>
-      <c r="E47" s="4"/>
-      <c r="F47" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1</v>
+      </c>
+      <c r="E47" s="4">
+        <v>2</v>
+      </c>
+      <c r="F47" s="4">
+        <v>1</v>
+      </c>
       <c r="G47" s="2" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="H47" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I47" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" ht="148.5">
+      <c r="A48" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D48" s="4">
+        <v>1</v>
+      </c>
+      <c r="E48" s="4">
+        <v>1</v>
+      </c>
+      <c r="F48" s="4">
+        <v>1</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I48" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" ht="54">
+      <c r="A49" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="4">
+        <v>1</v>
+      </c>
+      <c r="E49" s="4">
+        <v>1</v>
+      </c>
+      <c r="F49" s="4">
+        <v>1</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="I49" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" ht="54">
+      <c r="A50" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="4">
+        <v>1</v>
+      </c>
+      <c r="E50" s="4">
+        <v>1</v>
+      </c>
+      <c r="F50" s="4">
+        <v>1</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="I50" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" ht="168" customHeight="1">
+      <c r="A51" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D51" s="4">
+        <v>1</v>
+      </c>
+      <c r="E51" s="4">
+        <v>1</v>
+      </c>
+      <c r="F51" s="4">
+        <v>1</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I51" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" ht="168" customHeight="1">
+      <c r="A52" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D52" s="4">
+        <v>1</v>
+      </c>
+      <c r="E52" s="4">
+        <v>2</v>
+      </c>
+      <c r="F52" s="4">
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I52" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" ht="67.5">
+      <c r="A53" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D53" s="4">
+        <v>1</v>
+      </c>
+      <c r="E53" s="4">
+        <v>2</v>
+      </c>
+      <c r="F53" s="4">
+        <v>1</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I53" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" ht="67.5">
+      <c r="A54" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D54" s="4">
+        <v>1</v>
+      </c>
+      <c r="E54" s="4">
+        <v>2</v>
+      </c>
+      <c r="F54" s="4">
+        <v>1</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I54" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" ht="81">
+      <c r="A55" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D55" s="4">
+        <v>1</v>
+      </c>
+      <c r="E55" s="4">
+        <v>2</v>
+      </c>
+      <c r="F55" s="4">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I55" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" ht="135">
+      <c r="A56" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B56" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="I47" s="4"/>
-    </row>
-    <row r="48" spans="1:9" ht="67.5">
-      <c r="A48" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D48" s="4"/>
-      <c r="E48" s="4"/>
-      <c r="F48" s="4"/>
-      <c r="G48" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I48" s="4"/>
-    </row>
-    <row r="49" spans="1:9" ht="81">
-      <c r="A49" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C49" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D49" s="4"/>
-      <c r="E49" s="4"/>
-      <c r="F49" s="4"/>
-      <c r="G49" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="I49" s="4"/>
-    </row>
-    <row r="50" spans="1:9" ht="135">
-      <c r="A50" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D50" s="4"/>
-      <c r="E50" s="4"/>
-      <c r="F50" s="4"/>
-      <c r="G50" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H50" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I50" s="4"/>
-    </row>
-    <row r="51" spans="1:9" ht="54">
-      <c r="A51" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C51" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D51" s="4"/>
-      <c r="E51" s="4"/>
-      <c r="F51" s="4"/>
-      <c r="G51" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="I51" s="4"/>
-    </row>
-    <row r="52" spans="1:9" ht="54">
-      <c r="A52" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C52" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D52" s="4"/>
-      <c r="E52" s="4"/>
-      <c r="F52" s="4"/>
-      <c r="G52" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H52" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="I52" s="4"/>
-    </row>
-    <row r="53" spans="1:9" ht="168" customHeight="1">
-      <c r="A53" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C53" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D53" s="4"/>
-      <c r="E53" s="4"/>
-      <c r="F53" s="4"/>
-      <c r="G53" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="H53" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="I53" s="4"/>
-    </row>
-    <row r="54" spans="1:9" ht="168" customHeight="1">
-      <c r="A54" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C54" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D54" s="4"/>
-      <c r="E54" s="4"/>
-      <c r="F54" s="4"/>
-      <c r="G54" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="H54" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I54" s="4"/>
-    </row>
-    <row r="55" spans="1:9" ht="54">
-      <c r="A55" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C55" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D55" s="4"/>
-      <c r="E55" s="4"/>
-      <c r="F55" s="4"/>
-      <c r="G55" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H55" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I55" s="4"/>
-    </row>
-    <row r="56" spans="1:9" ht="54">
-      <c r="A56" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="C56" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D56" s="4"/>
-      <c r="E56" s="4"/>
-      <c r="F56" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D56" s="4">
+        <v>1</v>
+      </c>
+      <c r="E56" s="4">
+        <v>1</v>
+      </c>
+      <c r="F56" s="4">
+        <v>1</v>
+      </c>
       <c r="G56" s="2" t="s">
-        <v>189</v>
+        <v>89</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I56" s="4"/>
-    </row>
-    <row r="57" spans="1:9" ht="162">
+        <v>97</v>
+      </c>
+      <c r="I56" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" ht="54">
       <c r="A57" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="B57" s="5" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D57" s="4"/>
-      <c r="E57" s="4"/>
-      <c r="F57" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D57" s="4">
+        <v>1</v>
+      </c>
+      <c r="E57" s="4">
+        <v>1</v>
+      </c>
+      <c r="F57" s="4">
+        <v>1</v>
+      </c>
       <c r="G57" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I57" s="4"/>
+        <v>98</v>
+      </c>
+      <c r="I57" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="58" spans="1:9" ht="54">
       <c r="A58" s="2" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D58" s="4">
+        <v>1</v>
+      </c>
+      <c r="E58" s="4">
+        <v>1</v>
+      </c>
+      <c r="F58" s="4">
+        <v>1</v>
+      </c>
       <c r="G58" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="I58" s="4"/>
-    </row>
-    <row r="59" spans="1:9" ht="54">
+      <c r="I58" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" ht="168" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D59" s="4"/>
-      <c r="E59" s="4"/>
-      <c r="F59" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D59" s="4">
+        <v>1</v>
+      </c>
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+      <c r="F59" s="4">
+        <v>1</v>
+      </c>
       <c r="G59" s="2" t="s">
-        <v>106</v>
+        <v>156</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="I59" s="4"/>
+        <v>99</v>
+      </c>
+      <c r="I59" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="60" spans="1:9" ht="168" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>107</v>
+        <v>247</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D60" s="4"/>
-      <c r="E60" s="4"/>
-      <c r="F60" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D60" s="4">
+        <v>1</v>
+      </c>
+      <c r="E60" s="4">
+        <v>2</v>
+      </c>
+      <c r="F60" s="4">
+        <v>1</v>
+      </c>
       <c r="G60" s="2" t="s">
-        <v>190</v>
+        <v>157</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="I60" s="4"/>
-    </row>
-    <row r="61" spans="1:9" ht="168" customHeight="1">
-      <c r="A61" s="2" t="s">
-        <v>108</v>
+        <v>75</v>
+      </c>
+      <c r="I60" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" ht="67.5">
+      <c r="A61" s="6" t="s">
+        <v>248</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D61" s="4"/>
-      <c r="E61" s="4"/>
-      <c r="F61" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D61" s="4">
+        <v>1</v>
+      </c>
+      <c r="E61" s="4">
+        <v>2</v>
+      </c>
+      <c r="F61" s="4">
+        <v>1</v>
+      </c>
       <c r="G61" s="2" t="s">
-        <v>191</v>
+        <v>249</v>
       </c>
       <c r="H61" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I61" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" ht="54">
+      <c r="A62" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D62" s="4">
+        <v>1</v>
+      </c>
+      <c r="E62" s="4">
+        <v>2</v>
+      </c>
+      <c r="F62" s="4">
+        <v>1</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="I62" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" ht="54">
+      <c r="A63" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="I61" s="4"/>
-    </row>
-    <row r="62" spans="1:9" ht="67.5">
-      <c r="A62" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C62" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D62" s="4"/>
-      <c r="E62" s="4"/>
-      <c r="F62" s="4"/>
-      <c r="G62" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="H62" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I62" s="4"/>
-    </row>
-    <row r="63" spans="1:9" ht="81">
-      <c r="A63" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="C63" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D63" s="4"/>
-      <c r="E63" s="4"/>
-      <c r="F63" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D63" s="4">
+        <v>1</v>
+      </c>
+      <c r="E63" s="4">
+        <v>2</v>
+      </c>
+      <c r="F63" s="4">
+        <v>1</v>
+      </c>
       <c r="G63" s="2" t="s">
-        <v>193</v>
+        <v>159</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I63" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="I63" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="64" spans="1:9" ht="162">
       <c r="A64" s="2" t="s">
-        <v>146</v>
+        <v>104</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D64" s="4"/>
-      <c r="E64" s="4"/>
-      <c r="F64" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D64" s="4">
+        <v>1</v>
+      </c>
+      <c r="E64" s="4">
+        <v>1</v>
+      </c>
+      <c r="F64" s="4">
+        <v>1</v>
+      </c>
       <c r="G64" s="2" t="s">
-        <v>140</v>
+        <v>81</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I64" s="4"/>
+        <v>97</v>
+      </c>
+      <c r="I64" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="65" spans="1:9" ht="54">
       <c r="A65" s="2" t="s">
-        <v>141</v>
+        <v>82</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D65" s="4"/>
-      <c r="E65" s="4"/>
-      <c r="F65" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D65" s="4">
+        <v>1</v>
+      </c>
+      <c r="E65" s="4">
+        <v>1</v>
+      </c>
+      <c r="F65" s="4">
+        <v>1</v>
+      </c>
       <c r="G65" s="2" t="s">
-        <v>142</v>
+        <v>83</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="I65" s="4"/>
-    </row>
-    <row r="66" spans="1:9" ht="168" customHeight="1">
+        <v>98</v>
+      </c>
+      <c r="I65" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="54">
       <c r="A66" s="2" t="s">
-        <v>143</v>
+        <v>84</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D66" s="4"/>
-      <c r="E66" s="4"/>
-      <c r="F66" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D66" s="4">
+        <v>1</v>
+      </c>
+      <c r="E66" s="4">
+        <v>1</v>
+      </c>
+      <c r="F66" s="4">
+        <v>1</v>
+      </c>
       <c r="G66" s="2" t="s">
-        <v>194</v>
+        <v>85</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="I66" s="4"/>
+        <v>122</v>
+      </c>
+      <c r="I66" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="67" spans="1:9" ht="168" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>144</v>
+        <v>86</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D67" s="4"/>
-      <c r="E67" s="4"/>
-      <c r="F67" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D67" s="4">
+        <v>1</v>
+      </c>
+      <c r="E67" s="4">
+        <v>1</v>
+      </c>
+      <c r="F67" s="4">
+        <v>1</v>
+      </c>
       <c r="G67" s="2" t="s">
-        <v>195</v>
+        <v>160</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="I67" s="4"/>
-    </row>
-    <row r="68" spans="1:9" ht="67.5">
+        <v>99</v>
+      </c>
+      <c r="I67" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="168" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>145</v>
+        <v>251</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D68" s="4"/>
-      <c r="E68" s="4"/>
-      <c r="F68" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D68" s="4">
+        <v>1</v>
+      </c>
+      <c r="E68" s="4">
+        <v>2</v>
+      </c>
+      <c r="F68" s="4">
+        <v>1</v>
+      </c>
       <c r="G68" s="2" t="s">
-        <v>241</v>
+        <v>161</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="I68" s="4"/>
-    </row>
-    <row r="69" spans="1:9" ht="121.5">
+        <v>75</v>
+      </c>
+      <c r="I68" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" ht="67.5">
       <c r="A69" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>165</v>
+        <v>252</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D69" s="4"/>
-      <c r="E69" s="4"/>
-      <c r="F69" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D69" s="4">
+        <v>1</v>
+      </c>
+      <c r="E69" s="4">
+        <v>2</v>
+      </c>
+      <c r="F69" s="4">
+        <v>1</v>
+      </c>
       <c r="G69" s="2" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="I69" s="4"/>
-    </row>
-    <row r="70" spans="1:9" ht="162">
+        <v>223</v>
+      </c>
+      <c r="I69" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="67.5">
       <c r="A70" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>240</v>
-      </c>
-      <c r="D70" s="4"/>
-      <c r="E70" s="4"/>
-      <c r="F70" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D70" s="4">
+        <v>1</v>
+      </c>
+      <c r="E70" s="4">
+        <v>2</v>
+      </c>
+      <c r="F70" s="4">
+        <v>1</v>
+      </c>
       <c r="G70" s="2" t="s">
-        <v>242</v>
+        <v>162</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="I70" s="4"/>
-    </row>
-    <row r="71" spans="1:9" ht="54">
-      <c r="A71" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="D71" s="4"/>
-      <c r="E71" s="4"/>
-      <c r="F71" s="4"/>
+        <v>258</v>
+      </c>
+      <c r="I70" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="81">
+      <c r="A71" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D71" s="4">
+        <v>1</v>
+      </c>
+      <c r="E71" s="4">
+        <v>2</v>
+      </c>
+      <c r="F71" s="4">
+        <v>1</v>
+      </c>
       <c r="G71" s="2" t="s">
-        <v>244</v>
+        <v>163</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="I71" s="4"/>
-    </row>
-    <row r="72" spans="1:9" ht="67.5">
+        <v>30</v>
+      </c>
+      <c r="I71" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" ht="162">
       <c r="A72" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="B72" s="2"/>
+        <v>119</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>125</v>
+      </c>
       <c r="C72" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D72" s="4">
+        <v>1</v>
+      </c>
+      <c r="E72" s="4">
+        <v>1</v>
+      </c>
+      <c r="F72" s="4">
+        <v>1</v>
+      </c>
       <c r="G72" s="2" t="s">
-        <v>213</v>
+        <v>114</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="I72" s="4"/>
-    </row>
-    <row r="73" spans="1:9" ht="135">
+        <v>120</v>
+      </c>
+      <c r="I72" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" ht="54">
       <c r="A73" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D73" s="4">
+        <v>1</v>
+      </c>
+      <c r="E73" s="4">
+        <v>1</v>
+      </c>
+      <c r="F73" s="4">
+        <v>1</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H73" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I73" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="168" customHeight="1">
+      <c r="A74" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D74" s="4">
+        <v>1</v>
+      </c>
+      <c r="E74" s="4">
+        <v>1</v>
+      </c>
+      <c r="F74" s="4">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I74" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="168" customHeight="1">
+      <c r="A75" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D75" s="4">
+        <v>1</v>
+      </c>
+      <c r="E75" s="4">
+        <v>2</v>
+      </c>
+      <c r="F75" s="4">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="H75" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I75" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="67.5">
+      <c r="A76" s="6" t="s">
+        <v>255</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D76" s="4">
+        <v>1</v>
+      </c>
+      <c r="E76" s="4">
+        <v>2</v>
+      </c>
+      <c r="F76" s="4">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="I76" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="67.5">
+      <c r="A77" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D77" s="4">
+        <v>1</v>
+      </c>
+      <c r="E77" s="4">
+        <v>2</v>
+      </c>
+      <c r="F77" s="4">
+        <v>1</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H77" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I77" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="121.5">
+      <c r="A78" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D78" s="4">
+        <v>1</v>
+      </c>
+      <c r="E78" s="4">
+        <v>1</v>
+      </c>
+      <c r="F78" s="4">
+        <v>1</v>
+      </c>
+      <c r="G78" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="B73" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D73" s="4"/>
-      <c r="E73" s="4"/>
-      <c r="F73" s="4"/>
-      <c r="G73" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="H73" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="I73" s="4"/>
-    </row>
-    <row r="74" spans="1:9" ht="67.5">
-      <c r="A74" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C74" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="4"/>
-      <c r="G74" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="H74" s="2" t="s">
+      <c r="H78" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="I74" s="4"/>
-    </row>
-    <row r="75" spans="1:9" ht="121.5">
-      <c r="A75" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C75" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D75" s="4"/>
-      <c r="E75" s="4"/>
-      <c r="F75" s="4"/>
-      <c r="G75" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="H75" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="I75" s="4"/>
-    </row>
-    <row r="76" spans="1:9" ht="67.5">
-      <c r="A76" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D76" s="4">
-        <v>1</v>
-      </c>
-      <c r="E76" s="4"/>
-      <c r="F76" s="4"/>
-      <c r="G76" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H76" s="2"/>
-      <c r="I76" s="4"/>
-    </row>
-    <row r="77" spans="1:9" ht="121.5">
-      <c r="A77" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="B77" s="5" t="s">
+      <c r="I78" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="162">
+      <c r="A79" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D79" s="4">
+        <v>1</v>
+      </c>
+      <c r="E79" s="4">
+        <v>1</v>
+      </c>
+      <c r="F79" s="4">
+        <v>1</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="H79" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="C77" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D77" s="4"/>
-      <c r="E77" s="4"/>
-      <c r="F77" s="4"/>
-      <c r="G77" s="2" t="s">
+      <c r="I79" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="54">
+      <c r="A80" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="H77" s="2" t="s">
+      <c r="B80" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="I77" s="4"/>
-    </row>
-    <row r="78" spans="1:9" ht="54">
-      <c r="A78" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="C78" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D78" s="4"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="I78" s="4"/>
-    </row>
-    <row r="79" spans="1:9" ht="67.5">
-      <c r="A79" s="2" t="s">
+      <c r="C80" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D80" s="4">
+        <v>1</v>
+      </c>
+      <c r="E80" s="4">
+        <v>2</v>
+      </c>
+      <c r="F80" s="4">
+        <v>1</v>
+      </c>
+      <c r="G80" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="C79" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D79" s="4">
-        <v>1</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="80" spans="1:9" ht="121.5">
-      <c r="A80" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="C80" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D80" s="4"/>
-      <c r="E80" s="4"/>
-      <c r="F80" s="4"/>
-      <c r="G80" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="H80" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="I80" s="4"/>
-    </row>
-    <row r="81" spans="1:9" ht="54">
+        <v>212</v>
+      </c>
+      <c r="I80" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" ht="67.5">
       <c r="A81" s="2" t="s">
-        <v>222</v>
-      </c>
+        <v>166</v>
+      </c>
+      <c r="B81" s="2"/>
       <c r="C81" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D81" s="4">
+        <v>1</v>
+      </c>
+      <c r="E81" s="4">
+        <v>2</v>
+      </c>
+      <c r="F81" s="4">
+        <v>1</v>
+      </c>
       <c r="G81" s="2" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="I81" s="4"/>
-    </row>
-    <row r="82" spans="1:9" ht="121.5">
+        <v>167</v>
+      </c>
+      <c r="I81" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" ht="135">
       <c r="A82" s="2" t="s">
-        <v>209</v>
+        <v>170</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>212</v>
+        <v>168</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D82" s="4">
         <v>1</v>
       </c>
+      <c r="E82" s="4">
+        <v>1</v>
+      </c>
+      <c r="F82" s="4">
+        <v>1</v>
+      </c>
       <c r="G82" s="2" t="s">
-        <v>219</v>
+        <v>183</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>220</v>
+        <v>184</v>
+      </c>
+      <c r="I82" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:9" ht="67.5">
       <c r="A83" s="2" t="s">
-        <v>224</v>
+        <v>169</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="D83" s="4">
         <v>1</v>
       </c>
-      <c r="E83" s="4"/>
-      <c r="F83" s="4"/>
+      <c r="E83" s="4">
+        <v>1</v>
+      </c>
+      <c r="F83" s="4">
+        <v>1</v>
+      </c>
       <c r="G83" s="2" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="I83" s="4"/>
-    </row>
-    <row r="84" spans="1:9" ht="67.5">
+        <v>171</v>
+      </c>
+      <c r="I83" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" ht="121.5">
       <c r="A84" s="2" t="s">
-        <v>226</v>
+        <v>26</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="D84" s="4">
         <v>1</v>
       </c>
-      <c r="E84" s="4"/>
-      <c r="F84" s="4"/>
+      <c r="E84" s="4">
+        <v>2</v>
+      </c>
+      <c r="F84" s="4">
+        <v>1</v>
+      </c>
       <c r="G84" s="2" t="s">
-        <v>227</v>
+        <v>186</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="I84" s="4"/>
-    </row>
-    <row r="85" spans="1:9" ht="94.5">
+        <v>172</v>
+      </c>
+      <c r="I84" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" ht="67.5">
       <c r="A85" s="2" t="s">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>232</v>
+        <v>18</v>
       </c>
       <c r="D85" s="4">
         <v>1</v>
       </c>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
+      <c r="E85" s="4">
+        <v>2</v>
+      </c>
+      <c r="F85" s="4">
+        <v>1</v>
+      </c>
       <c r="G85" s="2" t="s">
-        <v>229</v>
+        <v>53</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="I85" s="4"/>
+        <v>259</v>
+      </c>
+      <c r="I85" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" ht="121.5">
+      <c r="A86" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D86" s="4">
+        <v>1</v>
+      </c>
+      <c r="E86" s="4">
+        <v>1</v>
+      </c>
+      <c r="F86" s="4">
+        <v>1</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I86" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" ht="54">
+      <c r="A87" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D87" s="4">
+        <v>1</v>
+      </c>
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+      <c r="F87" s="4">
+        <v>1</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I87" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" ht="67.5">
+      <c r="A88" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D88" s="4">
+        <v>1</v>
+      </c>
+      <c r="E88" s="4">
+        <v>1</v>
+      </c>
+      <c r="F88" s="4">
+        <v>1</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="I88" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" ht="121.5">
+      <c r="A89" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D89" s="4">
+        <v>1</v>
+      </c>
+      <c r="E89" s="4">
+        <v>1</v>
+      </c>
+      <c r="F89" s="4">
+        <v>1</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I89" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" ht="54">
+      <c r="A90" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D90" s="4">
+        <v>1</v>
+      </c>
+      <c r="E90" s="4">
+        <v>1</v>
+      </c>
+      <c r="F90" s="4">
+        <v>1</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="I90" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" ht="67.5">
+      <c r="A91" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D91" s="4">
+        <v>1</v>
+      </c>
+      <c r="E91" s="4">
+        <v>1</v>
+      </c>
+      <c r="F91" s="4">
+        <v>1</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="I91" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" ht="67.5">
+      <c r="A92" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D92" s="4">
+        <v>1</v>
+      </c>
+      <c r="E92" s="4">
+        <v>2</v>
+      </c>
+      <c r="F92" s="4">
+        <v>1</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I92" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" ht="67.5">
+      <c r="A93" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D93" s="4">
+        <v>1</v>
+      </c>
+      <c r="E93" s="4">
+        <v>2</v>
+      </c>
+      <c r="F93" s="4">
+        <v>1</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I93" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" ht="94.5">
+      <c r="A94" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D94" s="4">
+        <v>1</v>
+      </c>
+      <c r="E94" s="4">
+        <v>2</v>
+      </c>
+      <c r="F94" s="4">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I94" s="4">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
@@ -10,7 +10,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -94,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="261">
   <si>
     <t>name</t>
   </si>
@@ -169,27 +168,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，rule指定的字段名不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新失败，提示参数错误，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，rule为空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，rule更新符错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，格式错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，修改唯一索引的值重复</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -218,43 +197,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，$inc指定的字段跟原字段数据类型不一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$inc取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$set指定的字段名不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，覆盖$set字段值无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$set指定的字段跟原字段数据类型不一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新成功，指定的字段名和字段值在集合中被删除</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、更新成功，指定的字段名在记录中不存在则跳过不更新，跳过后往下继续更新</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$unset取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$addtose指定的字段名存在但字段值不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$addtose指定的字段名不存在</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -371,22 +318,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，覆盖$addtose字段值有效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，覆盖$addtose字段值无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$addtose指定的字段跟原字段数据类型不一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，覆盖$pop字段值有效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新成功，根据指定的字段名和值删除指定个数的数据删除正确，即：
 指定值为-1，则删除数组中第一个值；
 指定值为0，则不删除任何值；
@@ -400,40 +331,16 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，$pop指定字段名的值等于该数组内字段值总个数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$pop指定字段名的值大于该数组内字段值总个数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$pop取值非法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$pull更新数据，$pull指定的字段名和字段值存在
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，$pull指定的字段名存在但字段值不存在</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$pull更新数据，$pull指定的字段名存在但字段值不存在
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，$pull指定的字段名不存在</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$pull更新数据，$pull指定的字段名不存在
 2、检查更新结果</t>
-  </si>
-  <si>
-    <t>update，覆盖$pull字段值有效取值</t>
-  </si>
-  <si>
-    <t>update，$pull指定的字段跟原字段数据类型不一致</t>
   </si>
   <si>
     <t>1、更新失败，提示数值超出边界
@@ -441,78 +348,28 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，$addtose指定的字段名非数组对象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$pull指定的字段名和字段值存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$pop指定的字段名非数组对象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$pull取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$pull指定的字段名非数组对象</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$push_all更新数据，$push_all指定的字段名和字段值存在
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，$push_all指定的字段名存在但字段值不存在</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$push_all更新数据，$push_all指定的字段名存在但字段值不存在
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，$push_all指定的字段名不存在</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$push_all更新数据，$push_all指定的字段名不存在
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，覆盖$push_all字段值有效取值</t>
-  </si>
-  <si>
-    <t>update，$push_all指定的字段名非数组对象</t>
-  </si>
-  <si>
-    <t>update，$push指定的字段名和字段值存在</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$push更新数据，$push指定的字段名和字段值存在
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，$push指定的字段名存在但字段值不存在</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$push更新数据，$push指定的字段名存在但字段值不存在
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，$push指定的字段名不存在</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$push更新数据，$push指定的字段名不存在
 2、检查更新结果</t>
-  </si>
-  <si>
-    <t>update，覆盖$push字段值有效取值</t>
-  </si>
-  <si>
-    <t>update，$push指定的字段跟原字段数据类型不一致</t>
-  </si>
-  <si>
-    <t>update，$push指定的字段名非数组对象</t>
   </si>
   <si>
     <t>1、更新成功，存在指定的字段名和数值，指定的数值也会插入
@@ -550,58 +407,24 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，$push_all指定的字段名和字段值存在</t>
-  </si>
-  <si>
-    <t>update，$pull_all指定的字段名和字段值存在</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$pull_all更新数据，$pull_all指定的字段名和字段值存在
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，$pull_all指定的字段名存在但字段值不存在</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$pull_all更新数据，$pull_all指定的字段名存在但字段值不存在
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，$pull_all指定的字段名不存在</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$pull_all更新数据，$pull_all指定的字段名不存在
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，覆盖$pull_all字段值有效取值</t>
-  </si>
-  <si>
-    <t>update，$pull_all指定的字段跟原字段数据类型不一致</t>
-  </si>
-  <si>
-    <t>update，$pull_all指定的字段名非数组对象</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$replace更新数据，$replace指定的字段名和字段值存在
 2、检查更新结果</t>
   </si>
   <si>
-    <t>update，$replace指定的字段名不存在</t>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$replace更新数据，$replace指定的字段名不存在
 2、检查更新结果</t>
-  </si>
-  <si>
-    <t>update，覆盖$replace字段值有效取值</t>
-  </si>
-  <si>
-    <t>update，$replace指定的字段跟原字段数据类型不一致</t>
-  </si>
-  <si>
-    <t>update，$replace指定的字段名存在</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>1、更新成功，指定的字段名存在则直接替换为指定的值
@@ -647,10 +470,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，$pop取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>语法：
 {&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
 语法：{$replace:{&lt;字段名1&gt;:&lt;值1&gt;,&lt;字段名2&gt;:&lt;值2&gt;,...}}
@@ -683,10 +502,6 @@
 更新符：$pull，清除指定数组对象的指定值。操作对象必须为数组类型的字段。
 如果记录中不存在指定的数组对象，跳过不做任何操作；如果指定的值不存在数组对象中，也不做任何操作。</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$addtose指定的字段名和字段值存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、更新成功，字段名存在值也存在，则跳过不添加，其他指定字段更新成功
@@ -1038,10 +853,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，cond指定的字段名不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>更新失败，提示字段不存在，提示信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1052,14 +863,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，hint指定的字段值为null</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，hint指定的字段值为需要访问索引的名称</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>更新成功，遍历所有的记录更新，记录更新正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1077,18 +880,6 @@
   </si>
   <si>
     <t>同update</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upsert，指定无效的字段名和字段值更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>upsert，指定有效的字段名和字段值更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query.update，returnNew指定为true</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1098,10 +889,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>upsert，cond指定的字段名不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>格式：query.update(&lt;update&gt;,[returnNew])
 update：Json对象，更新规则。记录按update的内容更新。必填
 returnNew： bool，是否返回更新后的记录。非必填</t>
@@ -1149,19 +936,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>query.update，指定有效的字段名和字段值更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query.update，指定无效的字段名和字段值更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>同update，跟update交叉测试即可</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query.update，returnNew指定为false</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1171,17 +946,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>query.update，returnNew取值非法</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，query.update更新CL指定数据，returnNew取值非法，如：
 db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:test)
 2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>query.update，returnNew取值为空</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1206,18 +973,6 @@
   </si>
   <si>
     <t>更新成功，使用匹配符匹配数据正确，数据更新正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，cond指定匹配符更新数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，cond指定正确的"$+标识符"匹配数据</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，cond指定错误的"$+标识符"匹配数据</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1255,10 +1010,6 @@
   </si>
   <si>
     <t>更新失败，提示参数错误，提示信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，rule配置正确更新数据</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1345,14 +1096,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，覆盖$inc字段值有效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$inc指定更新的字段名不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，指定$inc更新符更新数据，对应的字段名不存在，如：
 {$inc:{&lt;字段名1&gt;:&lt;值1&gt;}，其中&lt;字段名1&gt;不存在
 2、检查更新结果</t>
@@ -1361,41 +1104,6 @@
   <si>
     <t>更新失败，提示分区键字段不能更新，提示信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，覆盖$set字段值有效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$unset指定的部分字段名不存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$inc指定更新的字段为分区键字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$set指定更新的字段为分区键字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$unset指定的字段名存在</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$unset指定更新的字段为分区键字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$addtose指定更新的字段为分区键字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$pop指定更新的字段为分区键字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，rule指定更新的字段为分区键字段</t>
   </si>
   <si>
     <t>1、进入sdb，update更新CL指定数据，rule指定更新的字段为分区键字段，如：
@@ -1441,25 +1149,9 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，覆盖$pull字段值无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$pull指定更新的字段为分区键字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL中数据，指定$pull更新符更新数据，数据为空，如：
 {$pull:{&lt;字段名1&gt;:}}  或  {$pull:{"":""}}
 2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，覆盖$pull_all字段值无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$pull_all字指定更新的字段为分区键字段</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1477,14 +1169,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，覆盖$push字段值无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$push字指定更新的字段为分区键字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，$push字指定更新的字段为分区键字段，如：
 {$push:&lt;字段名1&gt;:[&lt;值1&gt;}}
 ---其中"字段名1"为分区键字段
@@ -1492,18 +1176,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，$push_all指定的字段跟原字段数据类型不一致</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，覆盖$push_all字段值无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$push_all字指定更新的字段为分区键字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，$push_all字指定更新的字段为分区键字段，如：
 {$push_all:&lt;字段名1&gt;:[&lt;值1&gt;}}
 ---其中"字段名1"为分区键字段
@@ -1511,14 +1183,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，覆盖$replace字段值无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>update，$replace字指定更新的字段为分区键字段</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，update更新CL指定数据，$replace字指定更新的字段为分区键字段，如：
 {$replace:&lt;字段名1&gt;:[&lt;值1&gt;}}
 ---其中"字段名1"为分区键字段
@@ -1526,15 +1190,287 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>update，$inc字段值类型超出边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>更新失败，提示参数错误，提示信息合理准确</t>
   </si>
   <si>
     <t>更新失败，提示参数错误，提示信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>update，rule配置正确更新数据_st.verify.update.001</t>
+  </si>
+  <si>
+    <t>update，rule指定更新的字段为分区键字段_st.verify.update.002</t>
+  </si>
+  <si>
+    <t>update，rule指定的字段名不存在_st.verify.update.003</t>
+  </si>
+  <si>
+    <t>update，rule更新符错误_st.verify.update.004</t>
+  </si>
+  <si>
+    <t>update，rule为空串_st.verify.update.005</t>
+  </si>
+  <si>
+    <t>update，覆盖$inc字段值有效取值_st.verify.update.006</t>
+  </si>
+  <si>
+    <t>update，$inc指定更新的字段为分区键字段_st.verify.update.007</t>
+  </si>
+  <si>
+    <t>update，$inc指定更新的字段名不存在_st.verify.update.008</t>
+  </si>
+  <si>
+    <t>update，$inc字段值类型超出边界_st.verify.update.009</t>
+  </si>
+  <si>
+    <t>update，$inc指定的字段跟原字段数据类型不一致_st.verify.update.010</t>
+  </si>
+  <si>
+    <t>update，$inc取值为空_st.verify.update.011</t>
+  </si>
+  <si>
+    <t>update，覆盖$set字段值有效取值_st.verify.update.012</t>
+  </si>
+  <si>
+    <t>update，$set指定更新的字段为分区键字段_st.verify.update.013</t>
+  </si>
+  <si>
+    <t>update，$set指定的字段名不存在_st.verify.update.014</t>
+  </si>
+  <si>
+    <t>update，覆盖$set字段值无效取值_st.verify.update.015</t>
+  </si>
+  <si>
+    <t>update，$set指定的字段跟原字段数据类型不一致_st.verify.update.016</t>
+  </si>
+  <si>
+    <t>update，$unset指定的字段名存在_st.verify.update.017</t>
+  </si>
+  <si>
+    <t>update，$unset指定更新的字段为分区键字段_st.verify.update.018</t>
+  </si>
+  <si>
+    <t>update，$unset指定的部分字段名不存在_st.verify.update.019</t>
+  </si>
+  <si>
+    <t>update，$unset取值为空_st.verify.update.020</t>
+  </si>
+  <si>
+    <t>update，$addtose指定的字段名和字段值存在_st.verify.update.021</t>
+  </si>
+  <si>
+    <t>update，$addtose指定的字段名存在但字段值不存在_st.verify.update.022</t>
+  </si>
+  <si>
+    <t>update，$addtose指定的字段名不存在_st.verify.update.023</t>
+  </si>
+  <si>
+    <t>update，$addtose指定更新的字段为分区键字段_st.verify.update.024</t>
+  </si>
+  <si>
+    <t>update，覆盖$addtose字段值有效取值_st.verify.update.025</t>
+  </si>
+  <si>
+    <t>update，$addtose指定的字段名不存在_st.verify.update.026</t>
+  </si>
+  <si>
+    <t>update，覆盖$addtose字段值无效取值_st.verify.update.027</t>
+  </si>
+  <si>
+    <t>update，$addtose指定的字段跟原字段数据类型不一致_st.verify.update.028</t>
+  </si>
+  <si>
+    <t>update，$addtose指定的字段名非数组对象_st.verify.update.029</t>
+  </si>
+  <si>
+    <t>update，覆盖$pop字段值有效取值_st.verify.update.030</t>
+  </si>
+  <si>
+    <t>update，$pop指定字段名的值等于该数组内字段值总个数_st.verify.update.031</t>
+  </si>
+  <si>
+    <t>update，$pop指定字段名的值大于该数组内字段值总个数_st.verify.update.032</t>
+  </si>
+  <si>
+    <t>update，$pop指定更新的字段为分区键字段_st.verify.update.033</t>
+  </si>
+  <si>
+    <t>update，$pop取值为空_st.verify.update.034</t>
+  </si>
+  <si>
+    <t>update，$pop取值非法_st.verify.update.035</t>
+  </si>
+  <si>
+    <t>update，$pop指定的字段名非数组对象_st.verify.update.036</t>
+  </si>
+  <si>
+    <t>update，$pull指定的字段名和字段值存在_st.verify.update.037</t>
+  </si>
+  <si>
+    <t>update，$pull指定的字段名存在但字段值不存在_st.verify.update.038</t>
+  </si>
+  <si>
+    <t>update，$pull指定的字段名不存在_st.verify.update.039</t>
+  </si>
+  <si>
+    <t>update，覆盖$pull字段值有效取值_st.verify.update.040</t>
+  </si>
+  <si>
+    <t>update，覆盖$pull字段值无效取值_st.verify.update.041</t>
+  </si>
+  <si>
+    <t>update，$pull指定更新的字段为分区键字段_st.verify.update.042</t>
+  </si>
+  <si>
+    <t>update，$pull指定的字段跟原字段数据类型不一致_st.verify.update.043</t>
+  </si>
+  <si>
+    <t>update，$pull取值为空_st.verify.update.044</t>
+  </si>
+  <si>
+    <t>update，$pull指定的字段名非数组对象_st.verify.update.045</t>
+  </si>
+  <si>
+    <t>update，$pull_all指定的字段名和字段值存在_st.verify.update.046</t>
+  </si>
+  <si>
+    <t>update，$pull_all指定的字段名存在但字段值不存在_st.verify.update.047</t>
+  </si>
+  <si>
+    <t>update，$pull_all指定的字段名不存在_st.verify.update.048</t>
+  </si>
+  <si>
+    <t>update，覆盖$pull_all字段值有效取值_st.verify.update.049</t>
+  </si>
+  <si>
+    <t>update，覆盖$pull_all字段值无效取值_st.verify.update.050</t>
+  </si>
+  <si>
+    <t>update，$pull_all字指定更新的字段为分区键字段_st.verify.update.051</t>
+  </si>
+  <si>
+    <t>update，$pull_all指定的字段跟原字段数据类型不一致_st.verify.update.052</t>
+  </si>
+  <si>
+    <t>update，$pull_all指定的字段名非数组对象_st.verify.update.053</t>
+  </si>
+  <si>
+    <t>update，$push指定的字段名和字段值存在_st.verify.update.054</t>
+  </si>
+  <si>
+    <t>update，$push指定的字段名存在但字段值不存在_st.verify.update.055</t>
+  </si>
+  <si>
+    <t>update，$push指定的字段名不存在_st.verify.update.056</t>
+  </si>
+  <si>
+    <t>update，覆盖$push字段值有效取值_st.verify.update.057</t>
+  </si>
+  <si>
+    <t>update，覆盖$push字段值无效取值_st.verify.update.058</t>
+  </si>
+  <si>
+    <t>update，$push字指定更新的字段为分区键字段_st.verify.update.059</t>
+  </si>
+  <si>
+    <t>update，$push指定的字段跟原字段数据类型不一致_st.verify.update.060</t>
+  </si>
+  <si>
+    <t>update，$push指定的字段名非数组对象_st.verify.update.061</t>
+  </si>
+  <si>
+    <t>update，$push_all指定的字段名和字段值存在_st.verify.update.062</t>
+  </si>
+  <si>
+    <t>update，$push_all指定的字段名存在但字段值不存在_st.verify.update.063</t>
+  </si>
+  <si>
+    <t>update，$push_all指定的字段名不存在_st.verify.update.064</t>
+  </si>
+  <si>
+    <t>update，覆盖$push_all字段值有效取值_st.verify.update.065</t>
+  </si>
+  <si>
+    <t>update，覆盖$push_all字段值无效取值_st.verify.update.066</t>
+  </si>
+  <si>
+    <t>update，$push_all字指定更新的字段为分区键字段_st.verify.update.067</t>
+  </si>
+  <si>
+    <t>update，$push_all指定的字段跟原字段数据类型不一致_st.verify.update.068</t>
+  </si>
+  <si>
+    <t>update，$push_all指定的字段名非数组对象_st.verify.update.069</t>
+  </si>
+  <si>
+    <t>update，$replace指定的字段名存在_st.verify.update.070</t>
+  </si>
+  <si>
+    <t>update，$replace指定的字段名不存在_st.verify.update.071</t>
+  </si>
+  <si>
+    <t>update，覆盖$replace字段值有效取值_st.verify.update.072</t>
+  </si>
+  <si>
+    <t>update，覆盖$replace字段值无效取值_st.verify.update.073</t>
+  </si>
+  <si>
+    <t>update，$replace字指定更新的字段为分区键字段_st.verify.update.074</t>
+  </si>
+  <si>
+    <t>update，$replace指定的字段跟原字段数据类型不一致_st.verify.update.075</t>
+  </si>
+  <si>
+    <t>update，cond指定匹配符更新数据_st.verify.update.076</t>
+  </si>
+  <si>
+    <t>update，cond指定正确的"$+标识符"匹配数据_st.verify.update.077</t>
+  </si>
+  <si>
+    <t>update，cond指定错误的"$+标识符"匹配数据_st.verify.update.078</t>
+  </si>
+  <si>
+    <t>update，cond指定的字段名不存在_st.verify.update.079</t>
+  </si>
+  <si>
+    <t>update，hint指定的字段值为需要访问索引的名称_st.verify.update.080</t>
+  </si>
+  <si>
+    <t>update，hint指定的字段值为null_st.verify.update.081</t>
+  </si>
+  <si>
+    <t>update，修改唯一索引的值重复_st.verify.update.082</t>
+  </si>
+  <si>
+    <t>update，格式错误_st.verify.update.083</t>
+  </si>
+  <si>
+    <t>upsert，指定有效的字段名和字段值更新数据_st.verify.update.084</t>
+  </si>
+  <si>
+    <t>upsert，指定无效的字段名和字段值更新数据_st.verify.update.085</t>
+  </si>
+  <si>
+    <t>upsert，cond指定的字段名不存在_st.verify.update.086</t>
+  </si>
+  <si>
+    <t>query.update，指定有效的字段名和字段值更新数据_st.verify.update.087</t>
+  </si>
+  <si>
+    <t>query.update，指定无效的字段名和字段值更新数据_st.verify.update.088</t>
+  </si>
+  <si>
+    <t>query.update，returnNew指定为true_st.verify.update.089</t>
+  </si>
+  <si>
+    <t>query.update，returnNew指定为false_st.verify.update.090</t>
+  </si>
+  <si>
+    <t>query.update，returnNew取值非法_st.verify.update.091</t>
+  </si>
+  <si>
+    <t>query.update，returnNew取值为空_st.verify.update.092</t>
   </si>
 </sst>
 </file>
@@ -2048,7 +1984,7 @@
   <dimension ref="A1:I94"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="33.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.875" style="5" customWidth="1"/>
     <col min="3" max="3" width="25.75" style="1" customWidth="1"/>
     <col min="4" max="6" width="5" style="1" customWidth="1"/>
@@ -2118,10 +2054,10 @@
     </row>
     <row r="3" spans="1:9" ht="175.5">
       <c r="A3" s="2" t="s">
-        <v>213</v>
+        <v>169</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>219</v>
+        <v>151</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
@@ -2136,7 +2072,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>214</v>
+        <v>146</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>19</v>
@@ -2147,7 +2083,7 @@
     </row>
     <row r="4" spans="1:9" ht="81">
       <c r="A4" s="2" t="s">
-        <v>232</v>
+        <v>170</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
@@ -2162,7 +2098,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>233</v>
+        <v>154</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>20</v>
@@ -2173,7 +2109,7 @@
     </row>
     <row r="5" spans="1:9" ht="81">
       <c r="A5" s="2" t="s">
-        <v>21</v>
+        <v>171</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
@@ -2188,10 +2124,10 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>234</v>
+        <v>155</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>165</v>
+        <v>113</v>
       </c>
       <c r="I5" s="4">
         <v>1</v>
@@ -2199,7 +2135,7 @@
     </row>
     <row r="6" spans="1:9" ht="54">
       <c r="A6" s="2" t="s">
-        <v>24</v>
+        <v>172</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
@@ -2214,10 +2150,10 @@
         <v>1</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I6" s="4">
         <v>1</v>
@@ -2225,7 +2161,7 @@
     </row>
     <row r="7" spans="1:9" ht="67.5">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>173</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>18</v>
@@ -2240,10 +2176,10 @@
         <v>1</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I7" s="4">
         <v>1</v>
@@ -2251,10 +2187,10 @@
     </row>
     <row r="8" spans="1:9" ht="168" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>220</v>
+        <v>174</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>18</v>
@@ -2269,10 +2205,10 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>215</v>
+        <v>147</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I8" s="4">
         <v>1</v>
@@ -2280,7 +2216,7 @@
     </row>
     <row r="9" spans="1:9" ht="67.5">
       <c r="A9" s="2" t="s">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
@@ -2295,10 +2231,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>235</v>
+        <v>156</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -2306,7 +2242,7 @@
     </row>
     <row r="10" spans="1:9" ht="67.5">
       <c r="A10" s="2" t="s">
-        <v>221</v>
+        <v>176</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -2321,10 +2257,10 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>222</v>
+        <v>152</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I10" s="4">
         <v>1</v>
@@ -2332,7 +2268,7 @@
     </row>
     <row r="11" spans="1:9" ht="168" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>257</v>
+        <v>177</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
@@ -2347,10 +2283,10 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>216</v>
+        <v>148</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I11" s="4">
         <v>1</v>
@@ -2358,7 +2294,7 @@
     </row>
     <row r="12" spans="1:9" ht="67.5">
       <c r="A12" s="2" t="s">
-        <v>32</v>
+        <v>178</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>18</v>
@@ -2373,10 +2309,10 @@
         <v>1</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>259</v>
+        <v>168</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
@@ -2384,7 +2320,7 @@
     </row>
     <row r="13" spans="1:9" ht="54">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>179</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>18</v>
@@ -2399,10 +2335,10 @@
         <v>1</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I13" s="4">
         <v>1</v>
@@ -2410,10 +2346,10 @@
     </row>
     <row r="14" spans="1:9" ht="168" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>224</v>
+        <v>180</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>132</v>
+        <v>80</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>18</v>
@@ -2428,10 +2364,10 @@
         <v>1</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="I14" s="4">
         <v>1</v>
@@ -2439,7 +2375,7 @@
     </row>
     <row r="15" spans="1:9" ht="67.5">
       <c r="A15" s="2" t="s">
-        <v>227</v>
+        <v>181</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>18</v>
@@ -2454,10 +2390,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>236</v>
+        <v>157</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
@@ -2465,25 +2401,25 @@
     </row>
     <row r="16" spans="1:9" ht="67.5">
       <c r="A16" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" s="4">
+        <v>1</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D16" s="4">
-        <v>1</v>
-      </c>
-      <c r="E16" s="4">
-        <v>1</v>
-      </c>
-      <c r="F16" s="4">
-        <v>1</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="H16" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I16" s="4">
         <v>1</v>
@@ -2491,25 +2427,25 @@
     </row>
     <row r="17" spans="1:9" ht="168" customHeight="1">
       <c r="A17" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="4">
+        <v>1</v>
+      </c>
+      <c r="E17" s="4">
+        <v>2</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="4">
-        <v>2</v>
-      </c>
-      <c r="F17" s="4">
-        <v>1</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>48</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I17" s="4">
         <v>1</v>
@@ -2517,25 +2453,25 @@
     </row>
     <row r="18" spans="1:9" ht="67.5">
       <c r="A18" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="4">
+        <v>1</v>
+      </c>
+      <c r="E18" s="4">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D18" s="4">
-        <v>1</v>
-      </c>
-      <c r="E18" s="4">
-        <v>2</v>
-      </c>
-      <c r="F18" s="4">
-        <v>1</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>258</v>
+        <v>167</v>
       </c>
       <c r="I18" s="4">
         <v>1</v>
@@ -2543,10 +2479,10 @@
     </row>
     <row r="19" spans="1:9" ht="94.5">
       <c r="A19" s="2" t="s">
-        <v>228</v>
+        <v>185</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>217</v>
+        <v>149</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>18</v>
@@ -2561,10 +2497,10 @@
         <v>1</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="I19" s="4">
         <v>1</v>
@@ -2572,7 +2508,7 @@
     </row>
     <row r="20" spans="1:9" ht="67.5">
       <c r="A20" s="2" t="s">
-        <v>229</v>
+        <v>186</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>18</v>
@@ -2587,10 +2523,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>237</v>
+        <v>158</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -2598,7 +2534,7 @@
     </row>
     <row r="21" spans="1:9" ht="67.5">
       <c r="A21" s="2" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>18</v>
@@ -2613,10 +2549,10 @@
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="I21" s="4">
         <v>1</v>
@@ -2624,25 +2560,25 @@
     </row>
     <row r="22" spans="1:9" ht="54">
       <c r="A22" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="E22" s="4">
+        <v>2</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="E22" s="4">
-        <v>2</v>
-      </c>
-      <c r="F22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I22" s="4">
         <v>1</v>
@@ -2650,10 +2586,10 @@
     </row>
     <row r="23" spans="1:9" ht="162">
       <c r="A23" s="2" t="s">
-        <v>130</v>
+        <v>189</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>133</v>
+        <v>81</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>18</v>
@@ -2668,10 +2604,10 @@
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
       <c r="I23" s="4">
         <v>1</v>
@@ -2679,7 +2615,7 @@
     </row>
     <row r="24" spans="1:9" ht="54">
       <c r="A24" s="2" t="s">
-        <v>40</v>
+        <v>190</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>18</v>
@@ -2694,10 +2630,10 @@
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="I24" s="4">
         <v>1</v>
@@ -2705,7 +2641,7 @@
     </row>
     <row r="25" spans="1:9" ht="54">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>191</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>18</v>
@@ -2720,10 +2656,10 @@
         <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="I25" s="4">
         <v>1</v>
@@ -2731,7 +2667,7 @@
     </row>
     <row r="26" spans="1:9" ht="67.5">
       <c r="A26" s="6" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>18</v>
@@ -2746,10 +2682,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>238</v>
+        <v>159</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="I26" s="4">
         <v>1</v>
@@ -2757,7 +2693,7 @@
     </row>
     <row r="27" spans="1:9" ht="168" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>59</v>
+        <v>193</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>18</v>
@@ -2772,10 +2708,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I27" s="4">
         <v>1</v>
@@ -2783,7 +2719,7 @@
     </row>
     <row r="28" spans="1:9" ht="67.5">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>194</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>18</v>
@@ -2798,10 +2734,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="I28" s="4">
         <v>1</v>
@@ -2809,7 +2745,7 @@
     </row>
     <row r="29" spans="1:9" ht="168" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>60</v>
+        <v>195</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>18</v>
@@ -2824,10 +2760,10 @@
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
@@ -2835,7 +2771,7 @@
     </row>
     <row r="30" spans="1:9" ht="67.5">
       <c r="A30" s="2" t="s">
-        <v>61</v>
+        <v>196</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>18</v>
@@ -2850,10 +2786,10 @@
         <v>1</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>258</v>
+        <v>167</v>
       </c>
       <c r="I30" s="4">
         <v>1</v>
@@ -2861,7 +2797,7 @@
     </row>
     <row r="31" spans="1:9" ht="67.5">
       <c r="A31" s="2" t="s">
-        <v>76</v>
+        <v>197</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>18</v>
@@ -2876,10 +2812,10 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>141</v>
+        <v>89</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I31" s="4">
         <v>1</v>
@@ -2887,10 +2823,10 @@
     </row>
     <row r="32" spans="1:9" ht="175.5">
       <c r="A32" s="2" t="s">
-        <v>62</v>
+        <v>198</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>18</v>
@@ -2905,10 +2841,10 @@
         <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="I32" s="4">
         <v>1</v>
@@ -2916,7 +2852,7 @@
     </row>
     <row r="33" spans="1:9" ht="108">
       <c r="A33" s="2" t="s">
-        <v>65</v>
+        <v>199</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>18</v>
@@ -2931,10 +2867,10 @@
         <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>143</v>
+        <v>91</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="I33" s="4">
         <v>1</v>
@@ -2942,7 +2878,7 @@
     </row>
     <row r="34" spans="1:9" ht="108">
       <c r="A34" s="2" t="s">
-        <v>66</v>
+        <v>200</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>18</v>
@@ -2957,10 +2893,10 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>144</v>
+        <v>92</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="I34" s="4">
         <v>1</v>
@@ -2968,7 +2904,7 @@
     </row>
     <row r="35" spans="1:9" ht="67.5">
       <c r="A35" s="6" t="s">
-        <v>231</v>
+        <v>201</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>18</v>
@@ -2983,10 +2919,10 @@
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>239</v>
+        <v>160</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="I35" s="4">
         <v>1</v>
@@ -2994,7 +2930,7 @@
     </row>
     <row r="36" spans="1:9" ht="54">
       <c r="A36" s="2" t="s">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>18</v>
@@ -3009,10 +2945,10 @@
         <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>145</v>
+        <v>93</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I36" s="4">
         <v>1</v>
@@ -3020,7 +2956,7 @@
     </row>
     <row r="37" spans="1:9" ht="54">
       <c r="A37" s="2" t="s">
-        <v>67</v>
+        <v>203</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>18</v>
@@ -3035,10 +2971,10 @@
         <v>1</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>146</v>
+        <v>94</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I37" s="4">
         <v>1</v>
@@ -3046,7 +2982,7 @@
     </row>
     <row r="38" spans="1:9" ht="54">
       <c r="A38" s="2" t="s">
-        <v>78</v>
+        <v>204</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>18</v>
@@ -3061,10 +2997,10 @@
         <v>1</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>147</v>
+        <v>95</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I38" s="4">
         <v>1</v>
@@ -3072,10 +3008,10 @@
     </row>
     <row r="39" spans="1:9" ht="135">
       <c r="A39" s="2" t="s">
-        <v>77</v>
+        <v>205</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>18</v>
@@ -3090,10 +3026,10 @@
         <v>1</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="I39" s="4">
         <v>1</v>
@@ -3101,7 +3037,7 @@
     </row>
     <row r="40" spans="1:9" ht="54">
       <c r="A40" s="2" t="s">
-        <v>69</v>
+        <v>206</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>18</v>
@@ -3116,10 +3052,10 @@
         <v>1</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="I40" s="4">
         <v>1</v>
@@ -3127,7 +3063,7 @@
     </row>
     <row r="41" spans="1:9" ht="54">
       <c r="A41" s="2" t="s">
-        <v>71</v>
+        <v>207</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>18</v>
@@ -3142,10 +3078,10 @@
         <v>1</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>72</v>
+        <v>50</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="I41" s="4">
         <v>1</v>
@@ -3153,7 +3089,7 @@
     </row>
     <row r="42" spans="1:9" ht="168" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>73</v>
+        <v>208</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>18</v>
@@ -3168,10 +3104,10 @@
         <v>1</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="I42" s="4">
         <v>1</v>
@@ -3179,7 +3115,7 @@
     </row>
     <row r="43" spans="1:9" ht="168" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>18</v>
@@ -3194,10 +3130,10 @@
         <v>1</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>149</v>
+        <v>97</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="I43" s="4">
         <v>1</v>
@@ -3205,7 +3141,7 @@
     </row>
     <row r="44" spans="1:9" ht="67.5">
       <c r="A44" s="6" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>18</v>
@@ -3220,10 +3156,10 @@
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>246</v>
+        <v>163</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="I44" s="4">
         <v>1</v>
@@ -3231,7 +3167,7 @@
     </row>
     <row r="45" spans="1:9" ht="54">
       <c r="A45" s="2" t="s">
-        <v>74</v>
+        <v>211</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>18</v>
@@ -3246,10 +3182,10 @@
         <v>1</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>150</v>
+        <v>98</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>212</v>
+        <v>145</v>
       </c>
       <c r="I45" s="4">
         <v>1</v>
@@ -3257,7 +3193,7 @@
     </row>
     <row r="46" spans="1:9" ht="54">
       <c r="A46" s="2" t="s">
-        <v>79</v>
+        <v>212</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>18</v>
@@ -3272,10 +3208,10 @@
         <v>1</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>242</v>
+        <v>161</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="I46" s="4">
         <v>1</v>
@@ -3283,7 +3219,7 @@
     </row>
     <row r="47" spans="1:9" ht="54">
       <c r="A47" s="2" t="s">
-        <v>80</v>
+        <v>213</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>18</v>
@@ -3298,10 +3234,10 @@
         <v>1</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>151</v>
+        <v>99</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="I47" s="4">
         <v>1</v>
@@ -3309,10 +3245,10 @@
     </row>
     <row r="48" spans="1:9" ht="148.5">
       <c r="A48" s="2" t="s">
-        <v>105</v>
+        <v>214</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>18</v>
@@ -3327,10 +3263,10 @@
         <v>1</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="I48" s="4">
         <v>1</v>
@@ -3338,7 +3274,7 @@
     </row>
     <row r="49" spans="1:9" ht="54">
       <c r="A49" s="2" t="s">
-        <v>107</v>
+        <v>215</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>18</v>
@@ -3353,10 +3289,10 @@
         <v>1</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>108</v>
+        <v>66</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="I49" s="4">
         <v>1</v>
@@ -3364,7 +3300,7 @@
     </row>
     <row r="50" spans="1:9" ht="54">
       <c r="A50" s="2" t="s">
-        <v>109</v>
+        <v>216</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>18</v>
@@ -3379,10 +3315,10 @@
         <v>1</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>110</v>
+        <v>67</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="I50" s="4">
         <v>1</v>
@@ -3390,7 +3326,7 @@
     </row>
     <row r="51" spans="1:9" ht="168" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>111</v>
+        <v>217</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>18</v>
@@ -3405,10 +3341,10 @@
         <v>1</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="I51" s="4">
         <v>1</v>
@@ -3416,7 +3352,7 @@
     </row>
     <row r="52" spans="1:9" ht="168" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>243</v>
+        <v>218</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>18</v>
@@ -3431,10 +3367,10 @@
         <v>1</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="I52" s="4">
         <v>1</v>
@@ -3442,7 +3378,7 @@
     </row>
     <row r="53" spans="1:9" ht="67.5">
       <c r="A53" s="6" t="s">
-        <v>244</v>
+        <v>219</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>18</v>
@@ -3457,10 +3393,10 @@
         <v>1</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>245</v>
+        <v>162</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="I53" s="4">
         <v>1</v>
@@ -3468,7 +3404,7 @@
     </row>
     <row r="54" spans="1:9" ht="67.5">
       <c r="A54" s="2" t="s">
-        <v>112</v>
+        <v>220</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>18</v>
@@ -3483,10 +3419,10 @@
         <v>1</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>258</v>
+        <v>167</v>
       </c>
       <c r="I54" s="4">
         <v>1</v>
@@ -3494,7 +3430,7 @@
     </row>
     <row r="55" spans="1:9" ht="81">
       <c r="A55" s="2" t="s">
-        <v>113</v>
+        <v>221</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>18</v>
@@ -3509,10 +3445,10 @@
         <v>1</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>155</v>
+        <v>103</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="I55" s="4">
         <v>1</v>
@@ -3520,10 +3456,10 @@
     </row>
     <row r="56" spans="1:9" ht="135">
       <c r="A56" s="2" t="s">
-        <v>88</v>
+        <v>222</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>18</v>
@@ -3538,10 +3474,10 @@
         <v>1</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="I56" s="4">
         <v>1</v>
@@ -3549,7 +3485,7 @@
     </row>
     <row r="57" spans="1:9" ht="54">
       <c r="A57" s="2" t="s">
-        <v>90</v>
+        <v>223</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>18</v>
@@ -3564,10 +3500,10 @@
         <v>1</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>91</v>
+        <v>56</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="I57" s="4">
         <v>1</v>
@@ -3575,7 +3511,7 @@
     </row>
     <row r="58" spans="1:9" ht="54">
       <c r="A58" s="2" t="s">
-        <v>92</v>
+        <v>224</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>18</v>
@@ -3590,10 +3526,10 @@
         <v>1</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>93</v>
+        <v>57</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="I58" s="4">
         <v>1</v>
@@ -3601,7 +3537,7 @@
     </row>
     <row r="59" spans="1:9" ht="168" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>94</v>
+        <v>225</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>18</v>
@@ -3616,10 +3552,10 @@
         <v>1</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="I59" s="4">
         <v>1</v>
@@ -3627,7 +3563,7 @@
     </row>
     <row r="60" spans="1:9" ht="168" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>18</v>
@@ -3642,10 +3578,10 @@
         <v>1</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>157</v>
+        <v>105</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="I60" s="4">
         <v>1</v>
@@ -3653,7 +3589,7 @@
     </row>
     <row r="61" spans="1:9" ht="67.5">
       <c r="A61" s="6" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>18</v>
@@ -3668,10 +3604,10 @@
         <v>1</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>249</v>
+        <v>164</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="I61" s="4">
         <v>1</v>
@@ -3679,7 +3615,7 @@
     </row>
     <row r="62" spans="1:9" ht="54">
       <c r="A62" s="2" t="s">
-        <v>95</v>
+        <v>228</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>18</v>
@@ -3694,10 +3630,10 @@
         <v>1</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>158</v>
+        <v>106</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>258</v>
+        <v>167</v>
       </c>
       <c r="I62" s="4">
         <v>1</v>
@@ -3705,7 +3641,7 @@
     </row>
     <row r="63" spans="1:9" ht="54">
       <c r="A63" s="2" t="s">
-        <v>96</v>
+        <v>229</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>18</v>
@@ -3720,10 +3656,10 @@
         <v>1</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>159</v>
+        <v>107</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I63" s="4">
         <v>1</v>
@@ -3731,10 +3667,10 @@
     </row>
     <row r="64" spans="1:9" ht="162">
       <c r="A64" s="2" t="s">
-        <v>104</v>
+        <v>230</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>126</v>
+        <v>75</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>18</v>
@@ -3749,10 +3685,10 @@
         <v>1</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="I64" s="4">
         <v>1</v>
@@ -3760,7 +3696,7 @@
     </row>
     <row r="65" spans="1:9" ht="54">
       <c r="A65" s="2" t="s">
-        <v>82</v>
+        <v>231</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>18</v>
@@ -3775,10 +3711,10 @@
         <v>1</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="I65" s="4">
         <v>1</v>
@@ -3786,7 +3722,7 @@
     </row>
     <row r="66" spans="1:9" ht="54">
       <c r="A66" s="2" t="s">
-        <v>84</v>
+        <v>232</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>18</v>
@@ -3801,10 +3737,10 @@
         <v>1</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>85</v>
+        <v>54</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="I66" s="4">
         <v>1</v>
@@ -3812,7 +3748,7 @@
     </row>
     <row r="67" spans="1:9" ht="168" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>86</v>
+        <v>233</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>18</v>
@@ -3827,10 +3763,10 @@
         <v>1</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>160</v>
+        <v>108</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="I67" s="4">
         <v>1</v>
@@ -3838,7 +3774,7 @@
     </row>
     <row r="68" spans="1:9" ht="168" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>251</v>
+        <v>234</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>18</v>
@@ -3853,10 +3789,10 @@
         <v>1</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>161</v>
+        <v>109</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="I68" s="4">
         <v>1</v>
@@ -3864,7 +3800,7 @@
     </row>
     <row r="69" spans="1:9" ht="67.5">
       <c r="A69" s="6" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>18</v>
@@ -3879,10 +3815,10 @@
         <v>1</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>253</v>
+        <v>165</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="I69" s="4">
         <v>1</v>
@@ -3890,7 +3826,7 @@
     </row>
     <row r="70" spans="1:9" ht="67.5">
       <c r="A70" s="2" t="s">
-        <v>250</v>
+        <v>236</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>18</v>
@@ -3905,10 +3841,10 @@
         <v>1</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>162</v>
+        <v>110</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>258</v>
+        <v>167</v>
       </c>
       <c r="I70" s="4">
         <v>1</v>
@@ -3916,7 +3852,7 @@
     </row>
     <row r="71" spans="1:9" ht="81">
       <c r="A71" s="2" t="s">
-        <v>87</v>
+        <v>237</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>18</v>
@@ -3931,10 +3867,10 @@
         <v>1</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>163</v>
+        <v>111</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I71" s="4">
         <v>1</v>
@@ -3942,10 +3878,10 @@
     </row>
     <row r="72" spans="1:9" ht="162">
       <c r="A72" s="2" t="s">
-        <v>119</v>
+        <v>238</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>125</v>
+        <v>74</v>
       </c>
       <c r="C72" s="1" t="s">
         <v>18</v>
@@ -3960,10 +3896,10 @@
         <v>1</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="I72" s="4">
         <v>1</v>
@@ -3971,7 +3907,7 @@
     </row>
     <row r="73" spans="1:9" ht="54">
       <c r="A73" s="2" t="s">
-        <v>115</v>
+        <v>239</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>18</v>
@@ -3986,10 +3922,10 @@
         <v>1</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>116</v>
+        <v>69</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="I73" s="4">
         <v>1</v>
@@ -3997,7 +3933,7 @@
     </row>
     <row r="74" spans="1:9" ht="168" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>117</v>
+        <v>240</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>18</v>
@@ -4012,10 +3948,10 @@
         <v>1</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>164</v>
+        <v>112</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="I74" s="4">
         <v>1</v>
@@ -4023,7 +3959,7 @@
     </row>
     <row r="75" spans="1:9" ht="168" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>254</v>
+        <v>241</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>18</v>
@@ -4038,10 +3974,10 @@
         <v>1</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>218</v>
+        <v>150</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="I75" s="4">
         <v>1</v>
@@ -4049,7 +3985,7 @@
     </row>
     <row r="76" spans="1:9" ht="67.5">
       <c r="A76" s="6" t="s">
-        <v>255</v>
+        <v>242</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>18</v>
@@ -4064,10 +4000,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>256</v>
+        <v>166</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>223</v>
+        <v>153</v>
       </c>
       <c r="I76" s="4">
         <v>1</v>
@@ -4075,7 +4011,7 @@
     </row>
     <row r="77" spans="1:9" ht="67.5">
       <c r="A77" s="2" t="s">
-        <v>118</v>
+        <v>243</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>18</v>
@@ -4090,10 +4026,10 @@
         <v>1</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>208</v>
+        <v>141</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="I77" s="4">
         <v>1</v>
@@ -4101,10 +4037,10 @@
     </row>
     <row r="78" spans="1:9" ht="121.5">
       <c r="A78" s="6" t="s">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>136</v>
+        <v>84</v>
       </c>
       <c r="C78" s="1" t="s">
         <v>18</v>
@@ -4119,10 +4055,10 @@
         <v>1</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>201</v>
+        <v>137</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>202</v>
+        <v>138</v>
       </c>
       <c r="I78" s="4">
         <v>1</v>
@@ -4130,10 +4066,10 @@
     </row>
     <row r="79" spans="1:9" ht="162">
       <c r="A79" s="2" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>207</v>
+        <v>140</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>18</v>
@@ -4148,10 +4084,10 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>209</v>
+        <v>142</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>210</v>
+        <v>143</v>
       </c>
       <c r="I79" s="4">
         <v>1</v>
@@ -4159,10 +4095,10 @@
     </row>
     <row r="80" spans="1:9" ht="54">
       <c r="A80" s="6" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>206</v>
+        <v>139</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>18</v>
@@ -4177,10 +4113,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>211</v>
+        <v>144</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>212</v>
+        <v>145</v>
       </c>
       <c r="I80" s="4">
         <v>1</v>
@@ -4188,7 +4124,7 @@
     </row>
     <row r="81" spans="1:9" ht="67.5">
       <c r="A81" s="2" t="s">
-        <v>166</v>
+        <v>247</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" s="1" t="s">
@@ -4204,10 +4140,10 @@
         <v>1</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>182</v>
+        <v>123</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>167</v>
+        <v>114</v>
       </c>
       <c r="I81" s="4">
         <v>1</v>
@@ -4215,10 +4151,10 @@
     </row>
     <row r="82" spans="1:9" ht="135">
       <c r="A82" s="2" t="s">
-        <v>170</v>
+        <v>248</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>168</v>
+        <v>115</v>
       </c>
       <c r="C82" s="1" t="s">
         <v>18</v>
@@ -4233,10 +4169,10 @@
         <v>1</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>183</v>
+        <v>124</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>184</v>
+        <v>125</v>
       </c>
       <c r="I82" s="4">
         <v>1</v>
@@ -4244,7 +4180,7 @@
     </row>
     <row r="83" spans="1:9" ht="67.5">
       <c r="A83" s="2" t="s">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>18</v>
@@ -4259,10 +4195,10 @@
         <v>1</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>185</v>
+        <v>126</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>171</v>
+        <v>116</v>
       </c>
       <c r="I83" s="4">
         <v>1</v>
@@ -4270,7 +4206,7 @@
     </row>
     <row r="84" spans="1:9" ht="121.5">
       <c r="A84" s="2" t="s">
-        <v>26</v>
+        <v>250</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>18</v>
@@ -4285,10 +4221,10 @@
         <v>1</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>186</v>
+        <v>127</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>172</v>
+        <v>117</v>
       </c>
       <c r="I84" s="4">
         <v>1</v>
@@ -4296,7 +4232,7 @@
     </row>
     <row r="85" spans="1:9" ht="67.5">
       <c r="A85" s="2" t="s">
-        <v>25</v>
+        <v>251</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>18</v>
@@ -4311,10 +4247,10 @@
         <v>1</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>259</v>
+        <v>168</v>
       </c>
       <c r="I85" s="4">
         <v>1</v>
@@ -4322,10 +4258,10 @@
     </row>
     <row r="86" spans="1:9" ht="121.5">
       <c r="A86" s="2" t="s">
-        <v>177</v>
+        <v>252</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="C86" s="1" t="s">
         <v>18</v>
@@ -4340,10 +4276,10 @@
         <v>1</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="I86" s="4">
         <v>1</v>
@@ -4351,7 +4287,7 @@
     </row>
     <row r="87" spans="1:9" ht="54">
       <c r="A87" s="2" t="s">
-        <v>176</v>
+        <v>253</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>18</v>
@@ -4366,10 +4302,10 @@
         <v>1</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="I87" s="4">
         <v>1</v>
@@ -4377,7 +4313,7 @@
     </row>
     <row r="88" spans="1:9" ht="67.5">
       <c r="A88" s="2" t="s">
-        <v>180</v>
+        <v>254</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>18</v>
@@ -4392,10 +4328,10 @@
         <v>1</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>187</v>
+        <v>128</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>173</v>
+        <v>118</v>
       </c>
       <c r="I88" s="4">
         <v>1</v>
@@ -4403,10 +4339,10 @@
     </row>
     <row r="89" spans="1:9" ht="121.5">
       <c r="A89" s="2" t="s">
-        <v>190</v>
+        <v>255</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>181</v>
+        <v>122</v>
       </c>
       <c r="C89" s="1" t="s">
         <v>18</v>
@@ -4421,10 +4357,10 @@
         <v>1</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>192</v>
+        <v>131</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="I89" s="4">
         <v>1</v>
@@ -4432,7 +4368,7 @@
     </row>
     <row r="90" spans="1:9" ht="54">
       <c r="A90" s="2" t="s">
-        <v>191</v>
+        <v>256</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>18</v>
@@ -4447,10 +4383,10 @@
         <v>1</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>192</v>
+        <v>131</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="I90" s="4">
         <v>1</v>
@@ -4458,7 +4394,7 @@
     </row>
     <row r="91" spans="1:9" ht="67.5">
       <c r="A91" s="2" t="s">
-        <v>178</v>
+        <v>257</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>18</v>
@@ -4473,10 +4409,10 @@
         <v>1</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>188</v>
+        <v>129</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>189</v>
+        <v>130</v>
       </c>
       <c r="I91" s="4">
         <v>1</v>
@@ -4484,7 +4420,7 @@
     </row>
     <row r="92" spans="1:9" ht="67.5">
       <c r="A92" s="2" t="s">
-        <v>193</v>
+        <v>258</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>18</v>
@@ -4499,10 +4435,10 @@
         <v>1</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>194</v>
+        <v>132</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>199</v>
+        <v>135</v>
       </c>
       <c r="I92" s="4">
         <v>1</v>
@@ -4510,7 +4446,7 @@
     </row>
     <row r="93" spans="1:9" ht="67.5">
       <c r="A93" s="2" t="s">
-        <v>195</v>
+        <v>259</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>18</v>
@@ -4525,10 +4461,10 @@
         <v>1</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>196</v>
+        <v>133</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="I93" s="4">
         <v>1</v>
@@ -4536,7 +4472,7 @@
     </row>
     <row r="94" spans="1:9" ht="94.5">
       <c r="A94" s="2" t="s">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="C94" s="1" t="s">
         <v>18</v>
@@ -4551,10 +4487,10 @@
         <v>1</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>198</v>
+        <v>134</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>200</v>
+        <v>136</v>
       </c>
       <c r="I94" s="4">
         <v>1</v>

--- a/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/基本操作（update upsert）参数校验测试用例.xlsx
@@ -93,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="277">
   <si>
     <t>name</t>
   </si>
@@ -952,13 +952,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，query.update更新CL指定数据，returnNew取值为空，如：
-db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},returnNew:)
-db.CS.CL.find({age:{$gt:10}}).update({$inc:{age:1}},)
-2、检查更新结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、更新失败，结果不打印修改后的所有记录值
 2、db.cs.cl.find查看指定更新的字段更新正确</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1470,7 +1463,90 @@
     <t>query.update，returnNew取值非法_st.verify.update.091</t>
   </si>
   <si>
-    <t>query.update，returnNew取值为空_st.verify.update.092</t>
+    <t>更新成功，返回数据只显示skip后的n条数据，返回数据正确。find查看数据已被更新，更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update与query.count一起使用更新数据，如：
+&gt; cl.find().update({$replace:{a:1}},true).skip(5)
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update与query.skip()一起使用更新数据，并使用索引_st.verify.update.097</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新成功，返回数据只打印limit限制的条数，返回数据正确。find查看数据已被更新，更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update与query.count一起使用更新数据，如：
+&gt; cl.find().update({$replace:{a:1}},true).limit({a:1})
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update与query.limit()一起使用更新数据，并使用索引_st.verify.update.096</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新成功，find查看数据已被更新，更新正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update与query.count一起使用更新数据，如：
+&gt; cl.find().update({$replace:{a:1}},true).sort({_id:1})
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update与query.sort一起使用更新数据，并使用索引_st.verify.update.095</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新失败，提示sort与update或remove一起使用必须要用索引字段，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update与query.count一起使用更新数据，如：
+&gt; cl.find().update({$replace:{a:1}},true).sort({a:1})，其中a字段不是索引字段
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update与query.sort一起使用更新数据，不使用索引_st.verify.update.094</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新失败，提示count不能与update()或remove()一起使用，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update与query.count一起使用更新数据，如：
+&gt; cl.find().update({$replace:{a:1}},true).remove()
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update与query.remove一起使用更新数据_st.verify.update.093</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，query.update与query.count一起使用更新数据，如：
+&gt; cl.find().update({$replace:{a:1}},true).count()
+2、检查更新结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不能与 query.count()、query.remove()同时使用。
+与 query.sort()同时使用时，在单个节点上排序必须使用索引。
+在集群中与 query.limit()或 query.skip()同时使用时，要保证查询条件会在单个节点或单个子表上执行。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>query.update与query.count一起使用更新数据_st.verify.update.092</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1661,8 +1737,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I94" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I94"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I99" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I99"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1981,7 +2057,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I99"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="38.25" style="1" customWidth="1"/>
@@ -2054,10 +2130,10 @@
     </row>
     <row r="3" spans="1:9" ht="175.5">
       <c r="A3" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>18</v>
@@ -2072,7 +2148,7 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>19</v>
@@ -2083,7 +2159,7 @@
     </row>
     <row r="4" spans="1:9" ht="81">
       <c r="A4" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>18</v>
@@ -2098,7 +2174,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>20</v>
@@ -2109,7 +2185,7 @@
     </row>
     <row r="5" spans="1:9" ht="81">
       <c r="A5" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>18</v>
@@ -2124,7 +2200,7 @@
         <v>1</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>113</v>
@@ -2135,7 +2211,7 @@
     </row>
     <row r="6" spans="1:9" ht="54">
       <c r="A6" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>18</v>
@@ -2161,7 +2237,7 @@
     </row>
     <row r="7" spans="1:9" ht="67.5">
       <c r="A7" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>18</v>
@@ -2187,7 +2263,7 @@
     </row>
     <row r="8" spans="1:9" ht="168" customHeight="1">
       <c r="A8" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>83</v>
@@ -2205,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>22</v>
@@ -2216,7 +2292,7 @@
     </row>
     <row r="9" spans="1:9" ht="67.5">
       <c r="A9" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>18</v>
@@ -2231,10 +2307,10 @@
         <v>1</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I9" s="4">
         <v>1</v>
@@ -2242,7 +2318,7 @@
     </row>
     <row r="10" spans="1:9" ht="67.5">
       <c r="A10" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>18</v>
@@ -2257,7 +2333,7 @@
         <v>1</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>23</v>
@@ -2268,7 +2344,7 @@
     </row>
     <row r="11" spans="1:9" ht="168" customHeight="1">
       <c r="A11" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>18</v>
@@ -2283,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>24</v>
@@ -2294,7 +2370,7 @@
     </row>
     <row r="12" spans="1:9" ht="67.5">
       <c r="A12" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>18</v>
@@ -2312,7 +2388,7 @@
         <v>31</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I12" s="4">
         <v>1</v>
@@ -2320,7 +2396,7 @@
     </row>
     <row r="13" spans="1:9" ht="54">
       <c r="A13" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>18</v>
@@ -2346,7 +2422,7 @@
     </row>
     <row r="14" spans="1:9" ht="168" customHeight="1">
       <c r="A14" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>80</v>
@@ -2375,7 +2451,7 @@
     </row>
     <row r="15" spans="1:9" ht="67.5">
       <c r="A15" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>18</v>
@@ -2390,10 +2466,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I15" s="4">
         <v>1</v>
@@ -2401,7 +2477,7 @@
     </row>
     <row r="16" spans="1:9" ht="67.5">
       <c r="A16" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>18</v>
@@ -2427,7 +2503,7 @@
     </row>
     <row r="17" spans="1:9" ht="168" customHeight="1">
       <c r="A17" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>18</v>
@@ -2453,7 +2529,7 @@
     </row>
     <row r="18" spans="1:9" ht="67.5">
       <c r="A18" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>18</v>
@@ -2471,7 +2547,7 @@
         <v>36</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I18" s="4">
         <v>1</v>
@@ -2479,10 +2555,10 @@
     </row>
     <row r="19" spans="1:9" ht="94.5">
       <c r="A19" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>18</v>
@@ -2508,7 +2584,7 @@
     </row>
     <row r="20" spans="1:9" ht="67.5">
       <c r="A20" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>18</v>
@@ -2523,10 +2599,10 @@
         <v>1</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I20" s="4">
         <v>1</v>
@@ -2534,7 +2610,7 @@
     </row>
     <row r="21" spans="1:9" ht="67.5">
       <c r="A21" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>18</v>
@@ -2560,7 +2636,7 @@
     </row>
     <row r="22" spans="1:9" ht="54">
       <c r="A22" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>18</v>
@@ -2586,7 +2662,7 @@
     </row>
     <row r="23" spans="1:9" ht="162">
       <c r="A23" s="2" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>81</v>
@@ -2615,7 +2691,7 @@
     </row>
     <row r="24" spans="1:9" ht="54">
       <c r="A24" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>18</v>
@@ -2641,7 +2717,7 @@
     </row>
     <row r="25" spans="1:9" ht="54">
       <c r="A25" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>18</v>
@@ -2667,7 +2743,7 @@
     </row>
     <row r="26" spans="1:9" ht="67.5">
       <c r="A26" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>18</v>
@@ -2682,10 +2758,10 @@
         <v>1</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I26" s="4">
         <v>1</v>
@@ -2693,7 +2769,7 @@
     </row>
     <row r="27" spans="1:9" ht="168" customHeight="1">
       <c r="A27" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>18</v>
@@ -2719,7 +2795,7 @@
     </row>
     <row r="28" spans="1:9" ht="67.5">
       <c r="A28" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>18</v>
@@ -2745,7 +2821,7 @@
     </row>
     <row r="29" spans="1:9" ht="168" customHeight="1">
       <c r="A29" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>18</v>
@@ -2771,7 +2847,7 @@
     </row>
     <row r="30" spans="1:9" ht="67.5">
       <c r="A30" s="2" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>18</v>
@@ -2789,7 +2865,7 @@
         <v>88</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I30" s="4">
         <v>1</v>
@@ -2797,7 +2873,7 @@
     </row>
     <row r="31" spans="1:9" ht="67.5">
       <c r="A31" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>18</v>
@@ -2823,7 +2899,7 @@
     </row>
     <row r="32" spans="1:9" ht="175.5">
       <c r="A32" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>82</v>
@@ -2852,7 +2928,7 @@
     </row>
     <row r="33" spans="1:9" ht="108">
       <c r="A33" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>18</v>
@@ -2878,7 +2954,7 @@
     </row>
     <row r="34" spans="1:9" ht="108">
       <c r="A34" s="2" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>18</v>
@@ -2904,7 +2980,7 @@
     </row>
     <row r="35" spans="1:9" ht="67.5">
       <c r="A35" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>18</v>
@@ -2919,10 +2995,10 @@
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I35" s="4">
         <v>1</v>
@@ -2930,7 +3006,7 @@
     </row>
     <row r="36" spans="1:9" ht="54">
       <c r="A36" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>18</v>
@@ -2956,7 +3032,7 @@
     </row>
     <row r="37" spans="1:9" ht="54">
       <c r="A37" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>18</v>
@@ -2982,7 +3058,7 @@
     </row>
     <row r="38" spans="1:9" ht="54">
       <c r="A38" s="2" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>18</v>
@@ -3008,7 +3084,7 @@
     </row>
     <row r="39" spans="1:9" ht="135">
       <c r="A39" s="2" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>78</v>
@@ -3037,7 +3113,7 @@
     </row>
     <row r="40" spans="1:9" ht="54">
       <c r="A40" s="2" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>18</v>
@@ -3063,7 +3139,7 @@
     </row>
     <row r="41" spans="1:9" ht="54">
       <c r="A41" s="2" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>18</v>
@@ -3089,7 +3165,7 @@
     </row>
     <row r="42" spans="1:9" ht="168" customHeight="1">
       <c r="A42" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>18</v>
@@ -3115,7 +3191,7 @@
     </row>
     <row r="43" spans="1:9" ht="168" customHeight="1">
       <c r="A43" s="2" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>18</v>
@@ -3141,7 +3217,7 @@
     </row>
     <row r="44" spans="1:9" ht="67.5">
       <c r="A44" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>18</v>
@@ -3156,10 +3232,10 @@
         <v>1</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I44" s="4">
         <v>1</v>
@@ -3167,7 +3243,7 @@
     </row>
     <row r="45" spans="1:9" ht="54">
       <c r="A45" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>18</v>
@@ -3185,7 +3261,7 @@
         <v>98</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I45" s="4">
         <v>1</v>
@@ -3193,7 +3269,7 @@
     </row>
     <row r="46" spans="1:9" ht="54">
       <c r="A46" s="2" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>18</v>
@@ -3208,7 +3284,7 @@
         <v>1</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>64</v>
@@ -3219,7 +3295,7 @@
     </row>
     <row r="47" spans="1:9" ht="54">
       <c r="A47" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>18</v>
@@ -3245,7 +3321,7 @@
     </row>
     <row r="48" spans="1:9" ht="148.5">
       <c r="A48" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>77</v>
@@ -3274,7 +3350,7 @@
     </row>
     <row r="49" spans="1:9" ht="54">
       <c r="A49" s="2" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>18</v>
@@ -3300,7 +3376,7 @@
     </row>
     <row r="50" spans="1:9" ht="54">
       <c r="A50" s="2" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>18</v>
@@ -3326,7 +3402,7 @@
     </row>
     <row r="51" spans="1:9" ht="168" customHeight="1">
       <c r="A51" s="2" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>18</v>
@@ -3352,7 +3428,7 @@
     </row>
     <row r="52" spans="1:9" ht="168" customHeight="1">
       <c r="A52" s="2" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>18</v>
@@ -3378,7 +3454,7 @@
     </row>
     <row r="53" spans="1:9" ht="67.5">
       <c r="A53" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>18</v>
@@ -3393,10 +3469,10 @@
         <v>1</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I53" s="4">
         <v>1</v>
@@ -3404,7 +3480,7 @@
     </row>
     <row r="54" spans="1:9" ht="67.5">
       <c r="A54" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C54" s="1" t="s">
         <v>18</v>
@@ -3422,7 +3498,7 @@
         <v>102</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I54" s="4">
         <v>1</v>
@@ -3430,7 +3506,7 @@
     </row>
     <row r="55" spans="1:9" ht="81">
       <c r="A55" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C55" s="1" t="s">
         <v>18</v>
@@ -3456,7 +3532,7 @@
     </row>
     <row r="56" spans="1:9" ht="135">
       <c r="A56" s="2" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>76</v>
@@ -3485,7 +3561,7 @@
     </row>
     <row r="57" spans="1:9" ht="54">
       <c r="A57" s="2" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C57" s="1" t="s">
         <v>18</v>
@@ -3511,7 +3587,7 @@
     </row>
     <row r="58" spans="1:9" ht="54">
       <c r="A58" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C58" s="1" t="s">
         <v>18</v>
@@ -3537,7 +3613,7 @@
     </row>
     <row r="59" spans="1:9" ht="168" customHeight="1">
       <c r="A59" s="2" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>18</v>
@@ -3563,7 +3639,7 @@
     </row>
     <row r="60" spans="1:9" ht="168" customHeight="1">
       <c r="A60" s="2" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>18</v>
@@ -3589,7 +3665,7 @@
     </row>
     <row r="61" spans="1:9" ht="67.5">
       <c r="A61" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C61" s="1" t="s">
         <v>18</v>
@@ -3604,10 +3680,10 @@
         <v>1</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I61" s="4">
         <v>1</v>
@@ -3615,7 +3691,7 @@
     </row>
     <row r="62" spans="1:9" ht="54">
       <c r="A62" s="2" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>18</v>
@@ -3633,7 +3709,7 @@
         <v>106</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I62" s="4">
         <v>1</v>
@@ -3641,7 +3717,7 @@
     </row>
     <row r="63" spans="1:9" ht="54">
       <c r="A63" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>18</v>
@@ -3667,7 +3743,7 @@
     </row>
     <row r="64" spans="1:9" ht="162">
       <c r="A64" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>75</v>
@@ -3696,7 +3772,7 @@
     </row>
     <row r="65" spans="1:9" ht="54">
       <c r="A65" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>18</v>
@@ -3722,7 +3798,7 @@
     </row>
     <row r="66" spans="1:9" ht="54">
       <c r="A66" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>18</v>
@@ -3748,7 +3824,7 @@
     </row>
     <row r="67" spans="1:9" ht="168" customHeight="1">
       <c r="A67" s="2" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>18</v>
@@ -3774,7 +3850,7 @@
     </row>
     <row r="68" spans="1:9" ht="168" customHeight="1">
       <c r="A68" s="2" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C68" s="1" t="s">
         <v>18</v>
@@ -3800,7 +3876,7 @@
     </row>
     <row r="69" spans="1:9" ht="67.5">
       <c r="A69" s="6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>18</v>
@@ -3815,10 +3891,10 @@
         <v>1</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I69" s="4">
         <v>1</v>
@@ -3826,7 +3902,7 @@
     </row>
     <row r="70" spans="1:9" ht="67.5">
       <c r="A70" s="2" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>18</v>
@@ -3844,7 +3920,7 @@
         <v>110</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="I70" s="4">
         <v>1</v>
@@ -3852,7 +3928,7 @@
     </row>
     <row r="71" spans="1:9" ht="81">
       <c r="A71" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C71" s="1" t="s">
         <v>18</v>
@@ -3878,7 +3954,7 @@
     </row>
     <row r="72" spans="1:9" ht="162">
       <c r="A72" s="2" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B72" s="5" t="s">
         <v>74</v>
@@ -3907,7 +3983,7 @@
     </row>
     <row r="73" spans="1:9" ht="54">
       <c r="A73" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>18</v>
@@ -3933,7 +4009,7 @@
     </row>
     <row r="74" spans="1:9" ht="168" customHeight="1">
       <c r="A74" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C74" s="1" t="s">
         <v>18</v>
@@ -3959,7 +4035,7 @@
     </row>
     <row r="75" spans="1:9" ht="168" customHeight="1">
       <c r="A75" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C75" s="1" t="s">
         <v>18</v>
@@ -3974,7 +4050,7 @@
         <v>1</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>51</v>
@@ -3985,7 +4061,7 @@
     </row>
     <row r="76" spans="1:9" ht="67.5">
       <c r="A76" s="6" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C76" s="1" t="s">
         <v>18</v>
@@ -4000,10 +4076,10 @@
         <v>1</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I76" s="4">
         <v>1</v>
@@ -4011,7 +4087,7 @@
     </row>
     <row r="77" spans="1:9" ht="67.5">
       <c r="A77" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C77" s="1" t="s">
         <v>18</v>
@@ -4026,7 +4102,7 @@
         <v>1</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>25</v>
@@ -4037,7 +4113,7 @@
     </row>
     <row r="78" spans="1:9" ht="121.5">
       <c r="A78" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B78" s="5" t="s">
         <v>84</v>
@@ -4055,10 +4131,10 @@
         <v>1</v>
       </c>
       <c r="G78" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="H78" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="H78" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="I78" s="4">
         <v>1</v>
@@ -4066,10 +4142,10 @@
     </row>
     <row r="79" spans="1:9" ht="162">
       <c r="A79" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C79" s="1" t="s">
         <v>18</v>
@@ -4084,10 +4160,10 @@
         <v>1</v>
       </c>
       <c r="G79" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H79" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="H79" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="I79" s="4">
         <v>1</v>
@@ -4095,10 +4171,10 @@
     </row>
     <row r="80" spans="1:9" ht="54">
       <c r="A80" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C80" s="1" t="s">
         <v>18</v>
@@ -4113,10 +4189,10 @@
         <v>1</v>
       </c>
       <c r="G80" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="H80" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="I80" s="4">
         <v>1</v>
@@ -4124,7 +4200,7 @@
     </row>
     <row r="81" spans="1:9" ht="67.5">
       <c r="A81" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B81" s="2"/>
       <c r="C81" s="1" t="s">
@@ -4151,7 +4227,7 @@
     </row>
     <row r="82" spans="1:9" ht="135">
       <c r="A82" s="2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B82" s="5" t="s">
         <v>115</v>
@@ -4180,7 +4256,7 @@
     </row>
     <row r="83" spans="1:9" ht="67.5">
       <c r="A83" s="2" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C83" s="1" t="s">
         <v>18</v>
@@ -4206,7 +4282,7 @@
     </row>
     <row r="84" spans="1:9" ht="121.5">
       <c r="A84" s="2" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C84" s="1" t="s">
         <v>18</v>
@@ -4232,7 +4308,7 @@
     </row>
     <row r="85" spans="1:9" ht="67.5">
       <c r="A85" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C85" s="1" t="s">
         <v>18</v>
@@ -4250,7 +4326,7 @@
         <v>40</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="I85" s="4">
         <v>1</v>
@@ -4258,7 +4334,7 @@
     </row>
     <row r="86" spans="1:9" ht="121.5">
       <c r="A86" s="2" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B86" s="5" t="s">
         <v>121</v>
@@ -4287,7 +4363,7 @@
     </row>
     <row r="87" spans="1:9" ht="54">
       <c r="A87" s="2" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C87" s="1" t="s">
         <v>18</v>
@@ -4313,7 +4389,7 @@
     </row>
     <row r="88" spans="1:9" ht="67.5">
       <c r="A88" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C88" s="1" t="s">
         <v>18</v>
@@ -4339,7 +4415,7 @@
     </row>
     <row r="89" spans="1:9" ht="121.5">
       <c r="A89" s="2" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>122</v>
@@ -4368,7 +4444,7 @@
     </row>
     <row r="90" spans="1:9" ht="54">
       <c r="A90" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C90" s="1" t="s">
         <v>18</v>
@@ -4394,7 +4470,7 @@
     </row>
     <row r="91" spans="1:9" ht="67.5">
       <c r="A91" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C91" s="1" t="s">
         <v>18</v>
@@ -4420,7 +4496,7 @@
     </row>
     <row r="92" spans="1:9" ht="67.5">
       <c r="A92" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C92" s="1" t="s">
         <v>18</v>
@@ -4438,7 +4514,7 @@
         <v>132</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I92" s="4">
         <v>1</v>
@@ -4446,7 +4522,7 @@
     </row>
     <row r="93" spans="1:9" ht="67.5">
       <c r="A93" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C93" s="1" t="s">
         <v>18</v>
@@ -4464,35 +4540,168 @@
         <v>133</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I93" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:9" ht="94.5">
+    <row r="94" spans="1:9" ht="135">
       <c r="A94" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D94" s="4">
+        <v>1</v>
+      </c>
+      <c r="E94" s="4">
+        <v>1</v>
+      </c>
+      <c r="F94" s="4">
+        <v>1</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I94" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" ht="81">
+      <c r="A95" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D95" s="4">
+        <v>1</v>
+      </c>
+      <c r="E95" s="4">
+        <v>1</v>
+      </c>
+      <c r="F95" s="4">
+        <v>1</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="I95" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" ht="81">
+      <c r="A96" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D96" s="4">
+        <v>1</v>
+      </c>
+      <c r="E96" s="4">
+        <v>2</v>
+      </c>
+      <c r="F96" s="4">
+        <v>1</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="I96" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="81">
+      <c r="A97" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D97" s="4">
+        <v>1</v>
+      </c>
+      <c r="E97" s="4">
+        <v>2</v>
+      </c>
+      <c r="F97" s="4">
+        <v>1</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="I97" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="81">
+      <c r="A98" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D98" s="4">
+        <v>1</v>
+      </c>
+      <c r="E98" s="4">
+        <v>2</v>
+      </c>
+      <c r="F98" s="4">
+        <v>1</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="I98" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="81">
+      <c r="A99" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D99" s="4">
+        <v>1</v>
+      </c>
+      <c r="E99" s="4">
+        <v>2</v>
+      </c>
+      <c r="F99" s="4">
+        <v>1</v>
+      </c>
+      <c r="G99" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="C94" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D94" s="4">
-        <v>1</v>
-      </c>
-      <c r="E94" s="4">
-        <v>2</v>
-      </c>
-      <c r="F94" s="4">
-        <v>1</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="H94" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I94" s="4">
+      <c r="H99" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I99" s="4">
         <v>1</v>
       </c>
     </row>
